--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -589,12 +589,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 36</t>
+          <t>Name 85</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -617,7 +617,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 13</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -635,12 +635,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 69</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -658,12 +658,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 60</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Name 79</t>
+          <t>Name 12</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 22</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 68</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 40</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Name 40</t>
+          <t>Name 68</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 07, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 08, 2026.</t>
         </is>
       </c>
     </row>
@@ -539,19 +539,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relay between </t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2 and 3</t>
-        </is>
+          <t>Rounds</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Rounds</t>
+          <t>Boards per round</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -561,12 +559,10 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Boards per round</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>3</v>
-      </c>
+          <t>Square Movement</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -589,12 +585,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 69</t>
+          <t>Name 32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 85</t>
+          <t>Name 86</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -612,12 +608,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -635,12 +631,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 17</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -658,12 +654,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Name 60</t>
+          <t>Name 38</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Name 12</t>
+          <t>Name 18</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -706,12 +702,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 71</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -729,12 +725,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -752,12 +748,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 27</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 40</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -775,12 +771,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Name 68</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 32</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -585,12 +585,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 32</t>
+          <t>Name 25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -608,12 +608,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 84</t>
+          <t>Name 76</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -631,12 +631,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 17</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -654,12 +654,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Name 38</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Name 18</t>
+          <t>Name 17</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -702,12 +702,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 74</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -725,12 +725,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 68</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -748,12 +748,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 58</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -771,12 +771,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Name 32</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 08, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 10, 2026.</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 25</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 71</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -608,12 +608,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 41</t>
+          <t>Name 46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 76</t>
+          <t>Name 28</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -636,7 +636,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 40</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -654,12 +654,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 58</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Name 17</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -702,12 +702,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 74</t>
+          <t>Name 51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -725,12 +725,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 68</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -748,12 +748,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 25</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -771,12 +771,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Name 21</t>
+          <t>Name 34</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 10, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 11, 2026.</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -608,12 +608,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 46</t>
+          <t>Name 58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 13</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -631,12 +631,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 85</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 40</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -654,12 +654,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 18</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -702,12 +702,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 69</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -725,12 +725,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 25</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -748,12 +748,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 25</t>
+          <t>Name 90</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -771,12 +771,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -87,25 +87,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,8 +121,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -505,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 11, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 18, 2026.</t>
         </is>
       </c>
     </row>
@@ -570,13 +564,15 @@
           <t>NS Pairs</t>
         </is>
       </c>
-      <c r="D9" s="4">
-        <f>SUMIF('By Board'!D3:D50,"="&amp;A9,'By Board'!O3:O50)/12</f>
-        <v/>
-      </c>
-      <c r="E9" s="5">
-        <f>SUMIF('By Board'!D3:D50,"="&amp;A9,'By Board'!M3:M50)</f>
-        <v/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -585,19 +581,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 69</t>
-        </is>
-      </c>
-      <c r="D10" s="6">
+          <t>Name 30</t>
+        </is>
+      </c>
+      <c r="D10" s="4">
         <f>SUMIF('By Board'!D3:D50,"="&amp;A10,'By Board'!O3:O50)/12</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <f>SUMIF('By Board'!D3:D50,"="&amp;A10,'By Board'!M3:M50)</f>
         <v/>
       </c>
@@ -608,19 +604,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 13</t>
-        </is>
-      </c>
-      <c r="D11" s="6">
+          <t>Name 65</t>
+        </is>
+      </c>
+      <c r="D11" s="4">
         <f>SUMIF('By Board'!D3:D50,"="&amp;A11,'By Board'!O3:O50)/12</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <f>SUMIF('By Board'!D3:D50,"="&amp;A11,'By Board'!M3:M50)</f>
         <v/>
       </c>
@@ -631,40 +627,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 85</t>
+          <t>Name 19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 84</t>
-        </is>
-      </c>
-      <c r="D12" s="6">
+          <t>Name 89</t>
+        </is>
+      </c>
+      <c r="D12" s="4">
         <f>SUMIF('By Board'!D3:D50,"="&amp;A12,'By Board'!O3:O50)/12</f>
         <v/>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <f>SUMIF('By Board'!D3:D50,"="&amp;A12,'By Board'!M3:M50)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Name 30</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Name 18</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Name 34</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Name 46</t>
+        </is>
+      </c>
+      <c r="D13" s="8">
+        <f>SUMIF('By Board'!D3:D50,"="&amp;A13,'By Board'!O3:O50)/12</f>
+        <v/>
+      </c>
+      <c r="E13" s="9">
+        <f>SUMIF('By Board'!D3:D50,"="&amp;A13,'By Board'!M3:M50)</f>
+        <v/>
+      </c>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="C14" s="10" t="inlineStr">
@@ -687,13 +689,15 @@
           <t>EW Pairs</t>
         </is>
       </c>
-      <c r="D16" s="4">
-        <f>SUMIF('By Board'!E3:E50,"="&amp;A16,'By Board'!P3:P50)/12</f>
-        <v/>
-      </c>
-      <c r="E16" s="5">
-        <f>SUMIF('By Board'!E3:E50,"="&amp;A16,'By Board'!N3:N50)</f>
-        <v/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -702,19 +706,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 23</t>
+          <t>Name 57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 61</t>
-        </is>
-      </c>
-      <c r="D17" s="6">
+          <t>Name 79</t>
+        </is>
+      </c>
+      <c r="D17" s="4">
         <f>SUMIF('By Board'!E3:E50,"="&amp;A17,'By Board'!P3:P50)/12</f>
         <v/>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <f>SUMIF('By Board'!E3:E50,"="&amp;A17,'By Board'!N3:N50)</f>
         <v/>
       </c>
@@ -725,19 +729,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 73</t>
-        </is>
-      </c>
-      <c r="D18" s="6">
+          <t>Name 18</t>
+        </is>
+      </c>
+      <c r="D18" s="4">
         <f>SUMIF('By Board'!E3:E50,"="&amp;A18,'By Board'!P3:P50)/12</f>
         <v/>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <f>SUMIF('By Board'!E3:E50,"="&amp;A18,'By Board'!N3:N50)</f>
         <v/>
       </c>
@@ -748,40 +752,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 90</t>
-        </is>
-      </c>
-      <c r="D19" s="6">
+          <t>Name 29</t>
+        </is>
+      </c>
+      <c r="D19" s="4">
         <f>SUMIF('By Board'!E3:E50,"="&amp;A19,'By Board'!P3:P50)/12</f>
         <v/>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <f>SUMIF('By Board'!E3:E50,"="&amp;A19,'By Board'!N3:N50)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Name 65</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Name 16</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Name 51</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Name 11</t>
+        </is>
+      </c>
+      <c r="D20" s="8">
+        <f>SUMIF('By Board'!E3:E50,"="&amp;A20,'By Board'!P3:P50)/12</f>
+        <v/>
+      </c>
+      <c r="E20" s="9">
+        <f>SUMIF('By Board'!E3:E50,"="&amp;A20,'By Board'!N3:N50)</f>
+        <v/>
+      </c>
+      <c r="F20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="10" t="inlineStr">
@@ -1041,15 +1051,15 @@
         <f>AVERAGE(AA3:AC3)</f>
         <v/>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="5">
         <f>AVERAGE(AD3:AF3)</f>
         <v/>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="4">
         <f>IF(COUNT(U3:W3)&gt;0,Q3/COUNT(U3:W3),0.5)</f>
         <v/>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="4">
         <f>IF(COUNT(X3:Z3)&gt;0,R3/COUNT(X3:Z3),0.5)</f>
         <v/>
       </c>
@@ -1167,15 +1177,15 @@
         <f>AVERAGE(AA4:AC4)</f>
         <v/>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="5">
         <f>AVERAGE(AD4:AF4)</f>
         <v/>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="4">
         <f>IF(COUNT(U4:W4)&gt;0,Q4/COUNT(U4:W4),0.5)</f>
         <v/>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="4">
         <f>IF(COUNT(X4:Z4)&gt;0,R4/COUNT(X4:Z4),0.5)</f>
         <v/>
       </c>
@@ -1293,15 +1303,15 @@
         <f>AVERAGE(AA5:AC5)</f>
         <v/>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="5">
         <f>AVERAGE(AD5:AF5)</f>
         <v/>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="4">
         <f>IF(COUNT(U5:W5)&gt;0,Q5/COUNT(U5:W5),0.5)</f>
         <v/>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="4">
         <f>IF(COUNT(X5:Z5)&gt;0,R5/COUNT(X5:Z5),0.5)</f>
         <v/>
       </c>
@@ -1371,7 +1381,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n"/>
+      <c r="A6" s="7" t="n"/>
       <c r="B6" s="19">
         <f>'By Round'!A15</f>
         <v/>
@@ -1392,27 +1402,27 @@
         <f>IF(ISBLANK('By Round'!F24),"",'By Round'!F24)</f>
         <v/>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="7">
         <f>IF(ISBLANK('By Round'!G24),"",'By Round'!G24)</f>
         <v/>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="7">
         <f>IF(ISBLANK('By Round'!H24),"",'By Round'!H24)</f>
         <v/>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="7">
         <f>IF(ISBLANK('By Round'!I24),"",'By Round'!I24)</f>
         <v/>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <f>IF(ISBLANK('By Round'!J24),"",'By Round'!J24)</f>
         <v/>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="7">
         <f>IF(ISBLANK('By Round'!K24),"",'By Round'!K24)</f>
         <v/>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="7">
         <f>IF(ISBLANK('By Round'!L24),"",'By Round'!L24)</f>
         <v/>
       </c>
@@ -1420,79 +1430,79 @@
         <f>AVERAGE(AA6:AC6)</f>
         <v/>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="9">
         <f>AVERAGE(AD6:AF6)</f>
         <v/>
       </c>
-      <c r="O6" s="22">
+      <c r="O6" s="8">
         <f>IF(COUNT(U6:W6)&gt;0,Q6/COUNT(U6:W6),0.5)</f>
         <v/>
       </c>
-      <c r="P6" s="22">
+      <c r="P6" s="8">
         <f>IF(COUNT(X6:Z6)&gt;0,R6/COUNT(X6:Z6),0.5)</f>
         <v/>
       </c>
-      <c r="Q6" s="23">
+      <c r="Q6" s="21">
         <f>SUM(U6:W6)</f>
         <v/>
       </c>
-      <c r="R6" s="23">
+      <c r="R6" s="21">
         <f>SUM(X6:Z6)</f>
         <v/>
       </c>
-      <c r="S6" s="24">
+      <c r="S6" s="22">
         <f>IF(ISNUMBER(K6),K6,IF(ISNUMBER(L6),-L6,""))</f>
         <v/>
       </c>
-      <c r="T6" s="9">
+      <c r="T6" s="7">
         <f>IF(ISNUMBER(L6),L6,IF(ISNUMBER(K6),-K6,""))</f>
         <v/>
       </c>
-      <c r="U6" s="24">
+      <c r="U6" s="22">
         <f>IF(ISNUMBER(S6),IF(ISNUMBER(S3),IF(S6&gt;S3,1.0,IF(S6=S3,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V6" s="9">
+      <c r="V6" s="7">
         <f>IF(ISNUMBER(S6),IF(ISNUMBER(S4),IF(S6&gt;S4,1.0,IF(S6=S4,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W6" s="9">
+      <c r="W6" s="7">
         <f>IF(ISNUMBER(S6),IF(ISNUMBER(S5),IF(S6&gt;S5,1.0,IF(S6=S5,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X6" s="9">
+      <c r="X6" s="7">
         <f>IF(ISNUMBER(T6),IF(ISNUMBER(T3),IF(T6&gt;T3,1.0,IF(T6=T3,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y6" s="9">
+      <c r="Y6" s="7">
         <f>IF(ISNUMBER(T6),IF(ISNUMBER(T4),IF(T6&gt;T4,1.0,IF(T6=T4,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z6" s="9">
+      <c r="Z6" s="7">
         <f>IF(ISNUMBER(T6),IF(ISNUMBER(T5),IF(T6&gt;T5,1.0,IF(T6=T5,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA6" s="24">
+      <c r="AA6" s="22">
         <f>IF(AND(ISNUMBER(S6),ISNUMBER(S3)),VLOOKUP(ABS(S6-S3),'IMP Table'!$A$2:$C$26,3)*SIGN(S6-S3),0)</f>
         <v/>
       </c>
-      <c r="AB6" s="9">
+      <c r="AB6" s="7">
         <f>IF(AND(ISNUMBER(S6),ISNUMBER(S4)),VLOOKUP(ABS(S6-S4),'IMP Table'!$A$2:$C$26,3)*SIGN(S6-S4),0)</f>
         <v/>
       </c>
-      <c r="AC6" s="9">
+      <c r="AC6" s="7">
         <f>IF(AND(ISNUMBER(S6),ISNUMBER(S5)),VLOOKUP(ABS(S6-S5),'IMP Table'!$A$2:$C$26,3)*SIGN(S6-S5),0)</f>
         <v/>
       </c>
-      <c r="AD6" s="9">
+      <c r="AD6" s="7">
         <f>IF(AND(ISNUMBER(T6),ISNUMBER(T3)),VLOOKUP(ABS(T6-T3),'IMP Table'!$A$2:$C$26,3)*SIGN(T6-T3),0)</f>
         <v/>
       </c>
-      <c r="AE6" s="9">
+      <c r="AE6" s="7">
         <f>IF(AND(ISNUMBER(T6),ISNUMBER(T4)),VLOOKUP(ABS(T6-T4),'IMP Table'!$A$2:$C$26,3)*SIGN(T6-T4),0)</f>
         <v/>
       </c>
-      <c r="AF6" s="9">
+      <c r="AF6" s="7">
         <f>IF(AND(ISNUMBER(T6),ISNUMBER(T5)),VLOOKUP(ABS(T6-T5),'IMP Table'!$A$2:$C$26,3)*SIGN(T6-T5),0)</f>
         <v/>
       </c>
@@ -1549,15 +1559,15 @@
         <f>AVERAGE(AA7:AC7)</f>
         <v/>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="5">
         <f>AVERAGE(AD7:AF7)</f>
         <v/>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="4">
         <f>IF(COUNT(U7:W7)&gt;0,Q7/COUNT(U7:W7),0.5)</f>
         <v/>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="4">
         <f>IF(COUNT(X7:Z7)&gt;0,R7/COUNT(X7:Z7),0.5)</f>
         <v/>
       </c>
@@ -1675,15 +1685,15 @@
         <f>AVERAGE(AA8:AC8)</f>
         <v/>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="5">
         <f>AVERAGE(AD8:AF8)</f>
         <v/>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="4">
         <f>IF(COUNT(U8:W8)&gt;0,Q8/COUNT(U8:W8),0.5)</f>
         <v/>
       </c>
-      <c r="P8" s="6">
+      <c r="P8" s="4">
         <f>IF(COUNT(X8:Z8)&gt;0,R8/COUNT(X8:Z8),0.5)</f>
         <v/>
       </c>
@@ -1801,15 +1811,15 @@
         <f>AVERAGE(AA9:AC9)</f>
         <v/>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="5">
         <f>AVERAGE(AD9:AF9)</f>
         <v/>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="4">
         <f>IF(COUNT(U9:W9)&gt;0,Q9/COUNT(U9:W9),0.5)</f>
         <v/>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="4">
         <f>IF(COUNT(X9:Z9)&gt;0,R9/COUNT(X9:Z9),0.5)</f>
         <v/>
       </c>
@@ -1879,7 +1889,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
+      <c r="A10" s="7" t="n"/>
       <c r="B10" s="19">
         <f>'By Round'!A15</f>
         <v/>
@@ -1900,27 +1910,27 @@
         <f>IF(ISBLANK('By Round'!F25),"",'By Round'!F25)</f>
         <v/>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="7">
         <f>IF(ISBLANK('By Round'!G25),"",'By Round'!G25)</f>
         <v/>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="7">
         <f>IF(ISBLANK('By Round'!H25),"",'By Round'!H25)</f>
         <v/>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="7">
         <f>IF(ISBLANK('By Round'!I25),"",'By Round'!I25)</f>
         <v/>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="7">
         <f>IF(ISBLANK('By Round'!J25),"",'By Round'!J25)</f>
         <v/>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="7">
         <f>IF(ISBLANK('By Round'!K25),"",'By Round'!K25)</f>
         <v/>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="7">
         <f>IF(ISBLANK('By Round'!L25),"",'By Round'!L25)</f>
         <v/>
       </c>
@@ -1928,79 +1938,79 @@
         <f>AVERAGE(AA10:AC10)</f>
         <v/>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="9">
         <f>AVERAGE(AD10:AF10)</f>
         <v/>
       </c>
-      <c r="O10" s="22">
+      <c r="O10" s="8">
         <f>IF(COUNT(U10:W10)&gt;0,Q10/COUNT(U10:W10),0.5)</f>
         <v/>
       </c>
-      <c r="P10" s="22">
+      <c r="P10" s="8">
         <f>IF(COUNT(X10:Z10)&gt;0,R10/COUNT(X10:Z10),0.5)</f>
         <v/>
       </c>
-      <c r="Q10" s="23">
+      <c r="Q10" s="21">
         <f>SUM(U10:W10)</f>
         <v/>
       </c>
-      <c r="R10" s="23">
+      <c r="R10" s="21">
         <f>SUM(X10:Z10)</f>
         <v/>
       </c>
-      <c r="S10" s="24">
+      <c r="S10" s="22">
         <f>IF(ISNUMBER(K10),K10,IF(ISNUMBER(L10),-L10,""))</f>
         <v/>
       </c>
-      <c r="T10" s="9">
+      <c r="T10" s="7">
         <f>IF(ISNUMBER(L10),L10,IF(ISNUMBER(K10),-K10,""))</f>
         <v/>
       </c>
-      <c r="U10" s="24">
+      <c r="U10" s="22">
         <f>IF(ISNUMBER(S10),IF(ISNUMBER(S7),IF(S10&gt;S7,1.0,IF(S10=S7,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V10" s="9">
+      <c r="V10" s="7">
         <f>IF(ISNUMBER(S10),IF(ISNUMBER(S8),IF(S10&gt;S8,1.0,IF(S10=S8,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W10" s="9">
+      <c r="W10" s="7">
         <f>IF(ISNUMBER(S10),IF(ISNUMBER(S9),IF(S10&gt;S9,1.0,IF(S10=S9,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X10" s="9">
+      <c r="X10" s="7">
         <f>IF(ISNUMBER(T10),IF(ISNUMBER(T7),IF(T10&gt;T7,1.0,IF(T10=T7,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y10" s="9">
+      <c r="Y10" s="7">
         <f>IF(ISNUMBER(T10),IF(ISNUMBER(T8),IF(T10&gt;T8,1.0,IF(T10=T8,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z10" s="9">
+      <c r="Z10" s="7">
         <f>IF(ISNUMBER(T10),IF(ISNUMBER(T9),IF(T10&gt;T9,1.0,IF(T10=T9,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA10" s="24">
+      <c r="AA10" s="22">
         <f>IF(AND(ISNUMBER(S10),ISNUMBER(S7)),VLOOKUP(ABS(S10-S7),'IMP Table'!$A$2:$C$26,3)*SIGN(S10-S7),0)</f>
         <v/>
       </c>
-      <c r="AB10" s="9">
+      <c r="AB10" s="7">
         <f>IF(AND(ISNUMBER(S10),ISNUMBER(S8)),VLOOKUP(ABS(S10-S8),'IMP Table'!$A$2:$C$26,3)*SIGN(S10-S8),0)</f>
         <v/>
       </c>
-      <c r="AC10" s="9">
+      <c r="AC10" s="7">
         <f>IF(AND(ISNUMBER(S10),ISNUMBER(S9)),VLOOKUP(ABS(S10-S9),'IMP Table'!$A$2:$C$26,3)*SIGN(S10-S9),0)</f>
         <v/>
       </c>
-      <c r="AD10" s="9">
+      <c r="AD10" s="7">
         <f>IF(AND(ISNUMBER(T10),ISNUMBER(T7)),VLOOKUP(ABS(T10-T7),'IMP Table'!$A$2:$C$26,3)*SIGN(T10-T7),0)</f>
         <v/>
       </c>
-      <c r="AE10" s="9">
+      <c r="AE10" s="7">
         <f>IF(AND(ISNUMBER(T10),ISNUMBER(T8)),VLOOKUP(ABS(T10-T8),'IMP Table'!$A$2:$C$26,3)*SIGN(T10-T8),0)</f>
         <v/>
       </c>
-      <c r="AF10" s="9">
+      <c r="AF10" s="7">
         <f>IF(AND(ISNUMBER(T10),ISNUMBER(T9)),VLOOKUP(ABS(T10-T9),'IMP Table'!$A$2:$C$26,3)*SIGN(T10-T9),0)</f>
         <v/>
       </c>
@@ -2057,15 +2067,15 @@
         <f>AVERAGE(AA11:AC11)</f>
         <v/>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="5">
         <f>AVERAGE(AD11:AF11)</f>
         <v/>
       </c>
-      <c r="O11" s="6">
+      <c r="O11" s="4">
         <f>IF(COUNT(U11:W11)&gt;0,Q11/COUNT(U11:W11),0.5)</f>
         <v/>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="4">
         <f>IF(COUNT(X11:Z11)&gt;0,R11/COUNT(X11:Z11),0.5)</f>
         <v/>
       </c>
@@ -2183,15 +2193,15 @@
         <f>AVERAGE(AA12:AC12)</f>
         <v/>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="5">
         <f>AVERAGE(AD12:AF12)</f>
         <v/>
       </c>
-      <c r="O12" s="6">
+      <c r="O12" s="4">
         <f>IF(COUNT(U12:W12)&gt;0,Q12/COUNT(U12:W12),0.5)</f>
         <v/>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="4">
         <f>IF(COUNT(X12:Z12)&gt;0,R12/COUNT(X12:Z12),0.5)</f>
         <v/>
       </c>
@@ -2309,15 +2319,15 @@
         <f>AVERAGE(AA13:AC13)</f>
         <v/>
       </c>
-      <c r="N13" s="7">
+      <c r="N13" s="5">
         <f>AVERAGE(AD13:AF13)</f>
         <v/>
       </c>
-      <c r="O13" s="6">
+      <c r="O13" s="4">
         <f>IF(COUNT(U13:W13)&gt;0,Q13/COUNT(U13:W13),0.5)</f>
         <v/>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="4">
         <f>IF(COUNT(X13:Z13)&gt;0,R13/COUNT(X13:Z13),0.5)</f>
         <v/>
       </c>
@@ -2387,7 +2397,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
+      <c r="A14" s="7" t="n"/>
       <c r="B14" s="19">
         <f>'By Round'!A15</f>
         <v/>
@@ -2408,27 +2418,27 @@
         <f>IF(ISBLANK('By Round'!F26),"",'By Round'!F26)</f>
         <v/>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="7">
         <f>IF(ISBLANK('By Round'!G26),"",'By Round'!G26)</f>
         <v/>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="7">
         <f>IF(ISBLANK('By Round'!H26),"",'By Round'!H26)</f>
         <v/>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="7">
         <f>IF(ISBLANK('By Round'!I26),"",'By Round'!I26)</f>
         <v/>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="7">
         <f>IF(ISBLANK('By Round'!J26),"",'By Round'!J26)</f>
         <v/>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="7">
         <f>IF(ISBLANK('By Round'!K26),"",'By Round'!K26)</f>
         <v/>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="7">
         <f>IF(ISBLANK('By Round'!L26),"",'By Round'!L26)</f>
         <v/>
       </c>
@@ -2436,79 +2446,79 @@
         <f>AVERAGE(AA14:AC14)</f>
         <v/>
       </c>
-      <c r="N14" s="21">
+      <c r="N14" s="9">
         <f>AVERAGE(AD14:AF14)</f>
         <v/>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="8">
         <f>IF(COUNT(U14:W14)&gt;0,Q14/COUNT(U14:W14),0.5)</f>
         <v/>
       </c>
-      <c r="P14" s="22">
+      <c r="P14" s="8">
         <f>IF(COUNT(X14:Z14)&gt;0,R14/COUNT(X14:Z14),0.5)</f>
         <v/>
       </c>
-      <c r="Q14" s="23">
+      <c r="Q14" s="21">
         <f>SUM(U14:W14)</f>
         <v/>
       </c>
-      <c r="R14" s="23">
+      <c r="R14" s="21">
         <f>SUM(X14:Z14)</f>
         <v/>
       </c>
-      <c r="S14" s="24">
+      <c r="S14" s="22">
         <f>IF(ISNUMBER(K14),K14,IF(ISNUMBER(L14),-L14,""))</f>
         <v/>
       </c>
-      <c r="T14" s="9">
+      <c r="T14" s="7">
         <f>IF(ISNUMBER(L14),L14,IF(ISNUMBER(K14),-K14,""))</f>
         <v/>
       </c>
-      <c r="U14" s="24">
+      <c r="U14" s="22">
         <f>IF(ISNUMBER(S14),IF(ISNUMBER(S11),IF(S14&gt;S11,1.0,IF(S14=S11,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V14" s="9">
+      <c r="V14" s="7">
         <f>IF(ISNUMBER(S14),IF(ISNUMBER(S12),IF(S14&gt;S12,1.0,IF(S14=S12,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W14" s="9">
+      <c r="W14" s="7">
         <f>IF(ISNUMBER(S14),IF(ISNUMBER(S13),IF(S14&gt;S13,1.0,IF(S14=S13,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X14" s="9">
+      <c r="X14" s="7">
         <f>IF(ISNUMBER(T14),IF(ISNUMBER(T11),IF(T14&gt;T11,1.0,IF(T14=T11,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y14" s="9">
+      <c r="Y14" s="7">
         <f>IF(ISNUMBER(T14),IF(ISNUMBER(T12),IF(T14&gt;T12,1.0,IF(T14=T12,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z14" s="9">
+      <c r="Z14" s="7">
         <f>IF(ISNUMBER(T14),IF(ISNUMBER(T13),IF(T14&gt;T13,1.0,IF(T14=T13,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA14" s="24">
+      <c r="AA14" s="22">
         <f>IF(AND(ISNUMBER(S14),ISNUMBER(S11)),VLOOKUP(ABS(S14-S11),'IMP Table'!$A$2:$C$26,3)*SIGN(S14-S11),0)</f>
         <v/>
       </c>
-      <c r="AB14" s="9">
+      <c r="AB14" s="7">
         <f>IF(AND(ISNUMBER(S14),ISNUMBER(S12)),VLOOKUP(ABS(S14-S12),'IMP Table'!$A$2:$C$26,3)*SIGN(S14-S12),0)</f>
         <v/>
       </c>
-      <c r="AC14" s="9">
+      <c r="AC14" s="7">
         <f>IF(AND(ISNUMBER(S14),ISNUMBER(S13)),VLOOKUP(ABS(S14-S13),'IMP Table'!$A$2:$C$26,3)*SIGN(S14-S13),0)</f>
         <v/>
       </c>
-      <c r="AD14" s="9">
+      <c r="AD14" s="7">
         <f>IF(AND(ISNUMBER(T14),ISNUMBER(T11)),VLOOKUP(ABS(T14-T11),'IMP Table'!$A$2:$C$26,3)*SIGN(T14-T11),0)</f>
         <v/>
       </c>
-      <c r="AE14" s="9">
+      <c r="AE14" s="7">
         <f>IF(AND(ISNUMBER(T14),ISNUMBER(T12)),VLOOKUP(ABS(T14-T12),'IMP Table'!$A$2:$C$26,3)*SIGN(T14-T12),0)</f>
         <v/>
       </c>
-      <c r="AF14" s="9">
+      <c r="AF14" s="7">
         <f>IF(AND(ISNUMBER(T14),ISNUMBER(T13)),VLOOKUP(ABS(T14-T13),'IMP Table'!$A$2:$C$26,3)*SIGN(T14-T13),0)</f>
         <v/>
       </c>
@@ -2565,15 +2575,15 @@
         <f>AVERAGE(AA15:AC15)</f>
         <v/>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="5">
         <f>AVERAGE(AD15:AF15)</f>
         <v/>
       </c>
-      <c r="O15" s="6">
+      <c r="O15" s="4">
         <f>IF(COUNT(U15:W15)&gt;0,Q15/COUNT(U15:W15),0.5)</f>
         <v/>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="4">
         <f>IF(COUNT(X15:Z15)&gt;0,R15/COUNT(X15:Z15),0.5)</f>
         <v/>
       </c>
@@ -2691,15 +2701,15 @@
         <f>AVERAGE(AA16:AC16)</f>
         <v/>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="5">
         <f>AVERAGE(AD16:AF16)</f>
         <v/>
       </c>
-      <c r="O16" s="6">
+      <c r="O16" s="4">
         <f>IF(COUNT(U16:W16)&gt;0,Q16/COUNT(U16:W16),0.5)</f>
         <v/>
       </c>
-      <c r="P16" s="6">
+      <c r="P16" s="4">
         <f>IF(COUNT(X16:Z16)&gt;0,R16/COUNT(X16:Z16),0.5)</f>
         <v/>
       </c>
@@ -2817,15 +2827,15 @@
         <f>AVERAGE(AA17:AC17)</f>
         <v/>
       </c>
-      <c r="N17" s="7">
+      <c r="N17" s="5">
         <f>AVERAGE(AD17:AF17)</f>
         <v/>
       </c>
-      <c r="O17" s="6">
+      <c r="O17" s="4">
         <f>IF(COUNT(U17:W17)&gt;0,Q17/COUNT(U17:W17),0.5)</f>
         <v/>
       </c>
-      <c r="P17" s="6">
+      <c r="P17" s="4">
         <f>IF(COUNT(X17:Z17)&gt;0,R17/COUNT(X17:Z17),0.5)</f>
         <v/>
       </c>
@@ -2895,7 +2905,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
+      <c r="A18" s="7" t="n"/>
       <c r="B18" s="19">
         <f>'By Round'!A27</f>
         <v/>
@@ -2916,27 +2926,27 @@
         <f>IF(ISBLANK('By Round'!F36),"",'By Round'!F36)</f>
         <v/>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="7">
         <f>IF(ISBLANK('By Round'!G36),"",'By Round'!G36)</f>
         <v/>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="7">
         <f>IF(ISBLANK('By Round'!H36),"",'By Round'!H36)</f>
         <v/>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="7">
         <f>IF(ISBLANK('By Round'!I36),"",'By Round'!I36)</f>
         <v/>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="7">
         <f>IF(ISBLANK('By Round'!J36),"",'By Round'!J36)</f>
         <v/>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="7">
         <f>IF(ISBLANK('By Round'!K36),"",'By Round'!K36)</f>
         <v/>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="7">
         <f>IF(ISBLANK('By Round'!L36),"",'By Round'!L36)</f>
         <v/>
       </c>
@@ -2944,79 +2954,79 @@
         <f>AVERAGE(AA18:AC18)</f>
         <v/>
       </c>
-      <c r="N18" s="21">
+      <c r="N18" s="9">
         <f>AVERAGE(AD18:AF18)</f>
         <v/>
       </c>
-      <c r="O18" s="22">
+      <c r="O18" s="8">
         <f>IF(COUNT(U18:W18)&gt;0,Q18/COUNT(U18:W18),0.5)</f>
         <v/>
       </c>
-      <c r="P18" s="22">
+      <c r="P18" s="8">
         <f>IF(COUNT(X18:Z18)&gt;0,R18/COUNT(X18:Z18),0.5)</f>
         <v/>
       </c>
-      <c r="Q18" s="23">
+      <c r="Q18" s="21">
         <f>SUM(U18:W18)</f>
         <v/>
       </c>
-      <c r="R18" s="23">
+      <c r="R18" s="21">
         <f>SUM(X18:Z18)</f>
         <v/>
       </c>
-      <c r="S18" s="24">
+      <c r="S18" s="22">
         <f>IF(ISNUMBER(K18),K18,IF(ISNUMBER(L18),-L18,""))</f>
         <v/>
       </c>
-      <c r="T18" s="9">
+      <c r="T18" s="7">
         <f>IF(ISNUMBER(L18),L18,IF(ISNUMBER(K18),-K18,""))</f>
         <v/>
       </c>
-      <c r="U18" s="24">
+      <c r="U18" s="22">
         <f>IF(ISNUMBER(S18),IF(ISNUMBER(S15),IF(S18&gt;S15,1.0,IF(S18=S15,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V18" s="9">
+      <c r="V18" s="7">
         <f>IF(ISNUMBER(S18),IF(ISNUMBER(S16),IF(S18&gt;S16,1.0,IF(S18=S16,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W18" s="9">
+      <c r="W18" s="7">
         <f>IF(ISNUMBER(S18),IF(ISNUMBER(S17),IF(S18&gt;S17,1.0,IF(S18=S17,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X18" s="9">
+      <c r="X18" s="7">
         <f>IF(ISNUMBER(T18),IF(ISNUMBER(T15),IF(T18&gt;T15,1.0,IF(T18=T15,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y18" s="9">
+      <c r="Y18" s="7">
         <f>IF(ISNUMBER(T18),IF(ISNUMBER(T16),IF(T18&gt;T16,1.0,IF(T18=T16,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z18" s="9">
+      <c r="Z18" s="7">
         <f>IF(ISNUMBER(T18),IF(ISNUMBER(T17),IF(T18&gt;T17,1.0,IF(T18=T17,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA18" s="24">
+      <c r="AA18" s="22">
         <f>IF(AND(ISNUMBER(S18),ISNUMBER(S15)),VLOOKUP(ABS(S18-S15),'IMP Table'!$A$2:$C$26,3)*SIGN(S18-S15),0)</f>
         <v/>
       </c>
-      <c r="AB18" s="9">
+      <c r="AB18" s="7">
         <f>IF(AND(ISNUMBER(S18),ISNUMBER(S16)),VLOOKUP(ABS(S18-S16),'IMP Table'!$A$2:$C$26,3)*SIGN(S18-S16),0)</f>
         <v/>
       </c>
-      <c r="AC18" s="9">
+      <c r="AC18" s="7">
         <f>IF(AND(ISNUMBER(S18),ISNUMBER(S17)),VLOOKUP(ABS(S18-S17),'IMP Table'!$A$2:$C$26,3)*SIGN(S18-S17),0)</f>
         <v/>
       </c>
-      <c r="AD18" s="9">
+      <c r="AD18" s="7">
         <f>IF(AND(ISNUMBER(T18),ISNUMBER(T15)),VLOOKUP(ABS(T18-T15),'IMP Table'!$A$2:$C$26,3)*SIGN(T18-T15),0)</f>
         <v/>
       </c>
-      <c r="AE18" s="9">
+      <c r="AE18" s="7">
         <f>IF(AND(ISNUMBER(T18),ISNUMBER(T16)),VLOOKUP(ABS(T18-T16),'IMP Table'!$A$2:$C$26,3)*SIGN(T18-T16),0)</f>
         <v/>
       </c>
-      <c r="AF18" s="9">
+      <c r="AF18" s="7">
         <f>IF(AND(ISNUMBER(T18),ISNUMBER(T17)),VLOOKUP(ABS(T18-T17),'IMP Table'!$A$2:$C$26,3)*SIGN(T18-T17),0)</f>
         <v/>
       </c>
@@ -3073,15 +3083,15 @@
         <f>AVERAGE(AA19:AC19)</f>
         <v/>
       </c>
-      <c r="N19" s="7">
+      <c r="N19" s="5">
         <f>AVERAGE(AD19:AF19)</f>
         <v/>
       </c>
-      <c r="O19" s="6">
+      <c r="O19" s="4">
         <f>IF(COUNT(U19:W19)&gt;0,Q19/COUNT(U19:W19),0.5)</f>
         <v/>
       </c>
-      <c r="P19" s="6">
+      <c r="P19" s="4">
         <f>IF(COUNT(X19:Z19)&gt;0,R19/COUNT(X19:Z19),0.5)</f>
         <v/>
       </c>
@@ -3199,15 +3209,15 @@
         <f>AVERAGE(AA20:AC20)</f>
         <v/>
       </c>
-      <c r="N20" s="7">
+      <c r="N20" s="5">
         <f>AVERAGE(AD20:AF20)</f>
         <v/>
       </c>
-      <c r="O20" s="6">
+      <c r="O20" s="4">
         <f>IF(COUNT(U20:W20)&gt;0,Q20/COUNT(U20:W20),0.5)</f>
         <v/>
       </c>
-      <c r="P20" s="6">
+      <c r="P20" s="4">
         <f>IF(COUNT(X20:Z20)&gt;0,R20/COUNT(X20:Z20),0.5)</f>
         <v/>
       </c>
@@ -3325,15 +3335,15 @@
         <f>AVERAGE(AA21:AC21)</f>
         <v/>
       </c>
-      <c r="N21" s="7">
+      <c r="N21" s="5">
         <f>AVERAGE(AD21:AF21)</f>
         <v/>
       </c>
-      <c r="O21" s="6">
+      <c r="O21" s="4">
         <f>IF(COUNT(U21:W21)&gt;0,Q21/COUNT(U21:W21),0.5)</f>
         <v/>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="4">
         <f>IF(COUNT(X21:Z21)&gt;0,R21/COUNT(X21:Z21),0.5)</f>
         <v/>
       </c>
@@ -3403,7 +3413,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
+      <c r="A22" s="7" t="n"/>
       <c r="B22" s="19">
         <f>'By Round'!A27</f>
         <v/>
@@ -3424,27 +3434,27 @@
         <f>IF(ISBLANK('By Round'!F37),"",'By Round'!F37)</f>
         <v/>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="7">
         <f>IF(ISBLANK('By Round'!G37),"",'By Round'!G37)</f>
         <v/>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="7">
         <f>IF(ISBLANK('By Round'!H37),"",'By Round'!H37)</f>
         <v/>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="7">
         <f>IF(ISBLANK('By Round'!I37),"",'By Round'!I37)</f>
         <v/>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="7">
         <f>IF(ISBLANK('By Round'!J37),"",'By Round'!J37)</f>
         <v/>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="7">
         <f>IF(ISBLANK('By Round'!K37),"",'By Round'!K37)</f>
         <v/>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="7">
         <f>IF(ISBLANK('By Round'!L37),"",'By Round'!L37)</f>
         <v/>
       </c>
@@ -3452,79 +3462,79 @@
         <f>AVERAGE(AA22:AC22)</f>
         <v/>
       </c>
-      <c r="N22" s="21">
+      <c r="N22" s="9">
         <f>AVERAGE(AD22:AF22)</f>
         <v/>
       </c>
-      <c r="O22" s="22">
+      <c r="O22" s="8">
         <f>IF(COUNT(U22:W22)&gt;0,Q22/COUNT(U22:W22),0.5)</f>
         <v/>
       </c>
-      <c r="P22" s="22">
+      <c r="P22" s="8">
         <f>IF(COUNT(X22:Z22)&gt;0,R22/COUNT(X22:Z22),0.5)</f>
         <v/>
       </c>
-      <c r="Q22" s="23">
+      <c r="Q22" s="21">
         <f>SUM(U22:W22)</f>
         <v/>
       </c>
-      <c r="R22" s="23">
+      <c r="R22" s="21">
         <f>SUM(X22:Z22)</f>
         <v/>
       </c>
-      <c r="S22" s="24">
+      <c r="S22" s="22">
         <f>IF(ISNUMBER(K22),K22,IF(ISNUMBER(L22),-L22,""))</f>
         <v/>
       </c>
-      <c r="T22" s="9">
+      <c r="T22" s="7">
         <f>IF(ISNUMBER(L22),L22,IF(ISNUMBER(K22),-K22,""))</f>
         <v/>
       </c>
-      <c r="U22" s="24">
+      <c r="U22" s="22">
         <f>IF(ISNUMBER(S22),IF(ISNUMBER(S19),IF(S22&gt;S19,1.0,IF(S22=S19,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V22" s="9">
+      <c r="V22" s="7">
         <f>IF(ISNUMBER(S22),IF(ISNUMBER(S20),IF(S22&gt;S20,1.0,IF(S22=S20,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W22" s="9">
+      <c r="W22" s="7">
         <f>IF(ISNUMBER(S22),IF(ISNUMBER(S21),IF(S22&gt;S21,1.0,IF(S22=S21,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X22" s="9">
+      <c r="X22" s="7">
         <f>IF(ISNUMBER(T22),IF(ISNUMBER(T19),IF(T22&gt;T19,1.0,IF(T22=T19,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y22" s="9">
+      <c r="Y22" s="7">
         <f>IF(ISNUMBER(T22),IF(ISNUMBER(T20),IF(T22&gt;T20,1.0,IF(T22=T20,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z22" s="9">
+      <c r="Z22" s="7">
         <f>IF(ISNUMBER(T22),IF(ISNUMBER(T21),IF(T22&gt;T21,1.0,IF(T22=T21,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA22" s="24">
+      <c r="AA22" s="22">
         <f>IF(AND(ISNUMBER(S22),ISNUMBER(S19)),VLOOKUP(ABS(S22-S19),'IMP Table'!$A$2:$C$26,3)*SIGN(S22-S19),0)</f>
         <v/>
       </c>
-      <c r="AB22" s="9">
+      <c r="AB22" s="7">
         <f>IF(AND(ISNUMBER(S22),ISNUMBER(S20)),VLOOKUP(ABS(S22-S20),'IMP Table'!$A$2:$C$26,3)*SIGN(S22-S20),0)</f>
         <v/>
       </c>
-      <c r="AC22" s="9">
+      <c r="AC22" s="7">
         <f>IF(AND(ISNUMBER(S22),ISNUMBER(S21)),VLOOKUP(ABS(S22-S21),'IMP Table'!$A$2:$C$26,3)*SIGN(S22-S21),0)</f>
         <v/>
       </c>
-      <c r="AD22" s="9">
+      <c r="AD22" s="7">
         <f>IF(AND(ISNUMBER(T22),ISNUMBER(T19)),VLOOKUP(ABS(T22-T19),'IMP Table'!$A$2:$C$26,3)*SIGN(T22-T19),0)</f>
         <v/>
       </c>
-      <c r="AE22" s="9">
+      <c r="AE22" s="7">
         <f>IF(AND(ISNUMBER(T22),ISNUMBER(T20)),VLOOKUP(ABS(T22-T20),'IMP Table'!$A$2:$C$26,3)*SIGN(T22-T20),0)</f>
         <v/>
       </c>
-      <c r="AF22" s="9">
+      <c r="AF22" s="7">
         <f>IF(AND(ISNUMBER(T22),ISNUMBER(T21)),VLOOKUP(ABS(T22-T21),'IMP Table'!$A$2:$C$26,3)*SIGN(T22-T21),0)</f>
         <v/>
       </c>
@@ -3581,15 +3591,15 @@
         <f>AVERAGE(AA23:AC23)</f>
         <v/>
       </c>
-      <c r="N23" s="7">
+      <c r="N23" s="5">
         <f>AVERAGE(AD23:AF23)</f>
         <v/>
       </c>
-      <c r="O23" s="6">
+      <c r="O23" s="4">
         <f>IF(COUNT(U23:W23)&gt;0,Q23/COUNT(U23:W23),0.5)</f>
         <v/>
       </c>
-      <c r="P23" s="6">
+      <c r="P23" s="4">
         <f>IF(COUNT(X23:Z23)&gt;0,R23/COUNT(X23:Z23),0.5)</f>
         <v/>
       </c>
@@ -3707,15 +3717,15 @@
         <f>AVERAGE(AA24:AC24)</f>
         <v/>
       </c>
-      <c r="N24" s="7">
+      <c r="N24" s="5">
         <f>AVERAGE(AD24:AF24)</f>
         <v/>
       </c>
-      <c r="O24" s="6">
+      <c r="O24" s="4">
         <f>IF(COUNT(U24:W24)&gt;0,Q24/COUNT(U24:W24),0.5)</f>
         <v/>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="4">
         <f>IF(COUNT(X24:Z24)&gt;0,R24/COUNT(X24:Z24),0.5)</f>
         <v/>
       </c>
@@ -3833,15 +3843,15 @@
         <f>AVERAGE(AA25:AC25)</f>
         <v/>
       </c>
-      <c r="N25" s="7">
+      <c r="N25" s="5">
         <f>AVERAGE(AD25:AF25)</f>
         <v/>
       </c>
-      <c r="O25" s="6">
+      <c r="O25" s="4">
         <f>IF(COUNT(U25:W25)&gt;0,Q25/COUNT(U25:W25),0.5)</f>
         <v/>
       </c>
-      <c r="P25" s="6">
+      <c r="P25" s="4">
         <f>IF(COUNT(X25:Z25)&gt;0,R25/COUNT(X25:Z25),0.5)</f>
         <v/>
       </c>
@@ -3911,7 +3921,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
+      <c r="A26" s="7" t="n"/>
       <c r="B26" s="19">
         <f>'By Round'!A27</f>
         <v/>
@@ -3932,27 +3942,27 @@
         <f>IF(ISBLANK('By Round'!F38),"",'By Round'!F38)</f>
         <v/>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="7">
         <f>IF(ISBLANK('By Round'!G38),"",'By Round'!G38)</f>
         <v/>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="7">
         <f>IF(ISBLANK('By Round'!H38),"",'By Round'!H38)</f>
         <v/>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="7">
         <f>IF(ISBLANK('By Round'!I38),"",'By Round'!I38)</f>
         <v/>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="7">
         <f>IF(ISBLANK('By Round'!J38),"",'By Round'!J38)</f>
         <v/>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="7">
         <f>IF(ISBLANK('By Round'!K38),"",'By Round'!K38)</f>
         <v/>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="7">
         <f>IF(ISBLANK('By Round'!L38),"",'By Round'!L38)</f>
         <v/>
       </c>
@@ -3960,79 +3970,79 @@
         <f>AVERAGE(AA26:AC26)</f>
         <v/>
       </c>
-      <c r="N26" s="21">
+      <c r="N26" s="9">
         <f>AVERAGE(AD26:AF26)</f>
         <v/>
       </c>
-      <c r="O26" s="22">
+      <c r="O26" s="8">
         <f>IF(COUNT(U26:W26)&gt;0,Q26/COUNT(U26:W26),0.5)</f>
         <v/>
       </c>
-      <c r="P26" s="22">
+      <c r="P26" s="8">
         <f>IF(COUNT(X26:Z26)&gt;0,R26/COUNT(X26:Z26),0.5)</f>
         <v/>
       </c>
-      <c r="Q26" s="23">
+      <c r="Q26" s="21">
         <f>SUM(U26:W26)</f>
         <v/>
       </c>
-      <c r="R26" s="23">
+      <c r="R26" s="21">
         <f>SUM(X26:Z26)</f>
         <v/>
       </c>
-      <c r="S26" s="24">
+      <c r="S26" s="22">
         <f>IF(ISNUMBER(K26),K26,IF(ISNUMBER(L26),-L26,""))</f>
         <v/>
       </c>
-      <c r="T26" s="9">
+      <c r="T26" s="7">
         <f>IF(ISNUMBER(L26),L26,IF(ISNUMBER(K26),-K26,""))</f>
         <v/>
       </c>
-      <c r="U26" s="24">
+      <c r="U26" s="22">
         <f>IF(ISNUMBER(S26),IF(ISNUMBER(S23),IF(S26&gt;S23,1.0,IF(S26=S23,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V26" s="9">
+      <c r="V26" s="7">
         <f>IF(ISNUMBER(S26),IF(ISNUMBER(S24),IF(S26&gt;S24,1.0,IF(S26=S24,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W26" s="9">
+      <c r="W26" s="7">
         <f>IF(ISNUMBER(S26),IF(ISNUMBER(S25),IF(S26&gt;S25,1.0,IF(S26=S25,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X26" s="9">
+      <c r="X26" s="7">
         <f>IF(ISNUMBER(T26),IF(ISNUMBER(T23),IF(T26&gt;T23,1.0,IF(T26=T23,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y26" s="9">
+      <c r="Y26" s="7">
         <f>IF(ISNUMBER(T26),IF(ISNUMBER(T24),IF(T26&gt;T24,1.0,IF(T26=T24,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z26" s="9">
+      <c r="Z26" s="7">
         <f>IF(ISNUMBER(T26),IF(ISNUMBER(T25),IF(T26&gt;T25,1.0,IF(T26=T25,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA26" s="24">
+      <c r="AA26" s="22">
         <f>IF(AND(ISNUMBER(S26),ISNUMBER(S23)),VLOOKUP(ABS(S26-S23),'IMP Table'!$A$2:$C$26,3)*SIGN(S26-S23),0)</f>
         <v/>
       </c>
-      <c r="AB26" s="9">
+      <c r="AB26" s="7">
         <f>IF(AND(ISNUMBER(S26),ISNUMBER(S24)),VLOOKUP(ABS(S26-S24),'IMP Table'!$A$2:$C$26,3)*SIGN(S26-S24),0)</f>
         <v/>
       </c>
-      <c r="AC26" s="9">
+      <c r="AC26" s="7">
         <f>IF(AND(ISNUMBER(S26),ISNUMBER(S25)),VLOOKUP(ABS(S26-S25),'IMP Table'!$A$2:$C$26,3)*SIGN(S26-S25),0)</f>
         <v/>
       </c>
-      <c r="AD26" s="9">
+      <c r="AD26" s="7">
         <f>IF(AND(ISNUMBER(T26),ISNUMBER(T23)),VLOOKUP(ABS(T26-T23),'IMP Table'!$A$2:$C$26,3)*SIGN(T26-T23),0)</f>
         <v/>
       </c>
-      <c r="AE26" s="9">
+      <c r="AE26" s="7">
         <f>IF(AND(ISNUMBER(T26),ISNUMBER(T24)),VLOOKUP(ABS(T26-T24),'IMP Table'!$A$2:$C$26,3)*SIGN(T26-T24),0)</f>
         <v/>
       </c>
-      <c r="AF26" s="9">
+      <c r="AF26" s="7">
         <f>IF(AND(ISNUMBER(T26),ISNUMBER(T25)),VLOOKUP(ABS(T26-T25),'IMP Table'!$A$2:$C$26,3)*SIGN(T26-T25),0)</f>
         <v/>
       </c>
@@ -4089,15 +4099,15 @@
         <f>AVERAGE(AA27:AC27)</f>
         <v/>
       </c>
-      <c r="N27" s="7">
+      <c r="N27" s="5">
         <f>AVERAGE(AD27:AF27)</f>
         <v/>
       </c>
-      <c r="O27" s="6">
+      <c r="O27" s="4">
         <f>IF(COUNT(U27:W27)&gt;0,Q27/COUNT(U27:W27),0.5)</f>
         <v/>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="4">
         <f>IF(COUNT(X27:Z27)&gt;0,R27/COUNT(X27:Z27),0.5)</f>
         <v/>
       </c>
@@ -4215,15 +4225,15 @@
         <f>AVERAGE(AA28:AC28)</f>
         <v/>
       </c>
-      <c r="N28" s="7">
+      <c r="N28" s="5">
         <f>AVERAGE(AD28:AF28)</f>
         <v/>
       </c>
-      <c r="O28" s="6">
+      <c r="O28" s="4">
         <f>IF(COUNT(U28:W28)&gt;0,Q28/COUNT(U28:W28),0.5)</f>
         <v/>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="4">
         <f>IF(COUNT(X28:Z28)&gt;0,R28/COUNT(X28:Z28),0.5)</f>
         <v/>
       </c>
@@ -4341,15 +4351,15 @@
         <f>AVERAGE(AA29:AC29)</f>
         <v/>
       </c>
-      <c r="N29" s="7">
+      <c r="N29" s="5">
         <f>AVERAGE(AD29:AF29)</f>
         <v/>
       </c>
-      <c r="O29" s="6">
+      <c r="O29" s="4">
         <f>IF(COUNT(U29:W29)&gt;0,Q29/COUNT(U29:W29),0.5)</f>
         <v/>
       </c>
-      <c r="P29" s="6">
+      <c r="P29" s="4">
         <f>IF(COUNT(X29:Z29)&gt;0,R29/COUNT(X29:Z29),0.5)</f>
         <v/>
       </c>
@@ -4419,7 +4429,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
+      <c r="A30" s="7" t="n"/>
       <c r="B30" s="19">
         <f>'By Round'!A39</f>
         <v/>
@@ -4440,27 +4450,27 @@
         <f>IF(ISBLANK('By Round'!F48),"",'By Round'!F48)</f>
         <v/>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="7">
         <f>IF(ISBLANK('By Round'!G48),"",'By Round'!G48)</f>
         <v/>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="7">
         <f>IF(ISBLANK('By Round'!H48),"",'By Round'!H48)</f>
         <v/>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="7">
         <f>IF(ISBLANK('By Round'!I48),"",'By Round'!I48)</f>
         <v/>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="7">
         <f>IF(ISBLANK('By Round'!J48),"",'By Round'!J48)</f>
         <v/>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="7">
         <f>IF(ISBLANK('By Round'!K48),"",'By Round'!K48)</f>
         <v/>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="7">
         <f>IF(ISBLANK('By Round'!L48),"",'By Round'!L48)</f>
         <v/>
       </c>
@@ -4468,79 +4478,79 @@
         <f>AVERAGE(AA30:AC30)</f>
         <v/>
       </c>
-      <c r="N30" s="21">
+      <c r="N30" s="9">
         <f>AVERAGE(AD30:AF30)</f>
         <v/>
       </c>
-      <c r="O30" s="22">
+      <c r="O30" s="8">
         <f>IF(COUNT(U30:W30)&gt;0,Q30/COUNT(U30:W30),0.5)</f>
         <v/>
       </c>
-      <c r="P30" s="22">
+      <c r="P30" s="8">
         <f>IF(COUNT(X30:Z30)&gt;0,R30/COUNT(X30:Z30),0.5)</f>
         <v/>
       </c>
-      <c r="Q30" s="23">
+      <c r="Q30" s="21">
         <f>SUM(U30:W30)</f>
         <v/>
       </c>
-      <c r="R30" s="23">
+      <c r="R30" s="21">
         <f>SUM(X30:Z30)</f>
         <v/>
       </c>
-      <c r="S30" s="24">
+      <c r="S30" s="22">
         <f>IF(ISNUMBER(K30),K30,IF(ISNUMBER(L30),-L30,""))</f>
         <v/>
       </c>
-      <c r="T30" s="9">
+      <c r="T30" s="7">
         <f>IF(ISNUMBER(L30),L30,IF(ISNUMBER(K30),-K30,""))</f>
         <v/>
       </c>
-      <c r="U30" s="24">
+      <c r="U30" s="22">
         <f>IF(ISNUMBER(S30),IF(ISNUMBER(S27),IF(S30&gt;S27,1.0,IF(S30=S27,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V30" s="9">
+      <c r="V30" s="7">
         <f>IF(ISNUMBER(S30),IF(ISNUMBER(S28),IF(S30&gt;S28,1.0,IF(S30=S28,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W30" s="9">
+      <c r="W30" s="7">
         <f>IF(ISNUMBER(S30),IF(ISNUMBER(S29),IF(S30&gt;S29,1.0,IF(S30=S29,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X30" s="9">
+      <c r="X30" s="7">
         <f>IF(ISNUMBER(T30),IF(ISNUMBER(T27),IF(T30&gt;T27,1.0,IF(T30=T27,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y30" s="9">
+      <c r="Y30" s="7">
         <f>IF(ISNUMBER(T30),IF(ISNUMBER(T28),IF(T30&gt;T28,1.0,IF(T30=T28,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z30" s="9">
+      <c r="Z30" s="7">
         <f>IF(ISNUMBER(T30),IF(ISNUMBER(T29),IF(T30&gt;T29,1.0,IF(T30=T29,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA30" s="24">
+      <c r="AA30" s="22">
         <f>IF(AND(ISNUMBER(S30),ISNUMBER(S27)),VLOOKUP(ABS(S30-S27),'IMP Table'!$A$2:$C$26,3)*SIGN(S30-S27),0)</f>
         <v/>
       </c>
-      <c r="AB30" s="9">
+      <c r="AB30" s="7">
         <f>IF(AND(ISNUMBER(S30),ISNUMBER(S28)),VLOOKUP(ABS(S30-S28),'IMP Table'!$A$2:$C$26,3)*SIGN(S30-S28),0)</f>
         <v/>
       </c>
-      <c r="AC30" s="9">
+      <c r="AC30" s="7">
         <f>IF(AND(ISNUMBER(S30),ISNUMBER(S29)),VLOOKUP(ABS(S30-S29),'IMP Table'!$A$2:$C$26,3)*SIGN(S30-S29),0)</f>
         <v/>
       </c>
-      <c r="AD30" s="9">
+      <c r="AD30" s="7">
         <f>IF(AND(ISNUMBER(T30),ISNUMBER(T27)),VLOOKUP(ABS(T30-T27),'IMP Table'!$A$2:$C$26,3)*SIGN(T30-T27),0)</f>
         <v/>
       </c>
-      <c r="AE30" s="9">
+      <c r="AE30" s="7">
         <f>IF(AND(ISNUMBER(T30),ISNUMBER(T28)),VLOOKUP(ABS(T30-T28),'IMP Table'!$A$2:$C$26,3)*SIGN(T30-T28),0)</f>
         <v/>
       </c>
-      <c r="AF30" s="9">
+      <c r="AF30" s="7">
         <f>IF(AND(ISNUMBER(T30),ISNUMBER(T29)),VLOOKUP(ABS(T30-T29),'IMP Table'!$A$2:$C$26,3)*SIGN(T30-T29),0)</f>
         <v/>
       </c>
@@ -4597,15 +4607,15 @@
         <f>AVERAGE(AA31:AC31)</f>
         <v/>
       </c>
-      <c r="N31" s="7">
+      <c r="N31" s="5">
         <f>AVERAGE(AD31:AF31)</f>
         <v/>
       </c>
-      <c r="O31" s="6">
+      <c r="O31" s="4">
         <f>IF(COUNT(U31:W31)&gt;0,Q31/COUNT(U31:W31),0.5)</f>
         <v/>
       </c>
-      <c r="P31" s="6">
+      <c r="P31" s="4">
         <f>IF(COUNT(X31:Z31)&gt;0,R31/COUNT(X31:Z31),0.5)</f>
         <v/>
       </c>
@@ -4723,15 +4733,15 @@
         <f>AVERAGE(AA32:AC32)</f>
         <v/>
       </c>
-      <c r="N32" s="7">
+      <c r="N32" s="5">
         <f>AVERAGE(AD32:AF32)</f>
         <v/>
       </c>
-      <c r="O32" s="6">
+      <c r="O32" s="4">
         <f>IF(COUNT(U32:W32)&gt;0,Q32/COUNT(U32:W32),0.5)</f>
         <v/>
       </c>
-      <c r="P32" s="6">
+      <c r="P32" s="4">
         <f>IF(COUNT(X32:Z32)&gt;0,R32/COUNT(X32:Z32),0.5)</f>
         <v/>
       </c>
@@ -4849,15 +4859,15 @@
         <f>AVERAGE(AA33:AC33)</f>
         <v/>
       </c>
-      <c r="N33" s="7">
+      <c r="N33" s="5">
         <f>AVERAGE(AD33:AF33)</f>
         <v/>
       </c>
-      <c r="O33" s="6">
+      <c r="O33" s="4">
         <f>IF(COUNT(U33:W33)&gt;0,Q33/COUNT(U33:W33),0.5)</f>
         <v/>
       </c>
-      <c r="P33" s="6">
+      <c r="P33" s="4">
         <f>IF(COUNT(X33:Z33)&gt;0,R33/COUNT(X33:Z33),0.5)</f>
         <v/>
       </c>
@@ -4927,7 +4937,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n"/>
+      <c r="A34" s="7" t="n"/>
       <c r="B34" s="19">
         <f>'By Round'!A39</f>
         <v/>
@@ -4948,27 +4958,27 @@
         <f>IF(ISBLANK('By Round'!F49),"",'By Round'!F49)</f>
         <v/>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="7">
         <f>IF(ISBLANK('By Round'!G49),"",'By Round'!G49)</f>
         <v/>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="7">
         <f>IF(ISBLANK('By Round'!H49),"",'By Round'!H49)</f>
         <v/>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="7">
         <f>IF(ISBLANK('By Round'!I49),"",'By Round'!I49)</f>
         <v/>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="7">
         <f>IF(ISBLANK('By Round'!J49),"",'By Round'!J49)</f>
         <v/>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="7">
         <f>IF(ISBLANK('By Round'!K49),"",'By Round'!K49)</f>
         <v/>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="7">
         <f>IF(ISBLANK('By Round'!L49),"",'By Round'!L49)</f>
         <v/>
       </c>
@@ -4976,79 +4986,79 @@
         <f>AVERAGE(AA34:AC34)</f>
         <v/>
       </c>
-      <c r="N34" s="21">
+      <c r="N34" s="9">
         <f>AVERAGE(AD34:AF34)</f>
         <v/>
       </c>
-      <c r="O34" s="22">
+      <c r="O34" s="8">
         <f>IF(COUNT(U34:W34)&gt;0,Q34/COUNT(U34:W34),0.5)</f>
         <v/>
       </c>
-      <c r="P34" s="22">
+      <c r="P34" s="8">
         <f>IF(COUNT(X34:Z34)&gt;0,R34/COUNT(X34:Z34),0.5)</f>
         <v/>
       </c>
-      <c r="Q34" s="23">
+      <c r="Q34" s="21">
         <f>SUM(U34:W34)</f>
         <v/>
       </c>
-      <c r="R34" s="23">
+      <c r="R34" s="21">
         <f>SUM(X34:Z34)</f>
         <v/>
       </c>
-      <c r="S34" s="24">
+      <c r="S34" s="22">
         <f>IF(ISNUMBER(K34),K34,IF(ISNUMBER(L34),-L34,""))</f>
         <v/>
       </c>
-      <c r="T34" s="9">
+      <c r="T34" s="7">
         <f>IF(ISNUMBER(L34),L34,IF(ISNUMBER(K34),-K34,""))</f>
         <v/>
       </c>
-      <c r="U34" s="24">
+      <c r="U34" s="22">
         <f>IF(ISNUMBER(S34),IF(ISNUMBER(S31),IF(S34&gt;S31,1.0,IF(S34=S31,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V34" s="9">
+      <c r="V34" s="7">
         <f>IF(ISNUMBER(S34),IF(ISNUMBER(S32),IF(S34&gt;S32,1.0,IF(S34=S32,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W34" s="9">
+      <c r="W34" s="7">
         <f>IF(ISNUMBER(S34),IF(ISNUMBER(S33),IF(S34&gt;S33,1.0,IF(S34=S33,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X34" s="9">
+      <c r="X34" s="7">
         <f>IF(ISNUMBER(T34),IF(ISNUMBER(T31),IF(T34&gt;T31,1.0,IF(T34=T31,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y34" s="9">
+      <c r="Y34" s="7">
         <f>IF(ISNUMBER(T34),IF(ISNUMBER(T32),IF(T34&gt;T32,1.0,IF(T34=T32,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z34" s="9">
+      <c r="Z34" s="7">
         <f>IF(ISNUMBER(T34),IF(ISNUMBER(T33),IF(T34&gt;T33,1.0,IF(T34=T33,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA34" s="24">
+      <c r="AA34" s="22">
         <f>IF(AND(ISNUMBER(S34),ISNUMBER(S31)),VLOOKUP(ABS(S34-S31),'IMP Table'!$A$2:$C$26,3)*SIGN(S34-S31),0)</f>
         <v/>
       </c>
-      <c r="AB34" s="9">
+      <c r="AB34" s="7">
         <f>IF(AND(ISNUMBER(S34),ISNUMBER(S32)),VLOOKUP(ABS(S34-S32),'IMP Table'!$A$2:$C$26,3)*SIGN(S34-S32),0)</f>
         <v/>
       </c>
-      <c r="AC34" s="9">
+      <c r="AC34" s="7">
         <f>IF(AND(ISNUMBER(S34),ISNUMBER(S33)),VLOOKUP(ABS(S34-S33),'IMP Table'!$A$2:$C$26,3)*SIGN(S34-S33),0)</f>
         <v/>
       </c>
-      <c r="AD34" s="9">
+      <c r="AD34" s="7">
         <f>IF(AND(ISNUMBER(T34),ISNUMBER(T31)),VLOOKUP(ABS(T34-T31),'IMP Table'!$A$2:$C$26,3)*SIGN(T34-T31),0)</f>
         <v/>
       </c>
-      <c r="AE34" s="9">
+      <c r="AE34" s="7">
         <f>IF(AND(ISNUMBER(T34),ISNUMBER(T32)),VLOOKUP(ABS(T34-T32),'IMP Table'!$A$2:$C$26,3)*SIGN(T34-T32),0)</f>
         <v/>
       </c>
-      <c r="AF34" s="9">
+      <c r="AF34" s="7">
         <f>IF(AND(ISNUMBER(T34),ISNUMBER(T33)),VLOOKUP(ABS(T34-T33),'IMP Table'!$A$2:$C$26,3)*SIGN(T34-T33),0)</f>
         <v/>
       </c>
@@ -5105,15 +5115,15 @@
         <f>AVERAGE(AA35:AC35)</f>
         <v/>
       </c>
-      <c r="N35" s="7">
+      <c r="N35" s="5">
         <f>AVERAGE(AD35:AF35)</f>
         <v/>
       </c>
-      <c r="O35" s="6">
+      <c r="O35" s="4">
         <f>IF(COUNT(U35:W35)&gt;0,Q35/COUNT(U35:W35),0.5)</f>
         <v/>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="4">
         <f>IF(COUNT(X35:Z35)&gt;0,R35/COUNT(X35:Z35),0.5)</f>
         <v/>
       </c>
@@ -5231,15 +5241,15 @@
         <f>AVERAGE(AA36:AC36)</f>
         <v/>
       </c>
-      <c r="N36" s="7">
+      <c r="N36" s="5">
         <f>AVERAGE(AD36:AF36)</f>
         <v/>
       </c>
-      <c r="O36" s="6">
+      <c r="O36" s="4">
         <f>IF(COUNT(U36:W36)&gt;0,Q36/COUNT(U36:W36),0.5)</f>
         <v/>
       </c>
-      <c r="P36" s="6">
+      <c r="P36" s="4">
         <f>IF(COUNT(X36:Z36)&gt;0,R36/COUNT(X36:Z36),0.5)</f>
         <v/>
       </c>
@@ -5357,15 +5367,15 @@
         <f>AVERAGE(AA37:AC37)</f>
         <v/>
       </c>
-      <c r="N37" s="7">
+      <c r="N37" s="5">
         <f>AVERAGE(AD37:AF37)</f>
         <v/>
       </c>
-      <c r="O37" s="6">
+      <c r="O37" s="4">
         <f>IF(COUNT(U37:W37)&gt;0,Q37/COUNT(U37:W37),0.5)</f>
         <v/>
       </c>
-      <c r="P37" s="6">
+      <c r="P37" s="4">
         <f>IF(COUNT(X37:Z37)&gt;0,R37/COUNT(X37:Z37),0.5)</f>
         <v/>
       </c>
@@ -5435,7 +5445,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n"/>
+      <c r="A38" s="7" t="n"/>
       <c r="B38" s="19">
         <f>'By Round'!A39</f>
         <v/>
@@ -5456,27 +5466,27 @@
         <f>IF(ISBLANK('By Round'!F50),"",'By Round'!F50)</f>
         <v/>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="7">
         <f>IF(ISBLANK('By Round'!G50),"",'By Round'!G50)</f>
         <v/>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="7">
         <f>IF(ISBLANK('By Round'!H50),"",'By Round'!H50)</f>
         <v/>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="7">
         <f>IF(ISBLANK('By Round'!I50),"",'By Round'!I50)</f>
         <v/>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="7">
         <f>IF(ISBLANK('By Round'!J50),"",'By Round'!J50)</f>
         <v/>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="7">
         <f>IF(ISBLANK('By Round'!K50),"",'By Round'!K50)</f>
         <v/>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="7">
         <f>IF(ISBLANK('By Round'!L50),"",'By Round'!L50)</f>
         <v/>
       </c>
@@ -5484,79 +5494,79 @@
         <f>AVERAGE(AA38:AC38)</f>
         <v/>
       </c>
-      <c r="N38" s="21">
+      <c r="N38" s="9">
         <f>AVERAGE(AD38:AF38)</f>
         <v/>
       </c>
-      <c r="O38" s="22">
+      <c r="O38" s="8">
         <f>IF(COUNT(U38:W38)&gt;0,Q38/COUNT(U38:W38),0.5)</f>
         <v/>
       </c>
-      <c r="P38" s="22">
+      <c r="P38" s="8">
         <f>IF(COUNT(X38:Z38)&gt;0,R38/COUNT(X38:Z38),0.5)</f>
         <v/>
       </c>
-      <c r="Q38" s="23">
+      <c r="Q38" s="21">
         <f>SUM(U38:W38)</f>
         <v/>
       </c>
-      <c r="R38" s="23">
+      <c r="R38" s="21">
         <f>SUM(X38:Z38)</f>
         <v/>
       </c>
-      <c r="S38" s="24">
+      <c r="S38" s="22">
         <f>IF(ISNUMBER(K38),K38,IF(ISNUMBER(L38),-L38,""))</f>
         <v/>
       </c>
-      <c r="T38" s="9">
+      <c r="T38" s="7">
         <f>IF(ISNUMBER(L38),L38,IF(ISNUMBER(K38),-K38,""))</f>
         <v/>
       </c>
-      <c r="U38" s="24">
+      <c r="U38" s="22">
         <f>IF(ISNUMBER(S38),IF(ISNUMBER(S35),IF(S38&gt;S35,1.0,IF(S38=S35,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V38" s="9">
+      <c r="V38" s="7">
         <f>IF(ISNUMBER(S38),IF(ISNUMBER(S36),IF(S38&gt;S36,1.0,IF(S38=S36,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W38" s="9">
+      <c r="W38" s="7">
         <f>IF(ISNUMBER(S38),IF(ISNUMBER(S37),IF(S38&gt;S37,1.0,IF(S38=S37,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X38" s="9">
+      <c r="X38" s="7">
         <f>IF(ISNUMBER(T38),IF(ISNUMBER(T35),IF(T38&gt;T35,1.0,IF(T38=T35,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y38" s="9">
+      <c r="Y38" s="7">
         <f>IF(ISNUMBER(T38),IF(ISNUMBER(T36),IF(T38&gt;T36,1.0,IF(T38=T36,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z38" s="9">
+      <c r="Z38" s="7">
         <f>IF(ISNUMBER(T38),IF(ISNUMBER(T37),IF(T38&gt;T37,1.0,IF(T38=T37,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA38" s="24">
+      <c r="AA38" s="22">
         <f>IF(AND(ISNUMBER(S38),ISNUMBER(S35)),VLOOKUP(ABS(S38-S35),'IMP Table'!$A$2:$C$26,3)*SIGN(S38-S35),0)</f>
         <v/>
       </c>
-      <c r="AB38" s="9">
+      <c r="AB38" s="7">
         <f>IF(AND(ISNUMBER(S38),ISNUMBER(S36)),VLOOKUP(ABS(S38-S36),'IMP Table'!$A$2:$C$26,3)*SIGN(S38-S36),0)</f>
         <v/>
       </c>
-      <c r="AC38" s="9">
+      <c r="AC38" s="7">
         <f>IF(AND(ISNUMBER(S38),ISNUMBER(S37)),VLOOKUP(ABS(S38-S37),'IMP Table'!$A$2:$C$26,3)*SIGN(S38-S37),0)</f>
         <v/>
       </c>
-      <c r="AD38" s="9">
+      <c r="AD38" s="7">
         <f>IF(AND(ISNUMBER(T38),ISNUMBER(T35)),VLOOKUP(ABS(T38-T35),'IMP Table'!$A$2:$C$26,3)*SIGN(T38-T35),0)</f>
         <v/>
       </c>
-      <c r="AE38" s="9">
+      <c r="AE38" s="7">
         <f>IF(AND(ISNUMBER(T38),ISNUMBER(T36)),VLOOKUP(ABS(T38-T36),'IMP Table'!$A$2:$C$26,3)*SIGN(T38-T36),0)</f>
         <v/>
       </c>
-      <c r="AF38" s="9">
+      <c r="AF38" s="7">
         <f>IF(AND(ISNUMBER(T38),ISNUMBER(T37)),VLOOKUP(ABS(T38-T37),'IMP Table'!$A$2:$C$26,3)*SIGN(T38-T37),0)</f>
         <v/>
       </c>
@@ -5613,15 +5623,15 @@
         <f>AVERAGE(AA39:AC39)</f>
         <v/>
       </c>
-      <c r="N39" s="7">
+      <c r="N39" s="5">
         <f>AVERAGE(AD39:AF39)</f>
         <v/>
       </c>
-      <c r="O39" s="6">
+      <c r="O39" s="4">
         <f>IF(COUNT(U39:W39)&gt;0,Q39/COUNT(U39:W39),0.5)</f>
         <v/>
       </c>
-      <c r="P39" s="6">
+      <c r="P39" s="4">
         <f>IF(COUNT(X39:Z39)&gt;0,R39/COUNT(X39:Z39),0.5)</f>
         <v/>
       </c>
@@ -5739,15 +5749,15 @@
         <f>AVERAGE(AA40:AC40)</f>
         <v/>
       </c>
-      <c r="N40" s="7">
+      <c r="N40" s="5">
         <f>AVERAGE(AD40:AF40)</f>
         <v/>
       </c>
-      <c r="O40" s="6">
+      <c r="O40" s="4">
         <f>IF(COUNT(U40:W40)&gt;0,Q40/COUNT(U40:W40),0.5)</f>
         <v/>
       </c>
-      <c r="P40" s="6">
+      <c r="P40" s="4">
         <f>IF(COUNT(X40:Z40)&gt;0,R40/COUNT(X40:Z40),0.5)</f>
         <v/>
       </c>
@@ -5865,15 +5875,15 @@
         <f>AVERAGE(AA41:AC41)</f>
         <v/>
       </c>
-      <c r="N41" s="7">
+      <c r="N41" s="5">
         <f>AVERAGE(AD41:AF41)</f>
         <v/>
       </c>
-      <c r="O41" s="6">
+      <c r="O41" s="4">
         <f>IF(COUNT(U41:W41)&gt;0,Q41/COUNT(U41:W41),0.5)</f>
         <v/>
       </c>
-      <c r="P41" s="6">
+      <c r="P41" s="4">
         <f>IF(COUNT(X41:Z41)&gt;0,R41/COUNT(X41:Z41),0.5)</f>
         <v/>
       </c>
@@ -5943,7 +5953,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n"/>
+      <c r="A42" s="7" t="n"/>
       <c r="B42" s="19">
         <f>'By Round'!A3</f>
         <v/>
@@ -5964,27 +5974,27 @@
         <f>IF(ISBLANK('By Round'!F12),"",'By Round'!F12)</f>
         <v/>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="7">
         <f>IF(ISBLANK('By Round'!G12),"",'By Round'!G12)</f>
         <v/>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="7">
         <f>IF(ISBLANK('By Round'!H12),"",'By Round'!H12)</f>
         <v/>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="7">
         <f>IF(ISBLANK('By Round'!I12),"",'By Round'!I12)</f>
         <v/>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="7">
         <f>IF(ISBLANK('By Round'!J12),"",'By Round'!J12)</f>
         <v/>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="7">
         <f>IF(ISBLANK('By Round'!K12),"",'By Round'!K12)</f>
         <v/>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="7">
         <f>IF(ISBLANK('By Round'!L12),"",'By Round'!L12)</f>
         <v/>
       </c>
@@ -5992,79 +6002,79 @@
         <f>AVERAGE(AA42:AC42)</f>
         <v/>
       </c>
-      <c r="N42" s="21">
+      <c r="N42" s="9">
         <f>AVERAGE(AD42:AF42)</f>
         <v/>
       </c>
-      <c r="O42" s="22">
+      <c r="O42" s="8">
         <f>IF(COUNT(U42:W42)&gt;0,Q42/COUNT(U42:W42),0.5)</f>
         <v/>
       </c>
-      <c r="P42" s="22">
+      <c r="P42" s="8">
         <f>IF(COUNT(X42:Z42)&gt;0,R42/COUNT(X42:Z42),0.5)</f>
         <v/>
       </c>
-      <c r="Q42" s="23">
+      <c r="Q42" s="21">
         <f>SUM(U42:W42)</f>
         <v/>
       </c>
-      <c r="R42" s="23">
+      <c r="R42" s="21">
         <f>SUM(X42:Z42)</f>
         <v/>
       </c>
-      <c r="S42" s="24">
+      <c r="S42" s="22">
         <f>IF(ISNUMBER(K42),K42,IF(ISNUMBER(L42),-L42,""))</f>
         <v/>
       </c>
-      <c r="T42" s="9">
+      <c r="T42" s="7">
         <f>IF(ISNUMBER(L42),L42,IF(ISNUMBER(K42),-K42,""))</f>
         <v/>
       </c>
-      <c r="U42" s="24">
+      <c r="U42" s="22">
         <f>IF(ISNUMBER(S42),IF(ISNUMBER(S39),IF(S42&gt;S39,1.0,IF(S42=S39,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V42" s="9">
+      <c r="V42" s="7">
         <f>IF(ISNUMBER(S42),IF(ISNUMBER(S40),IF(S42&gt;S40,1.0,IF(S42=S40,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W42" s="9">
+      <c r="W42" s="7">
         <f>IF(ISNUMBER(S42),IF(ISNUMBER(S41),IF(S42&gt;S41,1.0,IF(S42=S41,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X42" s="9">
+      <c r="X42" s="7">
         <f>IF(ISNUMBER(T42),IF(ISNUMBER(T39),IF(T42&gt;T39,1.0,IF(T42=T39,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y42" s="9">
+      <c r="Y42" s="7">
         <f>IF(ISNUMBER(T42),IF(ISNUMBER(T40),IF(T42&gt;T40,1.0,IF(T42=T40,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z42" s="9">
+      <c r="Z42" s="7">
         <f>IF(ISNUMBER(T42),IF(ISNUMBER(T41),IF(T42&gt;T41,1.0,IF(T42=T41,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA42" s="24">
+      <c r="AA42" s="22">
         <f>IF(AND(ISNUMBER(S42),ISNUMBER(S39)),VLOOKUP(ABS(S42-S39),'IMP Table'!$A$2:$C$26,3)*SIGN(S42-S39),0)</f>
         <v/>
       </c>
-      <c r="AB42" s="9">
+      <c r="AB42" s="7">
         <f>IF(AND(ISNUMBER(S42),ISNUMBER(S40)),VLOOKUP(ABS(S42-S40),'IMP Table'!$A$2:$C$26,3)*SIGN(S42-S40),0)</f>
         <v/>
       </c>
-      <c r="AC42" s="9">
+      <c r="AC42" s="7">
         <f>IF(AND(ISNUMBER(S42),ISNUMBER(S41)),VLOOKUP(ABS(S42-S41),'IMP Table'!$A$2:$C$26,3)*SIGN(S42-S41),0)</f>
         <v/>
       </c>
-      <c r="AD42" s="9">
+      <c r="AD42" s="7">
         <f>IF(AND(ISNUMBER(T42),ISNUMBER(T39)),VLOOKUP(ABS(T42-T39),'IMP Table'!$A$2:$C$26,3)*SIGN(T42-T39),0)</f>
         <v/>
       </c>
-      <c r="AE42" s="9">
+      <c r="AE42" s="7">
         <f>IF(AND(ISNUMBER(T42),ISNUMBER(T40)),VLOOKUP(ABS(T42-T40),'IMP Table'!$A$2:$C$26,3)*SIGN(T42-T40),0)</f>
         <v/>
       </c>
-      <c r="AF42" s="9">
+      <c r="AF42" s="7">
         <f>IF(AND(ISNUMBER(T42),ISNUMBER(T41)),VLOOKUP(ABS(T42-T41),'IMP Table'!$A$2:$C$26,3)*SIGN(T42-T41),0)</f>
         <v/>
       </c>
@@ -6121,15 +6131,15 @@
         <f>AVERAGE(AA43:AC43)</f>
         <v/>
       </c>
-      <c r="N43" s="7">
+      <c r="N43" s="5">
         <f>AVERAGE(AD43:AF43)</f>
         <v/>
       </c>
-      <c r="O43" s="6">
+      <c r="O43" s="4">
         <f>IF(COUNT(U43:W43)&gt;0,Q43/COUNT(U43:W43),0.5)</f>
         <v/>
       </c>
-      <c r="P43" s="6">
+      <c r="P43" s="4">
         <f>IF(COUNT(X43:Z43)&gt;0,R43/COUNT(X43:Z43),0.5)</f>
         <v/>
       </c>
@@ -6247,15 +6257,15 @@
         <f>AVERAGE(AA44:AC44)</f>
         <v/>
       </c>
-      <c r="N44" s="7">
+      <c r="N44" s="5">
         <f>AVERAGE(AD44:AF44)</f>
         <v/>
       </c>
-      <c r="O44" s="6">
+      <c r="O44" s="4">
         <f>IF(COUNT(U44:W44)&gt;0,Q44/COUNT(U44:W44),0.5)</f>
         <v/>
       </c>
-      <c r="P44" s="6">
+      <c r="P44" s="4">
         <f>IF(COUNT(X44:Z44)&gt;0,R44/COUNT(X44:Z44),0.5)</f>
         <v/>
       </c>
@@ -6373,15 +6383,15 @@
         <f>AVERAGE(AA45:AC45)</f>
         <v/>
       </c>
-      <c r="N45" s="7">
+      <c r="N45" s="5">
         <f>AVERAGE(AD45:AF45)</f>
         <v/>
       </c>
-      <c r="O45" s="6">
+      <c r="O45" s="4">
         <f>IF(COUNT(U45:W45)&gt;0,Q45/COUNT(U45:W45),0.5)</f>
         <v/>
       </c>
-      <c r="P45" s="6">
+      <c r="P45" s="4">
         <f>IF(COUNT(X45:Z45)&gt;0,R45/COUNT(X45:Z45),0.5)</f>
         <v/>
       </c>
@@ -6451,7 +6461,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n"/>
+      <c r="A46" s="7" t="n"/>
       <c r="B46" s="19">
         <f>'By Round'!A3</f>
         <v/>
@@ -6472,27 +6482,27 @@
         <f>IF(ISBLANK('By Round'!F13),"",'By Round'!F13)</f>
         <v/>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="7">
         <f>IF(ISBLANK('By Round'!G13),"",'By Round'!G13)</f>
         <v/>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="7">
         <f>IF(ISBLANK('By Round'!H13),"",'By Round'!H13)</f>
         <v/>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="7">
         <f>IF(ISBLANK('By Round'!I13),"",'By Round'!I13)</f>
         <v/>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="7">
         <f>IF(ISBLANK('By Round'!J13),"",'By Round'!J13)</f>
         <v/>
       </c>
-      <c r="K46" s="9">
+      <c r="K46" s="7">
         <f>IF(ISBLANK('By Round'!K13),"",'By Round'!K13)</f>
         <v/>
       </c>
-      <c r="L46" s="9">
+      <c r="L46" s="7">
         <f>IF(ISBLANK('By Round'!L13),"",'By Round'!L13)</f>
         <v/>
       </c>
@@ -6500,79 +6510,79 @@
         <f>AVERAGE(AA46:AC46)</f>
         <v/>
       </c>
-      <c r="N46" s="21">
+      <c r="N46" s="9">
         <f>AVERAGE(AD46:AF46)</f>
         <v/>
       </c>
-      <c r="O46" s="22">
+      <c r="O46" s="8">
         <f>IF(COUNT(U46:W46)&gt;0,Q46/COUNT(U46:W46),0.5)</f>
         <v/>
       </c>
-      <c r="P46" s="22">
+      <c r="P46" s="8">
         <f>IF(COUNT(X46:Z46)&gt;0,R46/COUNT(X46:Z46),0.5)</f>
         <v/>
       </c>
-      <c r="Q46" s="23">
+      <c r="Q46" s="21">
         <f>SUM(U46:W46)</f>
         <v/>
       </c>
-      <c r="R46" s="23">
+      <c r="R46" s="21">
         <f>SUM(X46:Z46)</f>
         <v/>
       </c>
-      <c r="S46" s="24">
+      <c r="S46" s="22">
         <f>IF(ISNUMBER(K46),K46,IF(ISNUMBER(L46),-L46,""))</f>
         <v/>
       </c>
-      <c r="T46" s="9">
+      <c r="T46" s="7">
         <f>IF(ISNUMBER(L46),L46,IF(ISNUMBER(K46),-K46,""))</f>
         <v/>
       </c>
-      <c r="U46" s="24">
+      <c r="U46" s="22">
         <f>IF(ISNUMBER(S46),IF(ISNUMBER(S43),IF(S46&gt;S43,1.0,IF(S46=S43,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V46" s="9">
+      <c r="V46" s="7">
         <f>IF(ISNUMBER(S46),IF(ISNUMBER(S44),IF(S46&gt;S44,1.0,IF(S46=S44,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W46" s="9">
+      <c r="W46" s="7">
         <f>IF(ISNUMBER(S46),IF(ISNUMBER(S45),IF(S46&gt;S45,1.0,IF(S46=S45,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X46" s="9">
+      <c r="X46" s="7">
         <f>IF(ISNUMBER(T46),IF(ISNUMBER(T43),IF(T46&gt;T43,1.0,IF(T46=T43,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y46" s="9">
+      <c r="Y46" s="7">
         <f>IF(ISNUMBER(T46),IF(ISNUMBER(T44),IF(T46&gt;T44,1.0,IF(T46=T44,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z46" s="9">
+      <c r="Z46" s="7">
         <f>IF(ISNUMBER(T46),IF(ISNUMBER(T45),IF(T46&gt;T45,1.0,IF(T46=T45,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA46" s="24">
+      <c r="AA46" s="22">
         <f>IF(AND(ISNUMBER(S46),ISNUMBER(S43)),VLOOKUP(ABS(S46-S43),'IMP Table'!$A$2:$C$26,3)*SIGN(S46-S43),0)</f>
         <v/>
       </c>
-      <c r="AB46" s="9">
+      <c r="AB46" s="7">
         <f>IF(AND(ISNUMBER(S46),ISNUMBER(S44)),VLOOKUP(ABS(S46-S44),'IMP Table'!$A$2:$C$26,3)*SIGN(S46-S44),0)</f>
         <v/>
       </c>
-      <c r="AC46" s="9">
+      <c r="AC46" s="7">
         <f>IF(AND(ISNUMBER(S46),ISNUMBER(S45)),VLOOKUP(ABS(S46-S45),'IMP Table'!$A$2:$C$26,3)*SIGN(S46-S45),0)</f>
         <v/>
       </c>
-      <c r="AD46" s="9">
+      <c r="AD46" s="7">
         <f>IF(AND(ISNUMBER(T46),ISNUMBER(T43)),VLOOKUP(ABS(T46-T43),'IMP Table'!$A$2:$C$26,3)*SIGN(T46-T43),0)</f>
         <v/>
       </c>
-      <c r="AE46" s="9">
+      <c r="AE46" s="7">
         <f>IF(AND(ISNUMBER(T46),ISNUMBER(T44)),VLOOKUP(ABS(T46-T44),'IMP Table'!$A$2:$C$26,3)*SIGN(T46-T44),0)</f>
         <v/>
       </c>
-      <c r="AF46" s="9">
+      <c r="AF46" s="7">
         <f>IF(AND(ISNUMBER(T46),ISNUMBER(T45)),VLOOKUP(ABS(T46-T45),'IMP Table'!$A$2:$C$26,3)*SIGN(T46-T45),0)</f>
         <v/>
       </c>
@@ -6629,15 +6639,15 @@
         <f>AVERAGE(AA47:AC47)</f>
         <v/>
       </c>
-      <c r="N47" s="7">
+      <c r="N47" s="5">
         <f>AVERAGE(AD47:AF47)</f>
         <v/>
       </c>
-      <c r="O47" s="6">
+      <c r="O47" s="4">
         <f>IF(COUNT(U47:W47)&gt;0,Q47/COUNT(U47:W47),0.5)</f>
         <v/>
       </c>
-      <c r="P47" s="6">
+      <c r="P47" s="4">
         <f>IF(COUNT(X47:Z47)&gt;0,R47/COUNT(X47:Z47),0.5)</f>
         <v/>
       </c>
@@ -6755,15 +6765,15 @@
         <f>AVERAGE(AA48:AC48)</f>
         <v/>
       </c>
-      <c r="N48" s="7">
+      <c r="N48" s="5">
         <f>AVERAGE(AD48:AF48)</f>
         <v/>
       </c>
-      <c r="O48" s="6">
+      <c r="O48" s="4">
         <f>IF(COUNT(U48:W48)&gt;0,Q48/COUNT(U48:W48),0.5)</f>
         <v/>
       </c>
-      <c r="P48" s="6">
+      <c r="P48" s="4">
         <f>IF(COUNT(X48:Z48)&gt;0,R48/COUNT(X48:Z48),0.5)</f>
         <v/>
       </c>
@@ -6881,15 +6891,15 @@
         <f>AVERAGE(AA49:AC49)</f>
         <v/>
       </c>
-      <c r="N49" s="7">
+      <c r="N49" s="5">
         <f>AVERAGE(AD49:AF49)</f>
         <v/>
       </c>
-      <c r="O49" s="6">
+      <c r="O49" s="4">
         <f>IF(COUNT(U49:W49)&gt;0,Q49/COUNT(U49:W49),0.5)</f>
         <v/>
       </c>
-      <c r="P49" s="6">
+      <c r="P49" s="4">
         <f>IF(COUNT(X49:Z49)&gt;0,R49/COUNT(X49:Z49),0.5)</f>
         <v/>
       </c>
@@ -6959,7 +6969,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n"/>
+      <c r="A50" s="7" t="n"/>
       <c r="B50" s="19">
         <f>'By Round'!A3</f>
         <v/>
@@ -6980,27 +6990,27 @@
         <f>IF(ISBLANK('By Round'!F14),"",'By Round'!F14)</f>
         <v/>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="7">
         <f>IF(ISBLANK('By Round'!G14),"",'By Round'!G14)</f>
         <v/>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="7">
         <f>IF(ISBLANK('By Round'!H14),"",'By Round'!H14)</f>
         <v/>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="7">
         <f>IF(ISBLANK('By Round'!I14),"",'By Round'!I14)</f>
         <v/>
       </c>
-      <c r="J50" s="9">
+      <c r="J50" s="7">
         <f>IF(ISBLANK('By Round'!J14),"",'By Round'!J14)</f>
         <v/>
       </c>
-      <c r="K50" s="9">
+      <c r="K50" s="7">
         <f>IF(ISBLANK('By Round'!K14),"",'By Round'!K14)</f>
         <v/>
       </c>
-      <c r="L50" s="9">
+      <c r="L50" s="7">
         <f>IF(ISBLANK('By Round'!L14),"",'By Round'!L14)</f>
         <v/>
       </c>
@@ -7008,79 +7018,79 @@
         <f>AVERAGE(AA50:AC50)</f>
         <v/>
       </c>
-      <c r="N50" s="21">
+      <c r="N50" s="9">
         <f>AVERAGE(AD50:AF50)</f>
         <v/>
       </c>
-      <c r="O50" s="22">
+      <c r="O50" s="8">
         <f>IF(COUNT(U50:W50)&gt;0,Q50/COUNT(U50:W50),0.5)</f>
         <v/>
       </c>
-      <c r="P50" s="22">
+      <c r="P50" s="8">
         <f>IF(COUNT(X50:Z50)&gt;0,R50/COUNT(X50:Z50),0.5)</f>
         <v/>
       </c>
-      <c r="Q50" s="23">
+      <c r="Q50" s="21">
         <f>SUM(U50:W50)</f>
         <v/>
       </c>
-      <c r="R50" s="23">
+      <c r="R50" s="21">
         <f>SUM(X50:Z50)</f>
         <v/>
       </c>
-      <c r="S50" s="24">
+      <c r="S50" s="22">
         <f>IF(ISNUMBER(K50),K50,IF(ISNUMBER(L50),-L50,""))</f>
         <v/>
       </c>
-      <c r="T50" s="9">
+      <c r="T50" s="7">
         <f>IF(ISNUMBER(L50),L50,IF(ISNUMBER(K50),-K50,""))</f>
         <v/>
       </c>
-      <c r="U50" s="24">
+      <c r="U50" s="22">
         <f>IF(ISNUMBER(S50),IF(ISNUMBER(S47),IF(S50&gt;S47,1.0,IF(S50=S47,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="V50" s="9">
+      <c r="V50" s="7">
         <f>IF(ISNUMBER(S50),IF(ISNUMBER(S48),IF(S50&gt;S48,1.0,IF(S50=S48,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="W50" s="9">
+      <c r="W50" s="7">
         <f>IF(ISNUMBER(S50),IF(ISNUMBER(S49),IF(S50&gt;S49,1.0,IF(S50=S49,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="X50" s="9">
+      <c r="X50" s="7">
         <f>IF(ISNUMBER(T50),IF(ISNUMBER(T47),IF(T50&gt;T47,1.0,IF(T50=T47,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Y50" s="9">
+      <c r="Y50" s="7">
         <f>IF(ISNUMBER(T50),IF(ISNUMBER(T48),IF(T50&gt;T48,1.0,IF(T50=T48,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="Z50" s="9">
+      <c r="Z50" s="7">
         <f>IF(ISNUMBER(T50),IF(ISNUMBER(T49),IF(T50&gt;T49,1.0,IF(T50=T49,0.5,0.0)),""),"")</f>
         <v/>
       </c>
-      <c r="AA50" s="24">
+      <c r="AA50" s="22">
         <f>IF(AND(ISNUMBER(S50),ISNUMBER(S47)),VLOOKUP(ABS(S50-S47),'IMP Table'!$A$2:$C$26,3)*SIGN(S50-S47),0)</f>
         <v/>
       </c>
-      <c r="AB50" s="9">
+      <c r="AB50" s="7">
         <f>IF(AND(ISNUMBER(S50),ISNUMBER(S48)),VLOOKUP(ABS(S50-S48),'IMP Table'!$A$2:$C$26,3)*SIGN(S50-S48),0)</f>
         <v/>
       </c>
-      <c r="AC50" s="9">
+      <c r="AC50" s="7">
         <f>IF(AND(ISNUMBER(S50),ISNUMBER(S49)),VLOOKUP(ABS(S50-S49),'IMP Table'!$A$2:$C$26,3)*SIGN(S50-S49),0)</f>
         <v/>
       </c>
-      <c r="AD50" s="9">
+      <c r="AD50" s="7">
         <f>IF(AND(ISNUMBER(T50),ISNUMBER(T47)),VLOOKUP(ABS(T50-T47),'IMP Table'!$A$2:$C$26,3)*SIGN(T50-T47),0)</f>
         <v/>
       </c>
-      <c r="AE50" s="9">
+      <c r="AE50" s="7">
         <f>IF(AND(ISNUMBER(T50),ISNUMBER(T48)),VLOOKUP(ABS(T50-T48),'IMP Table'!$A$2:$C$26,3)*SIGN(T50-T48),0)</f>
         <v/>
       </c>
-      <c r="AF50" s="9">
+      <c r="AF50" s="7">
         <f>IF(AND(ISNUMBER(T50),ISNUMBER(T49)),VLOOKUP(ABS(T50-T49),'IMP Table'!$A$2:$C$26,3)*SIGN(T50-T49),0)</f>
         <v/>
       </c>
@@ -7237,12 +7247,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="15" t="n">
@@ -7288,12 +7298,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="15" t="n">
@@ -7339,12 +7349,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="15" t="n">
@@ -7379,7 +7389,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
+      <c r="A14" s="7" t="n"/>
       <c r="B14" s="19" t="n"/>
       <c r="C14" s="19" t="n"/>
       <c r="D14" s="19" t="n"/>
@@ -7391,12 +7401,12 @@
           <t>NS</t>
         </is>
       </c>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
@@ -7445,12 +7455,12 @@
           <t>NS</t>
         </is>
       </c>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="9" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="15" t="n">
@@ -7496,12 +7506,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="15" t="n">
@@ -7547,12 +7557,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="9" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="15" t="n">
@@ -7587,7 +7597,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
+      <c r="A26" s="7" t="n"/>
       <c r="B26" s="19" t="n"/>
       <c r="C26" s="19" t="n"/>
       <c r="D26" s="19" t="n"/>
@@ -7599,12 +7609,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
-      <c r="L26" s="9" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
@@ -7653,12 +7663,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="9" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="15" t="n">
@@ -7704,12 +7714,12 @@
           <t>NS</t>
         </is>
       </c>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
-      <c r="L32" s="9" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="15" t="n">
@@ -7755,12 +7765,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="9" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="7" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="15" t="n">
@@ -7795,7 +7805,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n"/>
+      <c r="A38" s="7" t="n"/>
       <c r="B38" s="19" t="n"/>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="19" t="n"/>
@@ -7807,12 +7817,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
-      <c r="L38" s="9" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="7" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
@@ -7861,12 +7871,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="L41" s="9" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="7" t="n"/>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="15" t="n">
@@ -7912,12 +7922,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
-      <c r="L44" s="9" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="15" t="n">
@@ -7963,12 +7973,12 @@
           <t>NS</t>
         </is>
       </c>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="9" t="n"/>
-      <c r="L47" s="9" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="15" t="n">
@@ -8003,7 +8013,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n"/>
+      <c r="A50" s="7" t="n"/>
       <c r="B50" s="19" t="n"/>
       <c r="C50" s="19" t="n"/>
       <c r="D50" s="19" t="n"/>
@@ -8015,12 +8025,12 @@
           <t>EW</t>
         </is>
       </c>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="9" t="n"/>
-      <c r="I50" s="9" t="n"/>
-      <c r="J50" s="9" t="n"/>
-      <c r="K50" s="9" t="n"/>
-      <c r="L50" s="9" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="7" t="n"/>
+      <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8441,22 +8451,22 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="25" t="n">
+      <c r="C3" s="23" t="n">
         <v>70</v>
       </c>
-      <c r="D3" s="25" t="n">
+      <c r="D3" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="E3" s="25" t="n">
+      <c r="E3" s="23" t="n">
         <v>230</v>
       </c>
-      <c r="F3" s="25" t="n">
+      <c r="F3" s="23" t="n">
         <v>70</v>
       </c>
-      <c r="G3" s="25" t="n">
+      <c r="G3" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="H3" s="25" t="n">
+      <c r="H3" s="23" t="n">
         <v>230</v>
       </c>
       <c r="J3" t="n">
@@ -8487,22 +8497,22 @@
       <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="23" t="n">
         <v>240</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="23" t="n">
         <v>430</v>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="F4" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="G4" s="25" t="n">
+      <c r="G4" s="23" t="n">
         <v>340</v>
       </c>
-      <c r="H4" s="25" t="n">
+      <c r="H4" s="23" t="n">
         <v>630</v>
       </c>
       <c r="J4" t="n">
@@ -8537,22 +8547,22 @@
       <c r="B5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="23" t="n">
         <v>340</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="23" t="n">
         <v>630</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="23" t="n">
         <v>540</v>
       </c>
-      <c r="H5" s="25" t="n">
+      <c r="H5" s="23" t="n">
         <v>1030</v>
       </c>
       <c r="J5" t="n">
@@ -8587,22 +8597,22 @@
       <c r="B6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="23" t="n">
         <v>130</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="23" t="n">
         <v>440</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="23" t="n">
         <v>830</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="23" t="n">
         <v>130</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="23" t="n">
         <v>740</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="23" t="n">
         <v>1430</v>
       </c>
       <c r="J6" t="n">
@@ -8637,22 +8647,22 @@
       <c r="B7" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="23" t="n">
         <v>540</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="23" t="n">
         <v>1030</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="23" t="n">
         <v>940</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="23" t="n">
         <v>1830</v>
       </c>
       <c r="J7" t="n">
@@ -8687,22 +8697,22 @@
       <c r="B8" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="23" t="n">
         <v>640</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="23" t="n">
         <v>1230</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="23" t="n">
         <v>1140</v>
       </c>
-      <c r="H8" s="25" t="n">
+      <c r="H8" s="23" t="n">
         <v>2230</v>
       </c>
       <c r="J8" t="n">
@@ -8737,22 +8747,22 @@
       <c r="B9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="23" t="n">
         <v>740</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="23" t="n">
         <v>1430</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="23" t="n">
         <v>1340</v>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="23" t="n">
         <v>2630</v>
       </c>
       <c r="J9" t="n">
@@ -8792,22 +8802,22 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="23" t="n">
         <v>80</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="23" t="n">
         <v>160</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="23" t="n">
         <v>520</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="23" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="25" t="n">
+      <c r="G10" s="23" t="n">
         <v>160</v>
       </c>
-      <c r="H10" s="25" t="n">
+      <c r="H10" s="23" t="n">
         <v>720</v>
       </c>
       <c r="J10" t="n">
@@ -8842,22 +8852,22 @@
       <c r="B11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="23" t="n">
         <v>260</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="23" t="n">
         <v>720</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="23" t="n">
         <v>360</v>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="23" t="n">
         <v>1120</v>
       </c>
       <c r="J11" t="n">
@@ -8892,22 +8902,22 @@
       <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="23" t="n">
         <v>360</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="23" t="n">
         <v>920</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="H12" s="25" t="n">
+      <c r="H12" s="23" t="n">
         <v>1520</v>
       </c>
       <c r="J12" t="n">
@@ -8942,22 +8952,22 @@
       <c r="B13" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="23" t="n">
         <v>460</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="23" t="n">
         <v>1120</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="23" t="n">
         <v>760</v>
       </c>
-      <c r="H13" s="25" t="n">
+      <c r="H13" s="23" t="n">
         <v>1920</v>
       </c>
       <c r="J13" t="n">
@@ -8992,22 +9002,22 @@
       <c r="B14" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="23" t="n">
         <v>1320</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="23" t="n">
         <v>960</v>
       </c>
-      <c r="H14" s="25" t="n">
+      <c r="H14" s="23" t="n">
         <v>2320</v>
       </c>
       <c r="J14" t="n">
@@ -9042,22 +9052,22 @@
       <c r="B15" t="n">
         <v>6</v>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="23" t="n">
         <v>230</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="23" t="n">
         <v>660</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="23" t="n">
         <v>1520</v>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="F15" s="23" t="n">
         <v>230</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G15" s="23" t="n">
         <v>1160</v>
       </c>
-      <c r="H15" s="25" t="n">
+      <c r="H15" s="23" t="n">
         <v>2720</v>
       </c>
       <c r="J15" t="n">
@@ -9092,22 +9102,22 @@
       <c r="B16" t="n">
         <v>7</v>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="23" t="n">
         <v>260</v>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="23" t="n">
         <v>760</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="23" t="n">
         <v>1720</v>
       </c>
-      <c r="F16" s="25" t="n">
+      <c r="F16" s="23" t="n">
         <v>260</v>
       </c>
-      <c r="G16" s="25" t="n">
+      <c r="G16" s="23" t="n">
         <v>1360</v>
       </c>
-      <c r="H16" s="25" t="n">
+      <c r="H16" s="23" t="n">
         <v>3120</v>
       </c>
     </row>
@@ -9120,22 +9130,22 @@
       <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="25" t="n">
+      <c r="C17" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="F17" s="25" t="n">
+      <c r="F17" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="H17" s="25" t="n">
+      <c r="H17" s="23" t="n">
         <v>760</v>
       </c>
     </row>
@@ -9143,22 +9153,22 @@
       <c r="B18" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="25" t="n">
+      <c r="C18" s="23" t="n">
         <v>120</v>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="23" t="n">
         <v>280</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="23" t="n">
         <v>760</v>
       </c>
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="23" t="n">
         <v>120</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="23" t="n">
         <v>380</v>
       </c>
-      <c r="H18" s="25" t="n">
+      <c r="H18" s="23" t="n">
         <v>1160</v>
       </c>
     </row>
@@ -9166,22 +9176,22 @@
       <c r="B19" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="23" t="n">
         <v>380</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="23" t="n">
         <v>960</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="23" t="n">
         <v>580</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="23" t="n">
         <v>1560</v>
       </c>
     </row>
@@ -9189,22 +9199,22 @@
       <c r="B20" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="23" t="n">
         <v>480</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="23" t="n">
         <v>1160</v>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F20" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="23" t="n">
         <v>1960</v>
       </c>
     </row>
@@ -9212,22 +9222,22 @@
       <c r="B21" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="23" t="n">
         <v>210</v>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="23" t="n">
         <v>580</v>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="23" t="n">
         <v>1360</v>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="F21" s="23" t="n">
         <v>210</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G21" s="23" t="n">
         <v>980</v>
       </c>
-      <c r="H21" s="25" t="n">
+      <c r="H21" s="23" t="n">
         <v>2360</v>
       </c>
     </row>
@@ -9235,22 +9245,22 @@
       <c r="B22" t="n">
         <v>6</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="23" t="n">
         <v>240</v>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D22" s="23" t="n">
         <v>680</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="23" t="n">
         <v>1560</v>
       </c>
-      <c r="F22" s="25" t="n">
+      <c r="F22" s="23" t="n">
         <v>240</v>
       </c>
-      <c r="G22" s="25" t="n">
+      <c r="G22" s="23" t="n">
         <v>1180</v>
       </c>
-      <c r="H22" s="25" t="n">
+      <c r="H22" s="23" t="n">
         <v>2760</v>
       </c>
     </row>
@@ -9258,22 +9268,22 @@
       <c r="B23" t="n">
         <v>7</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="23" t="n">
         <v>270</v>
       </c>
-      <c r="D23" s="25" t="n">
+      <c r="D23" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="23" t="n">
         <v>1760</v>
       </c>
-      <c r="F23" s="25" t="n">
+      <c r="F23" s="23" t="n">
         <v>270</v>
       </c>
-      <c r="G23" s="25" t="n">
+      <c r="G23" s="23" t="n">
         <v>1380</v>
       </c>
-      <c r="H23" s="25" t="n">
+      <c r="H23" s="23" t="n">
         <v>3160</v>
       </c>
     </row>
@@ -9286,22 +9296,22 @@
       <c r="B24" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="D24" s="25" t="n">
+      <c r="D24" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="F24" s="25" t="n">
+      <c r="F24" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="G24" s="25" t="n">
+      <c r="G24" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="H24" s="25" t="n">
+      <c r="H24" s="23" t="n">
         <v>760</v>
       </c>
     </row>
@@ -9309,22 +9319,22 @@
       <c r="B25" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="D25" s="25" t="n">
+      <c r="D25" s="23" t="n">
         <v>280</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="23" t="n">
         <v>760</v>
       </c>
-      <c r="F25" s="25" t="n">
+      <c r="F25" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="G25" s="25" t="n">
+      <c r="G25" s="23" t="n">
         <v>380</v>
       </c>
-      <c r="H25" s="25" t="n">
+      <c r="H25" s="23" t="n">
         <v>1160</v>
       </c>
     </row>
@@ -9332,22 +9342,22 @@
       <c r="B26" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="23" t="n">
         <v>130</v>
       </c>
-      <c r="D26" s="25" t="n">
+      <c r="D26" s="23" t="n">
         <v>380</v>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="23" t="n">
         <v>960</v>
       </c>
-      <c r="F26" s="25" t="n">
+      <c r="F26" s="23" t="n">
         <v>130</v>
       </c>
-      <c r="G26" s="25" t="n">
+      <c r="G26" s="23" t="n">
         <v>580</v>
       </c>
-      <c r="H26" s="25" t="n">
+      <c r="H26" s="23" t="n">
         <v>1560</v>
       </c>
     </row>
@@ -9355,22 +9365,22 @@
       <c r="B27" t="n">
         <v>5</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="D27" s="25" t="n">
+      <c r="D27" s="23" t="n">
         <v>480</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="23" t="n">
         <v>1160</v>
       </c>
-      <c r="F27" s="25" t="n">
+      <c r="F27" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="H27" s="25" t="n">
+      <c r="H27" s="23" t="n">
         <v>1960</v>
       </c>
     </row>
@@ -9378,22 +9388,22 @@
       <c r="B28" t="n">
         <v>6</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="D28" s="25" t="n">
+      <c r="D28" s="23" t="n">
         <v>580</v>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="23" t="n">
         <v>1360</v>
       </c>
-      <c r="F28" s="25" t="n">
+      <c r="F28" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="G28" s="25" t="n">
+      <c r="G28" s="23" t="n">
         <v>980</v>
       </c>
-      <c r="H28" s="25" t="n">
+      <c r="H28" s="23" t="n">
         <v>2360</v>
       </c>
     </row>
@@ -9401,22 +9411,22 @@
       <c r="B29" t="n">
         <v>7</v>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="D29" s="25" t="n">
+      <c r="D29" s="23" t="n">
         <v>680</v>
       </c>
-      <c r="E29" s="25" t="n">
+      <c r="E29" s="23" t="n">
         <v>1560</v>
       </c>
-      <c r="F29" s="25" t="n">
+      <c r="F29" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="23" t="n">
         <v>1180</v>
       </c>
-      <c r="H29" s="25" t="n">
+      <c r="H29" s="23" t="n">
         <v>2760</v>
       </c>
     </row>
@@ -9429,22 +9439,22 @@
       <c r="B30" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="D30" s="25" t="n">
+      <c r="D30" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="E30" s="25" t="n">
+      <c r="E30" s="23" t="n">
         <v>640</v>
       </c>
-      <c r="F30" s="25" t="n">
+      <c r="F30" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="G30" s="25" t="n">
+      <c r="G30" s="23" t="n">
         <v>670</v>
       </c>
-      <c r="H30" s="25" t="n">
+      <c r="H30" s="23" t="n">
         <v>840</v>
       </c>
     </row>
@@ -9452,22 +9462,22 @@
       <c r="B31" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="D31" s="25" t="n">
+      <c r="D31" s="23" t="n">
         <v>570</v>
       </c>
-      <c r="E31" s="25" t="n">
+      <c r="E31" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="F31" s="25" t="n">
+      <c r="F31" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="G31" s="25" t="n">
+      <c r="G31" s="23" t="n">
         <v>870</v>
       </c>
-      <c r="H31" s="25" t="n">
+      <c r="H31" s="23" t="n">
         <v>1240</v>
       </c>
     </row>
@@ -9475,22 +9485,22 @@
       <c r="B32" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="25" t="n">
+      <c r="C32" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="D32" s="25" t="n">
+      <c r="D32" s="23" t="n">
         <v>670</v>
       </c>
-      <c r="E32" s="25" t="n">
+      <c r="E32" s="23" t="n">
         <v>1040</v>
       </c>
-      <c r="F32" s="25" t="n">
+      <c r="F32" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="G32" s="25" t="n">
+      <c r="G32" s="23" t="n">
         <v>1070</v>
       </c>
-      <c r="H32" s="25" t="n">
+      <c r="H32" s="23" t="n">
         <v>1640</v>
       </c>
     </row>
@@ -9498,22 +9508,22 @@
       <c r="B33" t="n">
         <v>5</v>
       </c>
-      <c r="C33" s="25" t="n">
+      <c r="C33" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="D33" s="25" t="n">
+      <c r="D33" s="23" t="n">
         <v>770</v>
       </c>
-      <c r="E33" s="25" t="n">
+      <c r="E33" s="23" t="n">
         <v>1240</v>
       </c>
-      <c r="F33" s="25" t="n">
+      <c r="F33" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="G33" s="25" t="n">
+      <c r="G33" s="23" t="n">
         <v>1270</v>
       </c>
-      <c r="H33" s="25" t="n">
+      <c r="H33" s="23" t="n">
         <v>2040</v>
       </c>
     </row>
@@ -9521,22 +9531,22 @@
       <c r="B34" t="n">
         <v>6</v>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C34" s="23" t="n">
         <v>230</v>
       </c>
-      <c r="D34" s="25" t="n">
+      <c r="D34" s="23" t="n">
         <v>870</v>
       </c>
-      <c r="E34" s="25" t="n">
+      <c r="E34" s="23" t="n">
         <v>1440</v>
       </c>
-      <c r="F34" s="25" t="n">
+      <c r="F34" s="23" t="n">
         <v>230</v>
       </c>
-      <c r="G34" s="25" t="n">
+      <c r="G34" s="23" t="n">
         <v>1470</v>
       </c>
-      <c r="H34" s="25" t="n">
+      <c r="H34" s="23" t="n">
         <v>2440</v>
       </c>
     </row>
@@ -9544,22 +9554,22 @@
       <c r="B35" t="n">
         <v>7</v>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C35" s="23" t="n">
         <v>260</v>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D35" s="23" t="n">
         <v>970</v>
       </c>
-      <c r="E35" s="25" t="n">
+      <c r="E35" s="23" t="n">
         <v>1640</v>
       </c>
-      <c r="F35" s="25" t="n">
+      <c r="F35" s="23" t="n">
         <v>260</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G35" s="23" t="n">
         <v>1670</v>
       </c>
-      <c r="H35" s="25" t="n">
+      <c r="H35" s="23" t="n">
         <v>2840</v>
       </c>
     </row>
@@ -9572,22 +9582,22 @@
       <c r="B36" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="25" t="n">
+      <c r="C36" s="23" t="n">
         <v>120</v>
       </c>
-      <c r="D36" s="25" t="n">
+      <c r="D36" s="23" t="n">
         <v>490</v>
       </c>
-      <c r="E36" s="25" t="n">
+      <c r="E36" s="23" t="n">
         <v>680</v>
       </c>
-      <c r="F36" s="25" t="n">
+      <c r="F36" s="23" t="n">
         <v>120</v>
       </c>
-      <c r="G36" s="25" t="n">
+      <c r="G36" s="23" t="n">
         <v>690</v>
       </c>
-      <c r="H36" s="25" t="n">
+      <c r="H36" s="23" t="n">
         <v>880</v>
       </c>
     </row>
@@ -9595,22 +9605,22 @@
       <c r="B37" t="n">
         <v>3</v>
       </c>
-      <c r="C37" s="25" t="n">
+      <c r="C37" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="D37" s="25" t="n">
+      <c r="D37" s="23" t="n">
         <v>590</v>
       </c>
-      <c r="E37" s="25" t="n">
+      <c r="E37" s="23" t="n">
         <v>880</v>
       </c>
-      <c r="F37" s="25" t="n">
+      <c r="F37" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="G37" s="25" t="n">
+      <c r="G37" s="23" t="n">
         <v>890</v>
       </c>
-      <c r="H37" s="25" t="n">
+      <c r="H37" s="23" t="n">
         <v>1280</v>
       </c>
     </row>
@@ -9618,22 +9628,22 @@
       <c r="B38" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="25" t="n">
+      <c r="C38" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="D38" s="25" t="n">
+      <c r="D38" s="23" t="n">
         <v>690</v>
       </c>
-      <c r="E38" s="25" t="n">
+      <c r="E38" s="23" t="n">
         <v>1080</v>
       </c>
-      <c r="F38" s="25" t="n">
+      <c r="F38" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="G38" s="25" t="n">
+      <c r="G38" s="23" t="n">
         <v>1090</v>
       </c>
-      <c r="H38" s="25" t="n">
+      <c r="H38" s="23" t="n">
         <v>1680</v>
       </c>
     </row>
@@ -9641,22 +9651,22 @@
       <c r="B39" t="n">
         <v>5</v>
       </c>
-      <c r="C39" s="25" t="n">
+      <c r="C39" s="23" t="n">
         <v>210</v>
       </c>
-      <c r="D39" s="25" t="n">
+      <c r="D39" s="23" t="n">
         <v>790</v>
       </c>
-      <c r="E39" s="25" t="n">
+      <c r="E39" s="23" t="n">
         <v>1280</v>
       </c>
-      <c r="F39" s="25" t="n">
+      <c r="F39" s="23" t="n">
         <v>210</v>
       </c>
-      <c r="G39" s="25" t="n">
+      <c r="G39" s="23" t="n">
         <v>1290</v>
       </c>
-      <c r="H39" s="25" t="n">
+      <c r="H39" s="23" t="n">
         <v>2080</v>
       </c>
     </row>
@@ -9664,22 +9674,22 @@
       <c r="B40" t="n">
         <v>6</v>
       </c>
-      <c r="C40" s="25" t="n">
+      <c r="C40" s="23" t="n">
         <v>240</v>
       </c>
-      <c r="D40" s="25" t="n">
+      <c r="D40" s="23" t="n">
         <v>890</v>
       </c>
-      <c r="E40" s="25" t="n">
+      <c r="E40" s="23" t="n">
         <v>1480</v>
       </c>
-      <c r="F40" s="25" t="n">
+      <c r="F40" s="23" t="n">
         <v>240</v>
       </c>
-      <c r="G40" s="25" t="n">
+      <c r="G40" s="23" t="n">
         <v>1490</v>
       </c>
-      <c r="H40" s="25" t="n">
+      <c r="H40" s="23" t="n">
         <v>2480</v>
       </c>
     </row>
@@ -9687,22 +9697,22 @@
       <c r="B41" t="n">
         <v>7</v>
       </c>
-      <c r="C41" s="25" t="n">
+      <c r="C41" s="23" t="n">
         <v>270</v>
       </c>
-      <c r="D41" s="25" t="n">
+      <c r="D41" s="23" t="n">
         <v>990</v>
       </c>
-      <c r="E41" s="25" t="n">
+      <c r="E41" s="23" t="n">
         <v>1680</v>
       </c>
-      <c r="F41" s="25" t="n">
+      <c r="F41" s="23" t="n">
         <v>270</v>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="G41" s="23" t="n">
         <v>1690</v>
       </c>
-      <c r="H41" s="25" t="n">
+      <c r="H41" s="23" t="n">
         <v>2880</v>
       </c>
     </row>
@@ -9715,22 +9725,22 @@
       <c r="B42" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="25" t="n">
+      <c r="C42" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="D42" s="25" t="n">
+      <c r="D42" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="E42" s="25" t="n">
+      <c r="E42" s="23" t="n">
         <v>640</v>
       </c>
-      <c r="F42" s="25" t="n">
+      <c r="F42" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G42" s="23" t="n">
         <v>670</v>
       </c>
-      <c r="H42" s="25" t="n">
+      <c r="H42" s="23" t="n">
         <v>840</v>
       </c>
     </row>
@@ -9738,22 +9748,22 @@
       <c r="B43" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="25" t="n">
+      <c r="C43" s="23" t="n">
         <v>130</v>
       </c>
-      <c r="D43" s="25" t="n">
+      <c r="D43" s="23" t="n">
         <v>570</v>
       </c>
-      <c r="E43" s="25" t="n">
+      <c r="E43" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="F43" s="25" t="n">
+      <c r="F43" s="23" t="n">
         <v>130</v>
       </c>
-      <c r="G43" s="25" t="n">
+      <c r="G43" s="23" t="n">
         <v>870</v>
       </c>
-      <c r="H43" s="25" t="n">
+      <c r="H43" s="23" t="n">
         <v>1240</v>
       </c>
     </row>
@@ -9761,22 +9771,22 @@
       <c r="B44" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="25" t="n">
+      <c r="C44" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="D44" s="25" t="n">
+      <c r="D44" s="23" t="n">
         <v>670</v>
       </c>
-      <c r="E44" s="25" t="n">
+      <c r="E44" s="23" t="n">
         <v>1040</v>
       </c>
-      <c r="F44" s="25" t="n">
+      <c r="F44" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="G44" s="25" t="n">
+      <c r="G44" s="23" t="n">
         <v>1070</v>
       </c>
-      <c r="H44" s="25" t="n">
+      <c r="H44" s="23" t="n">
         <v>1640</v>
       </c>
     </row>
@@ -9784,22 +9794,22 @@
       <c r="B45" t="n">
         <v>6</v>
       </c>
-      <c r="C45" s="25" t="n">
+      <c r="C45" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="D45" s="25" t="n">
+      <c r="D45" s="23" t="n">
         <v>770</v>
       </c>
-      <c r="E45" s="25" t="n">
+      <c r="E45" s="23" t="n">
         <v>1240</v>
       </c>
-      <c r="F45" s="25" t="n">
+      <c r="F45" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="G45" s="25" t="n">
+      <c r="G45" s="23" t="n">
         <v>1270</v>
       </c>
-      <c r="H45" s="25" t="n">
+      <c r="H45" s="23" t="n">
         <v>2040</v>
       </c>
     </row>
@@ -9807,22 +9817,22 @@
       <c r="B46" t="n">
         <v>7</v>
       </c>
-      <c r="C46" s="25" t="n">
+      <c r="C46" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="D46" s="25" t="n">
+      <c r="D46" s="23" t="n">
         <v>870</v>
       </c>
-      <c r="E46" s="25" t="n">
+      <c r="E46" s="23" t="n">
         <v>1440</v>
       </c>
-      <c r="F46" s="25" t="n">
+      <c r="F46" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="G46" s="25" t="n">
+      <c r="G46" s="23" t="n">
         <v>1470</v>
       </c>
-      <c r="H46" s="25" t="n">
+      <c r="H46" s="23" t="n">
         <v>2440</v>
       </c>
     </row>
@@ -9835,22 +9845,22 @@
       <c r="B47" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="25" t="n">
+      <c r="C47" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="D47" s="25" t="n">
+      <c r="D47" s="23" t="n">
         <v>530</v>
       </c>
-      <c r="E47" s="25" t="n">
+      <c r="E47" s="23" t="n">
         <v>760</v>
       </c>
-      <c r="F47" s="25" t="n">
+      <c r="F47" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="G47" s="25" t="n">
+      <c r="G47" s="23" t="n">
         <v>730</v>
       </c>
-      <c r="H47" s="25" t="n">
+      <c r="H47" s="23" t="n">
         <v>960</v>
       </c>
     </row>
@@ -9858,22 +9868,22 @@
       <c r="B48" t="n">
         <v>4</v>
       </c>
-      <c r="C48" s="25" t="n">
+      <c r="C48" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="D48" s="25" t="n">
+      <c r="D48" s="23" t="n">
         <v>630</v>
       </c>
-      <c r="E48" s="25" t="n">
+      <c r="E48" s="23" t="n">
         <v>960</v>
       </c>
-      <c r="F48" s="25" t="n">
+      <c r="F48" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="G48" s="25" t="n">
+      <c r="G48" s="23" t="n">
         <v>930</v>
       </c>
-      <c r="H48" s="25" t="n">
+      <c r="H48" s="23" t="n">
         <v>1360</v>
       </c>
     </row>
@@ -9881,22 +9891,22 @@
       <c r="B49" t="n">
         <v>5</v>
       </c>
-      <c r="C49" s="25" t="n">
+      <c r="C49" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="D49" s="25" t="n">
+      <c r="D49" s="23" t="n">
         <v>730</v>
       </c>
-      <c r="E49" s="25" t="n">
+      <c r="E49" s="23" t="n">
         <v>1160</v>
       </c>
-      <c r="F49" s="25" t="n">
+      <c r="F49" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="G49" s="25" t="n">
+      <c r="G49" s="23" t="n">
         <v>1130</v>
       </c>
-      <c r="H49" s="25" t="n">
+      <c r="H49" s="23" t="n">
         <v>1760</v>
       </c>
     </row>
@@ -9904,22 +9914,22 @@
       <c r="B50" t="n">
         <v>6</v>
       </c>
-      <c r="C50" s="25" t="n">
+      <c r="C50" s="23" t="n">
         <v>230</v>
       </c>
-      <c r="D50" s="25" t="n">
+      <c r="D50" s="23" t="n">
         <v>830</v>
       </c>
-      <c r="E50" s="25" t="n">
+      <c r="E50" s="23" t="n">
         <v>1360</v>
       </c>
-      <c r="F50" s="25" t="n">
+      <c r="F50" s="23" t="n">
         <v>230</v>
       </c>
-      <c r="G50" s="25" t="n">
+      <c r="G50" s="23" t="n">
         <v>1330</v>
       </c>
-      <c r="H50" s="25" t="n">
+      <c r="H50" s="23" t="n">
         <v>2160</v>
       </c>
     </row>
@@ -9927,22 +9937,22 @@
       <c r="B51" t="n">
         <v>7</v>
       </c>
-      <c r="C51" s="25" t="n">
+      <c r="C51" s="23" t="n">
         <v>260</v>
       </c>
-      <c r="D51" s="25" t="n">
+      <c r="D51" s="23" t="n">
         <v>930</v>
       </c>
-      <c r="E51" s="25" t="n">
+      <c r="E51" s="23" t="n">
         <v>1560</v>
       </c>
-      <c r="F51" s="25" t="n">
+      <c r="F51" s="23" t="n">
         <v>260</v>
       </c>
-      <c r="G51" s="25" t="n">
+      <c r="G51" s="23" t="n">
         <v>1530</v>
       </c>
-      <c r="H51" s="25" t="n">
+      <c r="H51" s="23" t="n">
         <v>2560</v>
       </c>
     </row>
@@ -9955,22 +9965,22 @@
       <c r="B52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="25" t="n">
+      <c r="C52" s="23" t="n">
         <v>400</v>
       </c>
-      <c r="D52" s="25" t="n">
+      <c r="D52" s="23" t="n">
         <v>550</v>
       </c>
-      <c r="E52" s="25" t="n">
+      <c r="E52" s="23" t="n">
         <v>800</v>
       </c>
-      <c r="F52" s="25" t="n">
+      <c r="F52" s="23" t="n">
         <v>600</v>
       </c>
-      <c r="G52" s="25" t="n">
+      <c r="G52" s="23" t="n">
         <v>750</v>
       </c>
-      <c r="H52" s="25" t="n">
+      <c r="H52" s="23" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -9978,22 +9988,22 @@
       <c r="B53" t="n">
         <v>4</v>
       </c>
-      <c r="C53" s="25" t="n">
+      <c r="C53" s="23" t="n">
         <v>430</v>
       </c>
-      <c r="D53" s="25" t="n">
+      <c r="D53" s="23" t="n">
         <v>650</v>
       </c>
-      <c r="E53" s="25" t="n">
+      <c r="E53" s="23" t="n">
         <v>1000</v>
       </c>
-      <c r="F53" s="25" t="n">
+      <c r="F53" s="23" t="n">
         <v>630</v>
       </c>
-      <c r="G53" s="25" t="n">
+      <c r="G53" s="23" t="n">
         <v>950</v>
       </c>
-      <c r="H53" s="25" t="n">
+      <c r="H53" s="23" t="n">
         <v>1400</v>
       </c>
     </row>
@@ -10001,22 +10011,22 @@
       <c r="B54" t="n">
         <v>5</v>
       </c>
-      <c r="C54" s="25" t="n">
+      <c r="C54" s="23" t="n">
         <v>460</v>
       </c>
-      <c r="D54" s="25" t="n">
+      <c r="D54" s="23" t="n">
         <v>750</v>
       </c>
-      <c r="E54" s="25" t="n">
+      <c r="E54" s="23" t="n">
         <v>1200</v>
       </c>
-      <c r="F54" s="25" t="n">
+      <c r="F54" s="23" t="n">
         <v>660</v>
       </c>
-      <c r="G54" s="25" t="n">
+      <c r="G54" s="23" t="n">
         <v>1150</v>
       </c>
-      <c r="H54" s="25" t="n">
+      <c r="H54" s="23" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -10024,22 +10034,22 @@
       <c r="B55" t="n">
         <v>6</v>
       </c>
-      <c r="C55" s="25" t="n">
+      <c r="C55" s="23" t="n">
         <v>490</v>
       </c>
-      <c r="D55" s="25" t="n">
+      <c r="D55" s="23" t="n">
         <v>850</v>
       </c>
-      <c r="E55" s="25" t="n">
+      <c r="E55" s="23" t="n">
         <v>1400</v>
       </c>
-      <c r="F55" s="25" t="n">
+      <c r="F55" s="23" t="n">
         <v>690</v>
       </c>
-      <c r="G55" s="25" t="n">
+      <c r="G55" s="23" t="n">
         <v>1350</v>
       </c>
-      <c r="H55" s="25" t="n">
+      <c r="H55" s="23" t="n">
         <v>2200</v>
       </c>
     </row>
@@ -10047,22 +10057,22 @@
       <c r="B56" t="n">
         <v>7</v>
       </c>
-      <c r="C56" s="25" t="n">
+      <c r="C56" s="23" t="n">
         <v>520</v>
       </c>
-      <c r="D56" s="25" t="n">
+      <c r="D56" s="23" t="n">
         <v>950</v>
       </c>
-      <c r="E56" s="25" t="n">
+      <c r="E56" s="23" t="n">
         <v>1600</v>
       </c>
-      <c r="F56" s="25" t="n">
+      <c r="F56" s="23" t="n">
         <v>720</v>
       </c>
-      <c r="G56" s="25" t="n">
+      <c r="G56" s="23" t="n">
         <v>1550</v>
       </c>
-      <c r="H56" s="25" t="n">
+      <c r="H56" s="23" t="n">
         <v>2600</v>
       </c>
     </row>
@@ -10075,22 +10085,22 @@
       <c r="B57" t="n">
         <v>4</v>
       </c>
-      <c r="C57" s="25" t="n">
+      <c r="C57" s="23" t="n">
         <v>130</v>
       </c>
-      <c r="D57" s="25" t="n">
+      <c r="D57" s="23" t="n">
         <v>510</v>
       </c>
-      <c r="E57" s="25" t="n">
+      <c r="E57" s="23" t="n">
         <v>720</v>
       </c>
-      <c r="F57" s="25" t="n">
+      <c r="F57" s="23" t="n">
         <v>130</v>
       </c>
-      <c r="G57" s="25" t="n">
+      <c r="G57" s="23" t="n">
         <v>710</v>
       </c>
-      <c r="H57" s="25" t="n">
+      <c r="H57" s="23" t="n">
         <v>920</v>
       </c>
     </row>
@@ -10098,22 +10108,22 @@
       <c r="B58" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="25" t="n">
+      <c r="C58" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="D58" s="25" t="n">
+      <c r="D58" s="23" t="n">
         <v>610</v>
       </c>
-      <c r="E58" s="25" t="n">
+      <c r="E58" s="23" t="n">
         <v>920</v>
       </c>
-      <c r="F58" s="25" t="n">
+      <c r="F58" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="G58" s="25" t="n">
+      <c r="G58" s="23" t="n">
         <v>910</v>
       </c>
-      <c r="H58" s="25" t="n">
+      <c r="H58" s="23" t="n">
         <v>1320</v>
       </c>
     </row>
@@ -10121,22 +10131,22 @@
       <c r="B59" t="n">
         <v>6</v>
       </c>
-      <c r="C59" s="25" t="n">
+      <c r="C59" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="D59" s="25" t="n">
+      <c r="D59" s="23" t="n">
         <v>710</v>
       </c>
-      <c r="E59" s="25" t="n">
+      <c r="E59" s="23" t="n">
         <v>1120</v>
       </c>
-      <c r="F59" s="25" t="n">
+      <c r="F59" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="G59" s="25" t="n">
+      <c r="G59" s="23" t="n">
         <v>1110</v>
       </c>
-      <c r="H59" s="25" t="n">
+      <c r="H59" s="23" t="n">
         <v>1720</v>
       </c>
     </row>
@@ -10144,22 +10154,22 @@
       <c r="B60" t="n">
         <v>7</v>
       </c>
-      <c r="C60" s="25" t="n">
+      <c r="C60" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="D60" s="25" t="n">
+      <c r="D60" s="23" t="n">
         <v>810</v>
       </c>
-      <c r="E60" s="25" t="n">
+      <c r="E60" s="23" t="n">
         <v>1320</v>
       </c>
-      <c r="F60" s="25" t="n">
+      <c r="F60" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="G60" s="25" t="n">
+      <c r="G60" s="23" t="n">
         <v>1310</v>
       </c>
-      <c r="H60" s="25" t="n">
+      <c r="H60" s="23" t="n">
         <v>2120</v>
       </c>
     </row>
@@ -10172,22 +10182,22 @@
       <c r="B61" t="n">
         <v>4</v>
       </c>
-      <c r="C61" s="25" t="n">
+      <c r="C61" s="23" t="n">
         <v>420</v>
       </c>
-      <c r="D61" s="25" t="n">
+      <c r="D61" s="23" t="n">
         <v>590</v>
       </c>
-      <c r="E61" s="25" t="n">
+      <c r="E61" s="23" t="n">
         <v>880</v>
       </c>
-      <c r="F61" s="25" t="n">
+      <c r="F61" s="23" t="n">
         <v>620</v>
       </c>
-      <c r="G61" s="25" t="n">
+      <c r="G61" s="23" t="n">
         <v>790</v>
       </c>
-      <c r="H61" s="25" t="n">
+      <c r="H61" s="23" t="n">
         <v>1080</v>
       </c>
     </row>
@@ -10195,22 +10205,22 @@
       <c r="B62" t="n">
         <v>5</v>
       </c>
-      <c r="C62" s="25" t="n">
+      <c r="C62" s="23" t="n">
         <v>450</v>
       </c>
-      <c r="D62" s="25" t="n">
+      <c r="D62" s="23" t="n">
         <v>690</v>
       </c>
-      <c r="E62" s="25" t="n">
+      <c r="E62" s="23" t="n">
         <v>1080</v>
       </c>
-      <c r="F62" s="25" t="n">
+      <c r="F62" s="23" t="n">
         <v>650</v>
       </c>
-      <c r="G62" s="25" t="n">
+      <c r="G62" s="23" t="n">
         <v>990</v>
       </c>
-      <c r="H62" s="25" t="n">
+      <c r="H62" s="23" t="n">
         <v>1480</v>
       </c>
     </row>
@@ -10218,22 +10228,22 @@
       <c r="B63" t="n">
         <v>6</v>
       </c>
-      <c r="C63" s="25" t="n">
+      <c r="C63" s="23" t="n">
         <v>480</v>
       </c>
-      <c r="D63" s="25" t="n">
+      <c r="D63" s="23" t="n">
         <v>790</v>
       </c>
-      <c r="E63" s="25" t="n">
+      <c r="E63" s="23" t="n">
         <v>1280</v>
       </c>
-      <c r="F63" s="25" t="n">
+      <c r="F63" s="23" t="n">
         <v>680</v>
       </c>
-      <c r="G63" s="25" t="n">
+      <c r="G63" s="23" t="n">
         <v>1190</v>
       </c>
-      <c r="H63" s="25" t="n">
+      <c r="H63" s="23" t="n">
         <v>1880</v>
       </c>
     </row>
@@ -10241,22 +10251,22 @@
       <c r="B64" t="n">
         <v>7</v>
       </c>
-      <c r="C64" s="25" t="n">
+      <c r="C64" s="23" t="n">
         <v>510</v>
       </c>
-      <c r="D64" s="25" t="n">
+      <c r="D64" s="23" t="n">
         <v>890</v>
       </c>
-      <c r="E64" s="25" t="n">
+      <c r="E64" s="23" t="n">
         <v>1480</v>
       </c>
-      <c r="F64" s="25" t="n">
+      <c r="F64" s="23" t="n">
         <v>710</v>
       </c>
-      <c r="G64" s="25" t="n">
+      <c r="G64" s="23" t="n">
         <v>1390</v>
       </c>
-      <c r="H64" s="25" t="n">
+      <c r="H64" s="23" t="n">
         <v>2280</v>
       </c>
     </row>
@@ -10269,22 +10279,22 @@
       <c r="B65" t="n">
         <v>4</v>
       </c>
-      <c r="C65" s="25" t="n">
+      <c r="C65" s="23" t="n">
         <v>430</v>
       </c>
-      <c r="D65" s="25" t="n">
+      <c r="D65" s="23" t="n">
         <v>610</v>
       </c>
-      <c r="E65" s="25" t="n">
+      <c r="E65" s="23" t="n">
         <v>920</v>
       </c>
-      <c r="F65" s="25" t="n">
+      <c r="F65" s="23" t="n">
         <v>630</v>
       </c>
-      <c r="G65" s="25" t="n">
+      <c r="G65" s="23" t="n">
         <v>810</v>
       </c>
-      <c r="H65" s="25" t="n">
+      <c r="H65" s="23" t="n">
         <v>1120</v>
       </c>
     </row>
@@ -10292,22 +10302,22 @@
       <c r="B66" t="n">
         <v>5</v>
       </c>
-      <c r="C66" s="25" t="n">
+      <c r="C66" s="23" t="n">
         <v>460</v>
       </c>
-      <c r="D66" s="25" t="n">
+      <c r="D66" s="23" t="n">
         <v>710</v>
       </c>
-      <c r="E66" s="25" t="n">
+      <c r="E66" s="23" t="n">
         <v>1120</v>
       </c>
-      <c r="F66" s="25" t="n">
+      <c r="F66" s="23" t="n">
         <v>660</v>
       </c>
-      <c r="G66" s="25" t="n">
+      <c r="G66" s="23" t="n">
         <v>1010</v>
       </c>
-      <c r="H66" s="25" t="n">
+      <c r="H66" s="23" t="n">
         <v>1520</v>
       </c>
     </row>
@@ -10315,22 +10325,22 @@
       <c r="B67" t="n">
         <v>6</v>
       </c>
-      <c r="C67" s="25" t="n">
+      <c r="C67" s="23" t="n">
         <v>490</v>
       </c>
-      <c r="D67" s="25" t="n">
+      <c r="D67" s="23" t="n">
         <v>810</v>
       </c>
-      <c r="E67" s="25" t="n">
+      <c r="E67" s="23" t="n">
         <v>1320</v>
       </c>
-      <c r="F67" s="25" t="n">
+      <c r="F67" s="23" t="n">
         <v>690</v>
       </c>
-      <c r="G67" s="25" t="n">
+      <c r="G67" s="23" t="n">
         <v>1210</v>
       </c>
-      <c r="H67" s="25" t="n">
+      <c r="H67" s="23" t="n">
         <v>1920</v>
       </c>
     </row>
@@ -10338,22 +10348,22 @@
       <c r="B68" t="n">
         <v>7</v>
       </c>
-      <c r="C68" s="25" t="n">
+      <c r="C68" s="23" t="n">
         <v>520</v>
       </c>
-      <c r="D68" s="25" t="n">
+      <c r="D68" s="23" t="n">
         <v>910</v>
       </c>
-      <c r="E68" s="25" t="n">
+      <c r="E68" s="23" t="n">
         <v>1520</v>
       </c>
-      <c r="F68" s="25" t="n">
+      <c r="F68" s="23" t="n">
         <v>720</v>
       </c>
-      <c r="G68" s="25" t="n">
+      <c r="G68" s="23" t="n">
         <v>1410</v>
       </c>
-      <c r="H68" s="25" t="n">
+      <c r="H68" s="23" t="n">
         <v>2320</v>
       </c>
     </row>
@@ -10366,22 +10376,22 @@
       <c r="B69" t="n">
         <v>5</v>
       </c>
-      <c r="C69" s="25" t="n">
+      <c r="C69" s="23" t="n">
         <v>400</v>
       </c>
-      <c r="D69" s="25" t="n">
+      <c r="D69" s="23" t="n">
         <v>550</v>
       </c>
-      <c r="E69" s="25" t="n">
+      <c r="E69" s="23" t="n">
         <v>800</v>
       </c>
-      <c r="F69" s="25" t="n">
+      <c r="F69" s="23" t="n">
         <v>600</v>
       </c>
-      <c r="G69" s="25" t="n">
+      <c r="G69" s="23" t="n">
         <v>750</v>
       </c>
-      <c r="H69" s="25" t="n">
+      <c r="H69" s="23" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -10389,22 +10399,22 @@
       <c r="B70" t="n">
         <v>6</v>
       </c>
-      <c r="C70" s="25" t="n">
+      <c r="C70" s="23" t="n">
         <v>420</v>
       </c>
-      <c r="D70" s="25" t="n">
+      <c r="D70" s="23" t="n">
         <v>650</v>
       </c>
-      <c r="E70" s="25" t="n">
+      <c r="E70" s="23" t="n">
         <v>1000</v>
       </c>
-      <c r="F70" s="25" t="n">
+      <c r="F70" s="23" t="n">
         <v>620</v>
       </c>
-      <c r="G70" s="25" t="n">
+      <c r="G70" s="23" t="n">
         <v>950</v>
       </c>
-      <c r="H70" s="25" t="n">
+      <c r="H70" s="23" t="n">
         <v>1400</v>
       </c>
     </row>
@@ -10412,22 +10422,22 @@
       <c r="B71" t="n">
         <v>7</v>
       </c>
-      <c r="C71" s="25" t="n">
+      <c r="C71" s="23" t="n">
         <v>440</v>
       </c>
-      <c r="D71" s="25" t="n">
+      <c r="D71" s="23" t="n">
         <v>750</v>
       </c>
-      <c r="E71" s="25" t="n">
+      <c r="E71" s="23" t="n">
         <v>1200</v>
       </c>
-      <c r="F71" s="25" t="n">
+      <c r="F71" s="23" t="n">
         <v>640</v>
       </c>
-      <c r="G71" s="25" t="n">
+      <c r="G71" s="23" t="n">
         <v>1150</v>
       </c>
-      <c r="H71" s="25" t="n">
+      <c r="H71" s="23" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -10440,22 +10450,22 @@
       <c r="B72" t="n">
         <v>5</v>
       </c>
-      <c r="C72" s="25" t="n">
+      <c r="C72" s="23" t="n">
         <v>450</v>
       </c>
-      <c r="D72" s="25" t="n">
+      <c r="D72" s="23" t="n">
         <v>650</v>
       </c>
-      <c r="E72" s="25" t="n">
+      <c r="E72" s="23" t="n">
         <v>1000</v>
       </c>
-      <c r="F72" s="25" t="n">
+      <c r="F72" s="23" t="n">
         <v>650</v>
       </c>
-      <c r="G72" s="25" t="n">
+      <c r="G72" s="23" t="n">
         <v>850</v>
       </c>
-      <c r="H72" s="25" t="n">
+      <c r="H72" s="23" t="n">
         <v>1200</v>
       </c>
     </row>
@@ -10463,22 +10473,22 @@
       <c r="B73" t="n">
         <v>6</v>
       </c>
-      <c r="C73" s="25" t="n">
+      <c r="C73" s="23" t="n">
         <v>480</v>
       </c>
-      <c r="D73" s="25" t="n">
+      <c r="D73" s="23" t="n">
         <v>750</v>
       </c>
-      <c r="E73" s="25" t="n">
+      <c r="E73" s="23" t="n">
         <v>1200</v>
       </c>
-      <c r="F73" s="25" t="n">
+      <c r="F73" s="23" t="n">
         <v>680</v>
       </c>
-      <c r="G73" s="25" t="n">
+      <c r="G73" s="23" t="n">
         <v>1050</v>
       </c>
-      <c r="H73" s="25" t="n">
+      <c r="H73" s="23" t="n">
         <v>1600</v>
       </c>
     </row>
@@ -10486,22 +10496,22 @@
       <c r="B74" t="n">
         <v>7</v>
       </c>
-      <c r="C74" s="25" t="n">
+      <c r="C74" s="23" t="n">
         <v>510</v>
       </c>
-      <c r="D74" s="25" t="n">
+      <c r="D74" s="23" t="n">
         <v>850</v>
       </c>
-      <c r="E74" s="25" t="n">
+      <c r="E74" s="23" t="n">
         <v>1400</v>
       </c>
-      <c r="F74" s="25" t="n">
+      <c r="F74" s="23" t="n">
         <v>710</v>
       </c>
-      <c r="G74" s="25" t="n">
+      <c r="G74" s="23" t="n">
         <v>1250</v>
       </c>
-      <c r="H74" s="25" t="n">
+      <c r="H74" s="23" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -10514,22 +10524,22 @@
       <c r="B75" t="n">
         <v>5</v>
       </c>
-      <c r="C75" s="25" t="n">
+      <c r="C75" s="23" t="n">
         <v>460</v>
       </c>
-      <c r="D75" s="25" t="n">
+      <c r="D75" s="23" t="n">
         <v>670</v>
       </c>
-      <c r="E75" s="25" t="n">
+      <c r="E75" s="23" t="n">
         <v>1040</v>
       </c>
-      <c r="F75" s="25" t="n">
+      <c r="F75" s="23" t="n">
         <v>660</v>
       </c>
-      <c r="G75" s="25" t="n">
+      <c r="G75" s="23" t="n">
         <v>870</v>
       </c>
-      <c r="H75" s="25" t="n">
+      <c r="H75" s="23" t="n">
         <v>1240</v>
       </c>
     </row>
@@ -10537,22 +10547,22 @@
       <c r="B76" t="n">
         <v>6</v>
       </c>
-      <c r="C76" s="25" t="n">
+      <c r="C76" s="23" t="n">
         <v>490</v>
       </c>
-      <c r="D76" s="25" t="n">
+      <c r="D76" s="23" t="n">
         <v>770</v>
       </c>
-      <c r="E76" s="25" t="n">
+      <c r="E76" s="23" t="n">
         <v>1240</v>
       </c>
-      <c r="F76" s="25" t="n">
+      <c r="F76" s="23" t="n">
         <v>690</v>
       </c>
-      <c r="G76" s="25" t="n">
+      <c r="G76" s="23" t="n">
         <v>1070</v>
       </c>
-      <c r="H76" s="25" t="n">
+      <c r="H76" s="23" t="n">
         <v>1640</v>
       </c>
     </row>
@@ -10560,22 +10570,22 @@
       <c r="B77" t="n">
         <v>7</v>
       </c>
-      <c r="C77" s="25" t="n">
+      <c r="C77" s="23" t="n">
         <v>520</v>
       </c>
-      <c r="D77" s="25" t="n">
+      <c r="D77" s="23" t="n">
         <v>870</v>
       </c>
-      <c r="E77" s="25" t="n">
+      <c r="E77" s="23" t="n">
         <v>1440</v>
       </c>
-      <c r="F77" s="25" t="n">
+      <c r="F77" s="23" t="n">
         <v>720</v>
       </c>
-      <c r="G77" s="25" t="n">
+      <c r="G77" s="23" t="n">
         <v>1270</v>
       </c>
-      <c r="H77" s="25" t="n">
+      <c r="H77" s="23" t="n">
         <v>2040</v>
       </c>
     </row>
@@ -10588,22 +10598,22 @@
       <c r="B78" t="n">
         <v>6</v>
       </c>
-      <c r="C78" s="25" t="n">
+      <c r="C78" s="23" t="n">
         <v>920</v>
       </c>
-      <c r="D78" s="25" t="n">
+      <c r="D78" s="23" t="n">
         <v>1090</v>
       </c>
-      <c r="E78" s="25" t="n">
+      <c r="E78" s="23" t="n">
         <v>1380</v>
       </c>
-      <c r="F78" s="25" t="n">
+      <c r="F78" s="23" t="n">
         <v>1370</v>
       </c>
-      <c r="G78" s="25" t="n">
+      <c r="G78" s="23" t="n">
         <v>1540</v>
       </c>
-      <c r="H78" s="25" t="n">
+      <c r="H78" s="23" t="n">
         <v>1830</v>
       </c>
     </row>
@@ -10611,22 +10621,22 @@
       <c r="B79" t="n">
         <v>7</v>
       </c>
-      <c r="C79" s="25" t="n">
+      <c r="C79" s="23" t="n">
         <v>940</v>
       </c>
-      <c r="D79" s="25" t="n">
+      <c r="D79" s="23" t="n">
         <v>1190</v>
       </c>
-      <c r="E79" s="25" t="n">
+      <c r="E79" s="23" t="n">
         <v>1580</v>
       </c>
-      <c r="F79" s="25" t="n">
+      <c r="F79" s="23" t="n">
         <v>1390</v>
       </c>
-      <c r="G79" s="25" t="n">
+      <c r="G79" s="23" t="n">
         <v>1740</v>
       </c>
-      <c r="H79" s="25" t="n">
+      <c r="H79" s="23" t="n">
         <v>2230</v>
       </c>
     </row>
@@ -10639,22 +10649,22 @@
       <c r="B80" t="n">
         <v>6</v>
       </c>
-      <c r="C80" s="25" t="n">
+      <c r="C80" s="23" t="n">
         <v>980</v>
       </c>
-      <c r="D80" s="25" t="n">
+      <c r="D80" s="23" t="n">
         <v>1210</v>
       </c>
-      <c r="E80" s="25" t="n">
+      <c r="E80" s="23" t="n">
         <v>1620</v>
       </c>
-      <c r="F80" s="25" t="n">
+      <c r="F80" s="23" t="n">
         <v>1430</v>
       </c>
-      <c r="G80" s="25" t="n">
+      <c r="G80" s="23" t="n">
         <v>1660</v>
       </c>
-      <c r="H80" s="25" t="n">
+      <c r="H80" s="23" t="n">
         <v>2070</v>
       </c>
     </row>
@@ -10662,22 +10672,22 @@
       <c r="B81" t="n">
         <v>7</v>
       </c>
-      <c r="C81" s="25" t="n">
+      <c r="C81" s="23" t="n">
         <v>1010</v>
       </c>
-      <c r="D81" s="25" t="n">
+      <c r="D81" s="23" t="n">
         <v>1310</v>
       </c>
-      <c r="E81" s="25" t="n">
+      <c r="E81" s="23" t="n">
         <v>1820</v>
       </c>
-      <c r="F81" s="25" t="n">
+      <c r="F81" s="23" t="n">
         <v>1460</v>
       </c>
-      <c r="G81" s="25" t="n">
+      <c r="G81" s="23" t="n">
         <v>1860</v>
       </c>
-      <c r="H81" s="25" t="n">
+      <c r="H81" s="23" t="n">
         <v>2470</v>
       </c>
     </row>
@@ -10690,22 +10700,22 @@
       <c r="B82" t="n">
         <v>6</v>
       </c>
-      <c r="C82" s="25" t="n">
+      <c r="C82" s="23" t="n">
         <v>990</v>
       </c>
-      <c r="D82" s="25" t="n">
+      <c r="D82" s="23" t="n">
         <v>1230</v>
       </c>
-      <c r="E82" s="25" t="n">
+      <c r="E82" s="23" t="n">
         <v>1660</v>
       </c>
-      <c r="F82" s="25" t="n">
+      <c r="F82" s="23" t="n">
         <v>1440</v>
       </c>
-      <c r="G82" s="25" t="n">
+      <c r="G82" s="23" t="n">
         <v>1680</v>
       </c>
-      <c r="H82" s="25" t="n">
+      <c r="H82" s="23" t="n">
         <v>2110</v>
       </c>
     </row>
@@ -10713,22 +10723,22 @@
       <c r="B83" t="n">
         <v>7</v>
       </c>
-      <c r="C83" s="25" t="n">
+      <c r="C83" s="23" t="n">
         <v>1020</v>
       </c>
-      <c r="D83" s="25" t="n">
+      <c r="D83" s="23" t="n">
         <v>1330</v>
       </c>
-      <c r="E83" s="25" t="n">
+      <c r="E83" s="23" t="n">
         <v>1860</v>
       </c>
-      <c r="F83" s="25" t="n">
+      <c r="F83" s="23" t="n">
         <v>1470</v>
       </c>
-      <c r="G83" s="25" t="n">
+      <c r="G83" s="23" t="n">
         <v>1880</v>
       </c>
-      <c r="H83" s="25" t="n">
+      <c r="H83" s="23" t="n">
         <v>2510</v>
       </c>
     </row>
@@ -10741,22 +10751,22 @@
       <c r="B84" t="n">
         <v>7</v>
       </c>
-      <c r="C84" s="25" t="n">
+      <c r="C84" s="23" t="n">
         <v>1440</v>
       </c>
-      <c r="D84" s="25" t="n">
+      <c r="D84" s="23" t="n">
         <v>1630</v>
       </c>
-      <c r="E84" s="25" t="n">
+      <c r="E84" s="23" t="n">
         <v>1960</v>
       </c>
-      <c r="F84" s="25" t="n">
+      <c r="F84" s="23" t="n">
         <v>2140</v>
       </c>
-      <c r="G84" s="25" t="n">
+      <c r="G84" s="23" t="n">
         <v>2330</v>
       </c>
-      <c r="H84" s="25" t="n">
+      <c r="H84" s="23" t="n">
         <v>2660</v>
       </c>
     </row>
@@ -10769,22 +10779,22 @@
       <c r="B85" t="n">
         <v>7</v>
       </c>
-      <c r="C85" s="25" t="n">
+      <c r="C85" s="23" t="n">
         <v>1510</v>
       </c>
-      <c r="D85" s="25" t="n">
+      <c r="D85" s="23" t="n">
         <v>1770</v>
       </c>
-      <c r="E85" s="25" t="n">
+      <c r="E85" s="23" t="n">
         <v>2240</v>
       </c>
-      <c r="F85" s="25" t="n">
+      <c r="F85" s="23" t="n">
         <v>2210</v>
       </c>
-      <c r="G85" s="25" t="n">
+      <c r="G85" s="23" t="n">
         <v>2470</v>
       </c>
-      <c r="H85" s="25" t="n">
+      <c r="H85" s="23" t="n">
         <v>2940</v>
       </c>
     </row>
@@ -10797,22 +10807,22 @@
       <c r="B86" t="n">
         <v>7</v>
       </c>
-      <c r="C86" s="25" t="n">
+      <c r="C86" s="23" t="n">
         <v>1520</v>
       </c>
-      <c r="D86" s="25" t="n">
+      <c r="D86" s="23" t="n">
         <v>1790</v>
       </c>
-      <c r="E86" s="25" t="n">
+      <c r="E86" s="23" t="n">
         <v>2280</v>
       </c>
-      <c r="F86" s="25" t="n">
+      <c r="F86" s="23" t="n">
         <v>2220</v>
       </c>
-      <c r="G86" s="25" t="n">
+      <c r="G86" s="23" t="n">
         <v>2490</v>
       </c>
-      <c r="H86" s="25" t="n">
+      <c r="H86" s="23" t="n">
         <v>2980</v>
       </c>
     </row>

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -499,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 18, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 20, 2026.</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 90</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 52</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 17</t>
+          <t>Name 22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 19</t>
+          <t>Name 14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 89</t>
+          <t>Name 24</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 46</t>
+          <t>Name 41</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 57</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 79</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 54</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 18</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 32</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 29</t>
+          <t>Name 86</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 22</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -499,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 20, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Apr 08, 2026.</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 90</t>
+          <t>Name 86</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 52</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 22</t>
+          <t>Name 24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 21</t>
+          <t>Name 60</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 14</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 88</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 41</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 69</t>
+          <t>Name 42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 39</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 13</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 81</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 22</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -499,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Apr 08, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Apr 22, 2026.</t>
         </is>
       </c>
     </row>
@@ -581,16 +581,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>SUMIF('By Board'!D3:D50,"="&amp;A10,'By Board'!O3:O50)/12</f>
+        <f>SUMIF('By Board'!D3:D50,"="&amp;A10,'By Board'!Q3:Q50)/36</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -604,16 +604,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 60</t>
+          <t>Name 52</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>SUMIF('By Board'!D3:D50,"="&amp;A11,'By Board'!O3:O50)/12</f>
+        <f>SUMIF('By Board'!D3:D50,"="&amp;A11,'By Board'!Q3:Q50)/36</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -627,16 +627,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 29</t>
+          <t>Name 42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>SUMIF('By Board'!D3:D50,"="&amp;A12,'By Board'!O3:O50)/12</f>
+        <f>SUMIF('By Board'!D3:D50,"="&amp;A12,'By Board'!Q3:Q50)/36</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -650,16 +650,16 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 75</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 89</t>
         </is>
       </c>
       <c r="D13" s="8">
-        <f>SUMIF('By Board'!D3:D50,"="&amp;A13,'By Board'!O3:O50)/12</f>
+        <f>SUMIF('By Board'!D3:D50,"="&amp;A13,'By Board'!Q3:Q50)/36</f>
         <v/>
       </c>
       <c r="E13" s="9">
@@ -706,16 +706,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 57</t>
         </is>
       </c>
       <c r="D17" s="4">
-        <f>SUMIF('By Board'!E3:E50,"="&amp;A17,'By Board'!P3:P50)/12</f>
+        <f>SUMIF('By Board'!E3:E50,"="&amp;A17,'By Board'!R3:R50)/36</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -729,16 +729,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 21</t>
+          <t>Name 13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 13</t>
+          <t>Name 74</t>
         </is>
       </c>
       <c r="D18" s="4">
-        <f>SUMIF('By Board'!E3:E50,"="&amp;A18,'By Board'!P3:P50)/12</f>
+        <f>SUMIF('By Board'!E3:E50,"="&amp;A18,'By Board'!R3:R50)/36</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -752,16 +752,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 81</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="D19" s="4">
-        <f>SUMIF('By Board'!E3:E50,"="&amp;A19,'By Board'!P3:P50)/12</f>
+        <f>SUMIF('By Board'!E3:E50,"="&amp;A19,'By Board'!R3:R50)/36</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -780,11 +780,11 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 86</t>
         </is>
       </c>
       <c r="D20" s="8">
-        <f>SUMIF('By Board'!E3:E50,"="&amp;A20,'By Board'!P3:P50)/12</f>
+        <f>SUMIF('By Board'!E3:E50,"="&amp;A20,'By Board'!R3:R50)/36</f>
         <v/>
       </c>
       <c r="E20" s="9">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 27</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 60</t>
+          <t>Name 75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 52</t>
+          <t>Name 24</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 81</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 75</t>
+          <t>Name 35</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 89</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 57</t>
+          <t>Name 85</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 13</t>
+          <t>Name 58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 74</t>
+          <t>Name 77</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 29</t>
+          <t>Name 77</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 29</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 75</t>
+          <t>Name 71</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 81</t>
+          <t>Name 35</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 35</t>
+          <t>Name 25</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 69</t>
+          <t>Name 20</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 38</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 85</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 86</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 77</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 74</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 89</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -499,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Apr 22, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Apr 23, 2026.</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 77</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 35</t>
+          <t>Name 72</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 25</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 24</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 22</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 74</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 89</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="D20" s="8">
@@ -1080,27 +1080,27 @@
         <v/>
       </c>
       <c r="U3" s="18">
-        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S4),IF(S3&gt;S4,1.0,IF(S3=S4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S4),IF(S3&gt;S4,1.0,IF(S3=S4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V3">
-        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S5),IF(S3&gt;S5,1.0,IF(S3=S5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S5),IF(S3&gt;S5,1.0,IF(S3=S5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W3">
-        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S6),IF(S3&gt;S6,1.0,IF(S3=S6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S6),IF(S3&gt;S6,1.0,IF(S3=S6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X3">
-        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T4),IF(T3&gt;T4,1.0,IF(T3=T4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T4),IF(T3&gt;T4,1.0,IF(T3=T4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T5),IF(T3&gt;T5,1.0,IF(T3=T5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T5),IF(T3&gt;T5,1.0,IF(T3=T5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T6),IF(T3&gt;T6,1.0,IF(T3=T6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T6),IF(T3&gt;T6,1.0,IF(T3=T6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA3" s="18">
@@ -1206,27 +1206,27 @@
         <v/>
       </c>
       <c r="U4" s="18">
-        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S3),IF(S4&gt;S3,1.0,IF(S4=S3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S3),IF(S4&gt;S3,1.0,IF(S4=S3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V4">
-        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S5),IF(S4&gt;S5,1.0,IF(S4=S5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S5),IF(S4&gt;S5,1.0,IF(S4=S5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W4">
-        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S6),IF(S4&gt;S6,1.0,IF(S4=S6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S6),IF(S4&gt;S6,1.0,IF(S4=S6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X4">
-        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T3),IF(T4&gt;T3,1.0,IF(T4=T3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T3),IF(T4&gt;T3,1.0,IF(T4=T3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T5),IF(T4&gt;T5,1.0,IF(T4=T5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T5),IF(T4&gt;T5,1.0,IF(T4=T5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T6),IF(T4&gt;T6,1.0,IF(T4=T6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T6),IF(T4&gt;T6,1.0,IF(T4=T6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA4" s="18">
@@ -1332,27 +1332,27 @@
         <v/>
       </c>
       <c r="U5" s="18">
-        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S3),IF(S5&gt;S3,1.0,IF(S5=S3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S3),IF(S5&gt;S3,1.0,IF(S5=S3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V5">
-        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S4),IF(S5&gt;S4,1.0,IF(S5=S4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S4),IF(S5&gt;S4,1.0,IF(S5=S4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W5">
-        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S6),IF(S5&gt;S6,1.0,IF(S5=S6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S6),IF(S5&gt;S6,1.0,IF(S5=S6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X5">
-        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T3),IF(T5&gt;T3,1.0,IF(T5=T3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T3),IF(T5&gt;T3,1.0,IF(T5=T3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T4),IF(T5&gt;T4,1.0,IF(T5=T4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T4),IF(T5&gt;T4,1.0,IF(T5=T4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z5">
-        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T6),IF(T5&gt;T6,1.0,IF(T5=T6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T6),IF(T5&gt;T6,1.0,IF(T5=T6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA5" s="18">
@@ -1459,27 +1459,27 @@
         <v/>
       </c>
       <c r="U6" s="22">
-        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S3),IF(S6&gt;S3,1.0,IF(S6=S3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S3),IF(S6&gt;S3,1.0,IF(S6=S3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V6" s="7">
-        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S4),IF(S6&gt;S4,1.0,IF(S6=S4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S4),IF(S6&gt;S4,1.0,IF(S6=S4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W6" s="7">
-        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S5),IF(S6&gt;S5,1.0,IF(S6=S5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S5),IF(S6&gt;S5,1.0,IF(S6=S5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X6" s="7">
-        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T3),IF(T6&gt;T3,1.0,IF(T6=T3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T3),IF(T6&gt;T3,1.0,IF(T6=T3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y6" s="7">
-        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T4),IF(T6&gt;T4,1.0,IF(T6=T4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T4),IF(T6&gt;T4,1.0,IF(T6=T4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z6" s="7">
-        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T5),IF(T6&gt;T5,1.0,IF(T6=T5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T5),IF(T6&gt;T5,1.0,IF(T6=T5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA6" s="22">
@@ -1588,27 +1588,27 @@
         <v/>
       </c>
       <c r="U7" s="18">
-        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S8),IF(S7&gt;S8,1.0,IF(S7=S8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S8),IF(S7&gt;S8,1.0,IF(S7=S8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V7">
-        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S9),IF(S7&gt;S9,1.0,IF(S7=S9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S9),IF(S7&gt;S9,1.0,IF(S7=S9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W7">
-        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S10),IF(S7&gt;S10,1.0,IF(S7=S10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S10),IF(S7&gt;S10,1.0,IF(S7=S10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X7">
-        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T8),IF(T7&gt;T8,1.0,IF(T7=T8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T8),IF(T7&gt;T8,1.0,IF(T7=T8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T9),IF(T7&gt;T9,1.0,IF(T7=T9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T9),IF(T7&gt;T9,1.0,IF(T7=T9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z7">
-        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T10),IF(T7&gt;T10,1.0,IF(T7=T10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T10),IF(T7&gt;T10,1.0,IF(T7=T10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA7" s="18">
@@ -1714,27 +1714,27 @@
         <v/>
       </c>
       <c r="U8" s="18">
-        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S7),IF(S8&gt;S7,1.0,IF(S8=S7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S7),IF(S8&gt;S7,1.0,IF(S8=S7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V8">
-        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S9),IF(S8&gt;S9,1.0,IF(S8=S9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S9),IF(S8&gt;S9,1.0,IF(S8=S9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W8">
-        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S10),IF(S8&gt;S10,1.0,IF(S8=S10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S10),IF(S8&gt;S10,1.0,IF(S8=S10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X8">
-        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T7),IF(T8&gt;T7,1.0,IF(T8=T7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T7),IF(T8&gt;T7,1.0,IF(T8=T7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T9),IF(T8&gt;T9,1.0,IF(T8=T9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T9),IF(T8&gt;T9,1.0,IF(T8=T9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z8">
-        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T10),IF(T8&gt;T10,1.0,IF(T8=T10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T10),IF(T8&gt;T10,1.0,IF(T8=T10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA8" s="18">
@@ -1840,27 +1840,27 @@
         <v/>
       </c>
       <c r="U9" s="18">
-        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S7),IF(S9&gt;S7,1.0,IF(S9=S7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S7),IF(S9&gt;S7,1.0,IF(S9=S7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V9">
-        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S8),IF(S9&gt;S8,1.0,IF(S9=S8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S8),IF(S9&gt;S8,1.0,IF(S9=S8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W9">
-        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S10),IF(S9&gt;S10,1.0,IF(S9=S10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S10),IF(S9&gt;S10,1.0,IF(S9=S10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X9">
-        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T7),IF(T9&gt;T7,1.0,IF(T9=T7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T7),IF(T9&gt;T7,1.0,IF(T9=T7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T8),IF(T9&gt;T8,1.0,IF(T9=T8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T8),IF(T9&gt;T8,1.0,IF(T9=T8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z9">
-        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T10),IF(T9&gt;T10,1.0,IF(T9=T10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T10),IF(T9&gt;T10,1.0,IF(T9=T10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA9" s="18">
@@ -1967,27 +1967,27 @@
         <v/>
       </c>
       <c r="U10" s="22">
-        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S7),IF(S10&gt;S7,1.0,IF(S10=S7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S7),IF(S10&gt;S7,1.0,IF(S10=S7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V10" s="7">
-        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S8),IF(S10&gt;S8,1.0,IF(S10=S8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S8),IF(S10&gt;S8,1.0,IF(S10=S8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W10" s="7">
-        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S9),IF(S10&gt;S9,1.0,IF(S10=S9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S9),IF(S10&gt;S9,1.0,IF(S10=S9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X10" s="7">
-        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T7),IF(T10&gt;T7,1.0,IF(T10=T7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T7),IF(T10&gt;T7,1.0,IF(T10=T7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y10" s="7">
-        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T8),IF(T10&gt;T8,1.0,IF(T10=T8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T8),IF(T10&gt;T8,1.0,IF(T10=T8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z10" s="7">
-        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T9),IF(T10&gt;T9,1.0,IF(T10=T9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T9),IF(T10&gt;T9,1.0,IF(T10=T9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA10" s="22">
@@ -2096,27 +2096,27 @@
         <v/>
       </c>
       <c r="U11" s="18">
-        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S12),IF(S11&gt;S12,1.0,IF(S11=S12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S12),IF(S11&gt;S12,1.0,IF(S11=S12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V11">
-        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S13),IF(S11&gt;S13,1.0,IF(S11=S13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S13),IF(S11&gt;S13,1.0,IF(S11=S13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W11">
-        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S14),IF(S11&gt;S14,1.0,IF(S11=S14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S14),IF(S11&gt;S14,1.0,IF(S11=S14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X11">
-        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T12),IF(T11&gt;T12,1.0,IF(T11=T12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T12),IF(T11&gt;T12,1.0,IF(T11=T12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T13),IF(T11&gt;T13,1.0,IF(T11=T13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T13),IF(T11&gt;T13,1.0,IF(T11=T13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T14),IF(T11&gt;T14,1.0,IF(T11=T14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T14),IF(T11&gt;T14,1.0,IF(T11=T14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA11" s="18">
@@ -2222,27 +2222,27 @@
         <v/>
       </c>
       <c r="U12" s="18">
-        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S11),IF(S12&gt;S11,1.0,IF(S12=S11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S11),IF(S12&gt;S11,1.0,IF(S12=S11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V12">
-        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S13),IF(S12&gt;S13,1.0,IF(S12=S13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S13),IF(S12&gt;S13,1.0,IF(S12=S13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W12">
-        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S14),IF(S12&gt;S14,1.0,IF(S12=S14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S14),IF(S12&gt;S14,1.0,IF(S12=S14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X12">
-        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T11),IF(T12&gt;T11,1.0,IF(T12=T11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T11),IF(T12&gt;T11,1.0,IF(T12=T11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T13),IF(T12&gt;T13,1.0,IF(T12=T13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T13),IF(T12&gt;T13,1.0,IF(T12=T13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z12">
-        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T14),IF(T12&gt;T14,1.0,IF(T12=T14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T14),IF(T12&gt;T14,1.0,IF(T12=T14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA12" s="18">
@@ -2348,27 +2348,27 @@
         <v/>
       </c>
       <c r="U13" s="18">
-        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S11),IF(S13&gt;S11,1.0,IF(S13=S11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S11),IF(S13&gt;S11,1.0,IF(S13=S11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V13">
-        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S12),IF(S13&gt;S12,1.0,IF(S13=S12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S12),IF(S13&gt;S12,1.0,IF(S13=S12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W13">
-        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S14),IF(S13&gt;S14,1.0,IF(S13=S14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S14),IF(S13&gt;S14,1.0,IF(S13=S14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X13">
-        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T11),IF(T13&gt;T11,1.0,IF(T13=T11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T11),IF(T13&gt;T11,1.0,IF(T13=T11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T12),IF(T13&gt;T12,1.0,IF(T13=T12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T12),IF(T13&gt;T12,1.0,IF(T13=T12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z13">
-        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T14),IF(T13&gt;T14,1.0,IF(T13=T14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T14),IF(T13&gt;T14,1.0,IF(T13=T14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA13" s="18">
@@ -2475,27 +2475,27 @@
         <v/>
       </c>
       <c r="U14" s="22">
-        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S11),IF(S14&gt;S11,1.0,IF(S14=S11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S11),IF(S14&gt;S11,1.0,IF(S14=S11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V14" s="7">
-        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S12),IF(S14&gt;S12,1.0,IF(S14=S12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S12),IF(S14&gt;S12,1.0,IF(S14=S12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W14" s="7">
-        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S13),IF(S14&gt;S13,1.0,IF(S14=S13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S13),IF(S14&gt;S13,1.0,IF(S14=S13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X14" s="7">
-        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T11),IF(T14&gt;T11,1.0,IF(T14=T11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T11),IF(T14&gt;T11,1.0,IF(T14=T11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y14" s="7">
-        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T12),IF(T14&gt;T12,1.0,IF(T14=T12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T12),IF(T14&gt;T12,1.0,IF(T14=T12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z14" s="7">
-        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T13),IF(T14&gt;T13,1.0,IF(T14=T13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T13),IF(T14&gt;T13,1.0,IF(T14=T13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA14" s="22">
@@ -2604,27 +2604,27 @@
         <v/>
       </c>
       <c r="U15" s="18">
-        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S16),IF(S15&gt;S16,1.0,IF(S15=S16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S16),IF(S15&gt;S16,1.0,IF(S15=S16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V15">
-        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S17),IF(S15&gt;S17,1.0,IF(S15=S17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S17),IF(S15&gt;S17,1.0,IF(S15=S17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W15">
-        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S18),IF(S15&gt;S18,1.0,IF(S15=S18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S18),IF(S15&gt;S18,1.0,IF(S15=S18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X15">
-        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T16),IF(T15&gt;T16,1.0,IF(T15=T16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T16),IF(T15&gt;T16,1.0,IF(T15=T16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T17),IF(T15&gt;T17,1.0,IF(T15=T17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T17),IF(T15&gt;T17,1.0,IF(T15=T17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z15">
-        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T18),IF(T15&gt;T18,1.0,IF(T15=T18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T18),IF(T15&gt;T18,1.0,IF(T15=T18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA15" s="18">
@@ -2730,27 +2730,27 @@
         <v/>
       </c>
       <c r="U16" s="18">
-        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S15),IF(S16&gt;S15,1.0,IF(S16=S15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S15),IF(S16&gt;S15,1.0,IF(S16=S15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V16">
-        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S17),IF(S16&gt;S17,1.0,IF(S16=S17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S17),IF(S16&gt;S17,1.0,IF(S16=S17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W16">
-        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S18),IF(S16&gt;S18,1.0,IF(S16=S18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S18),IF(S16&gt;S18,1.0,IF(S16=S18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X16">
-        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T15),IF(T16&gt;T15,1.0,IF(T16=T15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T15),IF(T16&gt;T15,1.0,IF(T16=T15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T17),IF(T16&gt;T17,1.0,IF(T16=T17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T17),IF(T16&gt;T17,1.0,IF(T16=T17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z16">
-        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T18),IF(T16&gt;T18,1.0,IF(T16=T18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T18),IF(T16&gt;T18,1.0,IF(T16=T18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA16" s="18">
@@ -2856,27 +2856,27 @@
         <v/>
       </c>
       <c r="U17" s="18">
-        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S15),IF(S17&gt;S15,1.0,IF(S17=S15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S15),IF(S17&gt;S15,1.0,IF(S17=S15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V17">
-        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S16),IF(S17&gt;S16,1.0,IF(S17=S16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S16),IF(S17&gt;S16,1.0,IF(S17=S16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W17">
-        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S18),IF(S17&gt;S18,1.0,IF(S17=S18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S18),IF(S17&gt;S18,1.0,IF(S17=S18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X17">
-        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T15),IF(T17&gt;T15,1.0,IF(T17=T15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T15),IF(T17&gt;T15,1.0,IF(T17=T15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T16),IF(T17&gt;T16,1.0,IF(T17=T16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T16),IF(T17&gt;T16,1.0,IF(T17=T16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z17">
-        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T18),IF(T17&gt;T18,1.0,IF(T17=T18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T18),IF(T17&gt;T18,1.0,IF(T17=T18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA17" s="18">
@@ -2983,27 +2983,27 @@
         <v/>
       </c>
       <c r="U18" s="22">
-        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S15),IF(S18&gt;S15,1.0,IF(S18=S15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S15),IF(S18&gt;S15,1.0,IF(S18=S15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V18" s="7">
-        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S16),IF(S18&gt;S16,1.0,IF(S18=S16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S16),IF(S18&gt;S16,1.0,IF(S18=S16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W18" s="7">
-        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S17),IF(S18&gt;S17,1.0,IF(S18=S17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S17),IF(S18&gt;S17,1.0,IF(S18=S17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X18" s="7">
-        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T15),IF(T18&gt;T15,1.0,IF(T18=T15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T15),IF(T18&gt;T15,1.0,IF(T18=T15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y18" s="7">
-        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T16),IF(T18&gt;T16,1.0,IF(T18=T16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T16),IF(T18&gt;T16,1.0,IF(T18=T16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z18" s="7">
-        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T17),IF(T18&gt;T17,1.0,IF(T18=T17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T17),IF(T18&gt;T17,1.0,IF(T18=T17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA18" s="22">
@@ -3112,27 +3112,27 @@
         <v/>
       </c>
       <c r="U19" s="18">
-        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S20),IF(S19&gt;S20,1.0,IF(S19=S20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S20),IF(S19&gt;S20,1.0,IF(S19=S20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V19">
-        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S21),IF(S19&gt;S21,1.0,IF(S19=S21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S21),IF(S19&gt;S21,1.0,IF(S19=S21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W19">
-        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S22),IF(S19&gt;S22,1.0,IF(S19=S22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S22),IF(S19&gt;S22,1.0,IF(S19=S22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X19">
-        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T20),IF(T19&gt;T20,1.0,IF(T19=T20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T20),IF(T19&gt;T20,1.0,IF(T19=T20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T21),IF(T19&gt;T21,1.0,IF(T19=T21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T21),IF(T19&gt;T21,1.0,IF(T19=T21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z19">
-        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T22),IF(T19&gt;T22,1.0,IF(T19=T22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T22),IF(T19&gt;T22,1.0,IF(T19=T22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA19" s="18">
@@ -3238,27 +3238,27 @@
         <v/>
       </c>
       <c r="U20" s="18">
-        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S19),IF(S20&gt;S19,1.0,IF(S20=S19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S19),IF(S20&gt;S19,1.0,IF(S20=S19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V20">
-        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S21),IF(S20&gt;S21,1.0,IF(S20=S21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S21),IF(S20&gt;S21,1.0,IF(S20=S21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W20">
-        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S22),IF(S20&gt;S22,1.0,IF(S20=S22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S22),IF(S20&gt;S22,1.0,IF(S20=S22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X20">
-        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T19),IF(T20&gt;T19,1.0,IF(T20=T19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T19),IF(T20&gt;T19,1.0,IF(T20=T19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T21),IF(T20&gt;T21,1.0,IF(T20=T21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T21),IF(T20&gt;T21,1.0,IF(T20=T21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z20">
-        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T22),IF(T20&gt;T22,1.0,IF(T20=T22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T22),IF(T20&gt;T22,1.0,IF(T20=T22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA20" s="18">
@@ -3364,27 +3364,27 @@
         <v/>
       </c>
       <c r="U21" s="18">
-        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S19),IF(S21&gt;S19,1.0,IF(S21=S19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S19),IF(S21&gt;S19,1.0,IF(S21=S19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V21">
-        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S20),IF(S21&gt;S20,1.0,IF(S21=S20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S20),IF(S21&gt;S20,1.0,IF(S21=S20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W21">
-        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S22),IF(S21&gt;S22,1.0,IF(S21=S22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S22),IF(S21&gt;S22,1.0,IF(S21=S22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X21">
-        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T19),IF(T21&gt;T19,1.0,IF(T21=T19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T19),IF(T21&gt;T19,1.0,IF(T21=T19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T20),IF(T21&gt;T20,1.0,IF(T21=T20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T20),IF(T21&gt;T20,1.0,IF(T21=T20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z21">
-        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T22),IF(T21&gt;T22,1.0,IF(T21=T22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T22),IF(T21&gt;T22,1.0,IF(T21=T22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA21" s="18">
@@ -3491,27 +3491,27 @@
         <v/>
       </c>
       <c r="U22" s="22">
-        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S19),IF(S22&gt;S19,1.0,IF(S22=S19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S19),IF(S22&gt;S19,1.0,IF(S22=S19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V22" s="7">
-        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S20),IF(S22&gt;S20,1.0,IF(S22=S20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S20),IF(S22&gt;S20,1.0,IF(S22=S20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W22" s="7">
-        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S21),IF(S22&gt;S21,1.0,IF(S22=S21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S21),IF(S22&gt;S21,1.0,IF(S22=S21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X22" s="7">
-        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T19),IF(T22&gt;T19,1.0,IF(T22=T19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T19),IF(T22&gt;T19,1.0,IF(T22=T19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y22" s="7">
-        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T20),IF(T22&gt;T20,1.0,IF(T22=T20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T20),IF(T22&gt;T20,1.0,IF(T22=T20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z22" s="7">
-        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T21),IF(T22&gt;T21,1.0,IF(T22=T21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T21),IF(T22&gt;T21,1.0,IF(T22=T21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA22" s="22">
@@ -3620,27 +3620,27 @@
         <v/>
       </c>
       <c r="U23" s="18">
-        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S24),IF(S23&gt;S24,1.0,IF(S23=S24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S24),IF(S23&gt;S24,1.0,IF(S23=S24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V23">
-        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S25),IF(S23&gt;S25,1.0,IF(S23=S25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S25),IF(S23&gt;S25,1.0,IF(S23=S25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W23">
-        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S26),IF(S23&gt;S26,1.0,IF(S23=S26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S26),IF(S23&gt;S26,1.0,IF(S23=S26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X23">
-        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T24),IF(T23&gt;T24,1.0,IF(T23=T24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T24),IF(T23&gt;T24,1.0,IF(T23=T24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T25),IF(T23&gt;T25,1.0,IF(T23=T25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T25),IF(T23&gt;T25,1.0,IF(T23=T25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z23">
-        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T26),IF(T23&gt;T26,1.0,IF(T23=T26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T26),IF(T23&gt;T26,1.0,IF(T23=T26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA23" s="18">
@@ -3746,27 +3746,27 @@
         <v/>
       </c>
       <c r="U24" s="18">
-        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S23),IF(S24&gt;S23,1.0,IF(S24=S23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S23),IF(S24&gt;S23,1.0,IF(S24=S23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V24">
-        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S25),IF(S24&gt;S25,1.0,IF(S24=S25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S25),IF(S24&gt;S25,1.0,IF(S24=S25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W24">
-        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S26),IF(S24&gt;S26,1.0,IF(S24=S26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S26),IF(S24&gt;S26,1.0,IF(S24=S26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X24">
-        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T23),IF(T24&gt;T23,1.0,IF(T24=T23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T23),IF(T24&gt;T23,1.0,IF(T24=T23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T25),IF(T24&gt;T25,1.0,IF(T24=T25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T25),IF(T24&gt;T25,1.0,IF(T24=T25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z24">
-        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T26),IF(T24&gt;T26,1.0,IF(T24=T26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T26),IF(T24&gt;T26,1.0,IF(T24=T26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA24" s="18">
@@ -3872,27 +3872,27 @@
         <v/>
       </c>
       <c r="U25" s="18">
-        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S23),IF(S25&gt;S23,1.0,IF(S25=S23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S23),IF(S25&gt;S23,1.0,IF(S25=S23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V25">
-        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S24),IF(S25&gt;S24,1.0,IF(S25=S24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S24),IF(S25&gt;S24,1.0,IF(S25=S24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W25">
-        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S26),IF(S25&gt;S26,1.0,IF(S25=S26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S26),IF(S25&gt;S26,1.0,IF(S25=S26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X25">
-        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T23),IF(T25&gt;T23,1.0,IF(T25=T23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T23),IF(T25&gt;T23,1.0,IF(T25=T23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T24),IF(T25&gt;T24,1.0,IF(T25=T24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T24),IF(T25&gt;T24,1.0,IF(T25=T24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z25">
-        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T26),IF(T25&gt;T26,1.0,IF(T25=T26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T26),IF(T25&gt;T26,1.0,IF(T25=T26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA25" s="18">
@@ -3999,27 +3999,27 @@
         <v/>
       </c>
       <c r="U26" s="22">
-        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S23),IF(S26&gt;S23,1.0,IF(S26=S23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S23),IF(S26&gt;S23,1.0,IF(S26=S23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V26" s="7">
-        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S24),IF(S26&gt;S24,1.0,IF(S26=S24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S24),IF(S26&gt;S24,1.0,IF(S26=S24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W26" s="7">
-        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S25),IF(S26&gt;S25,1.0,IF(S26=S25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S25),IF(S26&gt;S25,1.0,IF(S26=S25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X26" s="7">
-        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T23),IF(T26&gt;T23,1.0,IF(T26=T23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T23),IF(T26&gt;T23,1.0,IF(T26=T23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y26" s="7">
-        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T24),IF(T26&gt;T24,1.0,IF(T26=T24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T24),IF(T26&gt;T24,1.0,IF(T26=T24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z26" s="7">
-        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T25),IF(T26&gt;T25,1.0,IF(T26=T25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T25),IF(T26&gt;T25,1.0,IF(T26=T25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA26" s="22">
@@ -4128,27 +4128,27 @@
         <v/>
       </c>
       <c r="U27" s="18">
-        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S28),IF(S27&gt;S28,1.0,IF(S27=S28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S28),IF(S27&gt;S28,1.0,IF(S27=S28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V27">
-        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S29),IF(S27&gt;S29,1.0,IF(S27=S29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S29),IF(S27&gt;S29,1.0,IF(S27=S29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W27">
-        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S30),IF(S27&gt;S30,1.0,IF(S27=S30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S30),IF(S27&gt;S30,1.0,IF(S27=S30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X27">
-        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T28),IF(T27&gt;T28,1.0,IF(T27=T28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T28),IF(T27&gt;T28,1.0,IF(T27=T28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T29),IF(T27&gt;T29,1.0,IF(T27=T29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T29),IF(T27&gt;T29,1.0,IF(T27=T29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z27">
-        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T30),IF(T27&gt;T30,1.0,IF(T27=T30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T30),IF(T27&gt;T30,1.0,IF(T27=T30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA27" s="18">
@@ -4254,27 +4254,27 @@
         <v/>
       </c>
       <c r="U28" s="18">
-        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S27),IF(S28&gt;S27,1.0,IF(S28=S27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S27),IF(S28&gt;S27,1.0,IF(S28=S27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V28">
-        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S29),IF(S28&gt;S29,1.0,IF(S28=S29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S29),IF(S28&gt;S29,1.0,IF(S28=S29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W28">
-        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S30),IF(S28&gt;S30,1.0,IF(S28=S30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S30),IF(S28&gt;S30,1.0,IF(S28=S30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X28">
-        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T27),IF(T28&gt;T27,1.0,IF(T28=T27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T27),IF(T28&gt;T27,1.0,IF(T28=T27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T29),IF(T28&gt;T29,1.0,IF(T28=T29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T29),IF(T28&gt;T29,1.0,IF(T28=T29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z28">
-        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T30),IF(T28&gt;T30,1.0,IF(T28=T30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T30),IF(T28&gt;T30,1.0,IF(T28=T30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA28" s="18">
@@ -4380,27 +4380,27 @@
         <v/>
       </c>
       <c r="U29" s="18">
-        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S27),IF(S29&gt;S27,1.0,IF(S29=S27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S27),IF(S29&gt;S27,1.0,IF(S29=S27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V29">
-        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S28),IF(S29&gt;S28,1.0,IF(S29=S28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S28),IF(S29&gt;S28,1.0,IF(S29=S28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W29">
-        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S30),IF(S29&gt;S30,1.0,IF(S29=S30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S30),IF(S29&gt;S30,1.0,IF(S29=S30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X29">
-        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T27),IF(T29&gt;T27,1.0,IF(T29=T27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T27),IF(T29&gt;T27,1.0,IF(T29=T27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T28),IF(T29&gt;T28,1.0,IF(T29=T28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T28),IF(T29&gt;T28,1.0,IF(T29=T28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z29">
-        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T30),IF(T29&gt;T30,1.0,IF(T29=T30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T30),IF(T29&gt;T30,1.0,IF(T29=T30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA29" s="18">
@@ -4507,27 +4507,27 @@
         <v/>
       </c>
       <c r="U30" s="22">
-        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S27),IF(S30&gt;S27,1.0,IF(S30=S27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S27),IF(S30&gt;S27,1.0,IF(S30=S27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V30" s="7">
-        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S28),IF(S30&gt;S28,1.0,IF(S30=S28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S28),IF(S30&gt;S28,1.0,IF(S30=S28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W30" s="7">
-        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S29),IF(S30&gt;S29,1.0,IF(S30=S29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S29),IF(S30&gt;S29,1.0,IF(S30=S29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X30" s="7">
-        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T27),IF(T30&gt;T27,1.0,IF(T30=T27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T27),IF(T30&gt;T27,1.0,IF(T30=T27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y30" s="7">
-        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T28),IF(T30&gt;T28,1.0,IF(T30=T28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T28),IF(T30&gt;T28,1.0,IF(T30=T28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z30" s="7">
-        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T29),IF(T30&gt;T29,1.0,IF(T30=T29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T29),IF(T30&gt;T29,1.0,IF(T30=T29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA30" s="22">
@@ -4636,27 +4636,27 @@
         <v/>
       </c>
       <c r="U31" s="18">
-        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S32),IF(S31&gt;S32,1.0,IF(S31=S32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S32),IF(S31&gt;S32,1.0,IF(S31=S32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V31">
-        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S33),IF(S31&gt;S33,1.0,IF(S31=S33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S33),IF(S31&gt;S33,1.0,IF(S31=S33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W31">
-        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S34),IF(S31&gt;S34,1.0,IF(S31=S34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S34),IF(S31&gt;S34,1.0,IF(S31=S34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X31">
-        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T32),IF(T31&gt;T32,1.0,IF(T31=T32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T32),IF(T31&gt;T32,1.0,IF(T31=T32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T33),IF(T31&gt;T33,1.0,IF(T31=T33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T33),IF(T31&gt;T33,1.0,IF(T31=T33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z31">
-        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T34),IF(T31&gt;T34,1.0,IF(T31=T34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T34),IF(T31&gt;T34,1.0,IF(T31=T34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA31" s="18">
@@ -4762,27 +4762,27 @@
         <v/>
       </c>
       <c r="U32" s="18">
-        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S31),IF(S32&gt;S31,1.0,IF(S32=S31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S31),IF(S32&gt;S31,1.0,IF(S32=S31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V32">
-        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S33),IF(S32&gt;S33,1.0,IF(S32=S33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S33),IF(S32&gt;S33,1.0,IF(S32=S33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W32">
-        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S34),IF(S32&gt;S34,1.0,IF(S32=S34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S34),IF(S32&gt;S34,1.0,IF(S32=S34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X32">
-        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T31),IF(T32&gt;T31,1.0,IF(T32=T31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T31),IF(T32&gt;T31,1.0,IF(T32=T31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T33),IF(T32&gt;T33,1.0,IF(T32=T33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T33),IF(T32&gt;T33,1.0,IF(T32=T33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z32">
-        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T34),IF(T32&gt;T34,1.0,IF(T32=T34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T34),IF(T32&gt;T34,1.0,IF(T32=T34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA32" s="18">
@@ -4888,27 +4888,27 @@
         <v/>
       </c>
       <c r="U33" s="18">
-        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S31),IF(S33&gt;S31,1.0,IF(S33=S31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S31),IF(S33&gt;S31,1.0,IF(S33=S31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V33">
-        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S32),IF(S33&gt;S32,1.0,IF(S33=S32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S32),IF(S33&gt;S32,1.0,IF(S33=S32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W33">
-        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S34),IF(S33&gt;S34,1.0,IF(S33=S34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S34),IF(S33&gt;S34,1.0,IF(S33=S34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X33">
-        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T31),IF(T33&gt;T31,1.0,IF(T33=T31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T31),IF(T33&gt;T31,1.0,IF(T33=T31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T32),IF(T33&gt;T32,1.0,IF(T33=T32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T32),IF(T33&gt;T32,1.0,IF(T33=T32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z33">
-        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T34),IF(T33&gt;T34,1.0,IF(T33=T34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T34),IF(T33&gt;T34,1.0,IF(T33=T34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA33" s="18">
@@ -5015,27 +5015,27 @@
         <v/>
       </c>
       <c r="U34" s="22">
-        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S31),IF(S34&gt;S31,1.0,IF(S34=S31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S31),IF(S34&gt;S31,1.0,IF(S34=S31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V34" s="7">
-        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S32),IF(S34&gt;S32,1.0,IF(S34=S32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S32),IF(S34&gt;S32,1.0,IF(S34=S32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W34" s="7">
-        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S33),IF(S34&gt;S33,1.0,IF(S34=S33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S33),IF(S34&gt;S33,1.0,IF(S34=S33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X34" s="7">
-        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T31),IF(T34&gt;T31,1.0,IF(T34=T31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T31),IF(T34&gt;T31,1.0,IF(T34=T31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y34" s="7">
-        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T32),IF(T34&gt;T32,1.0,IF(T34=T32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T32),IF(T34&gt;T32,1.0,IF(T34=T32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z34" s="7">
-        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T33),IF(T34&gt;T33,1.0,IF(T34=T33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T33),IF(T34&gt;T33,1.0,IF(T34=T33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA34" s="22">
@@ -5144,27 +5144,27 @@
         <v/>
       </c>
       <c r="U35" s="18">
-        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S36),IF(S35&gt;S36,1.0,IF(S35=S36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S36),IF(S35&gt;S36,1.0,IF(S35=S36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V35">
-        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S37),IF(S35&gt;S37,1.0,IF(S35=S37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S37),IF(S35&gt;S37,1.0,IF(S35=S37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W35">
-        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S38),IF(S35&gt;S38,1.0,IF(S35=S38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S38),IF(S35&gt;S38,1.0,IF(S35=S38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X35">
-        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T36),IF(T35&gt;T36,1.0,IF(T35=T36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T36),IF(T35&gt;T36,1.0,IF(T35=T36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T37),IF(T35&gt;T37,1.0,IF(T35=T37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T37),IF(T35&gt;T37,1.0,IF(T35=T37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z35">
-        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T38),IF(T35&gt;T38,1.0,IF(T35=T38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T38),IF(T35&gt;T38,1.0,IF(T35=T38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA35" s="18">
@@ -5270,27 +5270,27 @@
         <v/>
       </c>
       <c r="U36" s="18">
-        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S35),IF(S36&gt;S35,1.0,IF(S36=S35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S35),IF(S36&gt;S35,1.0,IF(S36=S35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V36">
-        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S37),IF(S36&gt;S37,1.0,IF(S36=S37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S37),IF(S36&gt;S37,1.0,IF(S36=S37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W36">
-        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S38),IF(S36&gt;S38,1.0,IF(S36=S38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S38),IF(S36&gt;S38,1.0,IF(S36=S38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X36">
-        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T35),IF(T36&gt;T35,1.0,IF(T36=T35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T35),IF(T36&gt;T35,1.0,IF(T36=T35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T37),IF(T36&gt;T37,1.0,IF(T36=T37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T37),IF(T36&gt;T37,1.0,IF(T36=T37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z36">
-        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T38),IF(T36&gt;T38,1.0,IF(T36=T38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T38),IF(T36&gt;T38,1.0,IF(T36=T38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA36" s="18">
@@ -5396,27 +5396,27 @@
         <v/>
       </c>
       <c r="U37" s="18">
-        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S35),IF(S37&gt;S35,1.0,IF(S37=S35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S35),IF(S37&gt;S35,1.0,IF(S37=S35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V37">
-        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S36),IF(S37&gt;S36,1.0,IF(S37=S36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S36),IF(S37&gt;S36,1.0,IF(S37=S36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W37">
-        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S38),IF(S37&gt;S38,1.0,IF(S37=S38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S38),IF(S37&gt;S38,1.0,IF(S37=S38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X37">
-        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T35),IF(T37&gt;T35,1.0,IF(T37=T35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T35),IF(T37&gt;T35,1.0,IF(T37=T35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T36),IF(T37&gt;T36,1.0,IF(T37=T36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T36),IF(T37&gt;T36,1.0,IF(T37=T36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z37">
-        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T38),IF(T37&gt;T38,1.0,IF(T37=T38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T38),IF(T37&gt;T38,1.0,IF(T37=T38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA37" s="18">
@@ -5523,27 +5523,27 @@
         <v/>
       </c>
       <c r="U38" s="22">
-        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S35),IF(S38&gt;S35,1.0,IF(S38=S35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S35),IF(S38&gt;S35,1.0,IF(S38=S35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V38" s="7">
-        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S36),IF(S38&gt;S36,1.0,IF(S38=S36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S36),IF(S38&gt;S36,1.0,IF(S38=S36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W38" s="7">
-        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S37),IF(S38&gt;S37,1.0,IF(S38=S37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S37),IF(S38&gt;S37,1.0,IF(S38=S37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X38" s="7">
-        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T35),IF(T38&gt;T35,1.0,IF(T38=T35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T35),IF(T38&gt;T35,1.0,IF(T38=T35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y38" s="7">
-        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T36),IF(T38&gt;T36,1.0,IF(T38=T36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T36),IF(T38&gt;T36,1.0,IF(T38=T36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z38" s="7">
-        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T37),IF(T38&gt;T37,1.0,IF(T38=T37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T37),IF(T38&gt;T37,1.0,IF(T38=T37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA38" s="22">
@@ -5652,27 +5652,27 @@
         <v/>
       </c>
       <c r="U39" s="18">
-        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S40),IF(S39&gt;S40,1.0,IF(S39=S40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S40),IF(S39&gt;S40,1.0,IF(S39=S40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V39">
-        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S41),IF(S39&gt;S41,1.0,IF(S39=S41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S41),IF(S39&gt;S41,1.0,IF(S39=S41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W39">
-        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S42),IF(S39&gt;S42,1.0,IF(S39=S42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S42),IF(S39&gt;S42,1.0,IF(S39=S42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X39">
-        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T40),IF(T39&gt;T40,1.0,IF(T39=T40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T40),IF(T39&gt;T40,1.0,IF(T39=T40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T41),IF(T39&gt;T41,1.0,IF(T39=T41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T41),IF(T39&gt;T41,1.0,IF(T39=T41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z39">
-        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T42),IF(T39&gt;T42,1.0,IF(T39=T42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T42),IF(T39&gt;T42,1.0,IF(T39=T42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA39" s="18">
@@ -5778,27 +5778,27 @@
         <v/>
       </c>
       <c r="U40" s="18">
-        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S39),IF(S40&gt;S39,1.0,IF(S40=S39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S39),IF(S40&gt;S39,1.0,IF(S40=S39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V40">
-        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S41),IF(S40&gt;S41,1.0,IF(S40=S41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S41),IF(S40&gt;S41,1.0,IF(S40=S41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W40">
-        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S42),IF(S40&gt;S42,1.0,IF(S40=S42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S42),IF(S40&gt;S42,1.0,IF(S40=S42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X40">
-        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T39),IF(T40&gt;T39,1.0,IF(T40=T39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T39),IF(T40&gt;T39,1.0,IF(T40=T39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T41),IF(T40&gt;T41,1.0,IF(T40=T41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T41),IF(T40&gt;T41,1.0,IF(T40=T41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z40">
-        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T42),IF(T40&gt;T42,1.0,IF(T40=T42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T42),IF(T40&gt;T42,1.0,IF(T40=T42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA40" s="18">
@@ -5904,27 +5904,27 @@
         <v/>
       </c>
       <c r="U41" s="18">
-        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S39),IF(S41&gt;S39,1.0,IF(S41=S39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S39),IF(S41&gt;S39,1.0,IF(S41=S39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V41">
-        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S40),IF(S41&gt;S40,1.0,IF(S41=S40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S40),IF(S41&gt;S40,1.0,IF(S41=S40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W41">
-        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S42),IF(S41&gt;S42,1.0,IF(S41=S42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S42),IF(S41&gt;S42,1.0,IF(S41=S42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X41">
-        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T39),IF(T41&gt;T39,1.0,IF(T41=T39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T39),IF(T41&gt;T39,1.0,IF(T41=T39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T40),IF(T41&gt;T40,1.0,IF(T41=T40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T40),IF(T41&gt;T40,1.0,IF(T41=T40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z41">
-        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T42),IF(T41&gt;T42,1.0,IF(T41=T42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T42),IF(T41&gt;T42,1.0,IF(T41=T42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA41" s="18">
@@ -6031,27 +6031,27 @@
         <v/>
       </c>
       <c r="U42" s="22">
-        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S39),IF(S42&gt;S39,1.0,IF(S42=S39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S39),IF(S42&gt;S39,1.0,IF(S42=S39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V42" s="7">
-        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S40),IF(S42&gt;S40,1.0,IF(S42=S40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S40),IF(S42&gt;S40,1.0,IF(S42=S40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W42" s="7">
-        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S41),IF(S42&gt;S41,1.0,IF(S42=S41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S41),IF(S42&gt;S41,1.0,IF(S42=S41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X42" s="7">
-        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T39),IF(T42&gt;T39,1.0,IF(T42=T39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T39),IF(T42&gt;T39,1.0,IF(T42=T39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y42" s="7">
-        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T40),IF(T42&gt;T40,1.0,IF(T42=T40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T40),IF(T42&gt;T40,1.0,IF(T42=T40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z42" s="7">
-        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T41),IF(T42&gt;T41,1.0,IF(T42=T41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T41),IF(T42&gt;T41,1.0,IF(T42=T41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA42" s="22">
@@ -6160,27 +6160,27 @@
         <v/>
       </c>
       <c r="U43" s="18">
-        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S44),IF(S43&gt;S44,1.0,IF(S43=S44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S44),IF(S43&gt;S44,1.0,IF(S43=S44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V43">
-        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S45),IF(S43&gt;S45,1.0,IF(S43=S45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S45),IF(S43&gt;S45,1.0,IF(S43=S45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W43">
-        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S46),IF(S43&gt;S46,1.0,IF(S43=S46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S46),IF(S43&gt;S46,1.0,IF(S43=S46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X43">
-        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T44),IF(T43&gt;T44,1.0,IF(T43=T44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T44),IF(T43&gt;T44,1.0,IF(T43=T44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T45),IF(T43&gt;T45,1.0,IF(T43=T45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T45),IF(T43&gt;T45,1.0,IF(T43=T45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z43">
-        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T46),IF(T43&gt;T46,1.0,IF(T43=T46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T46),IF(T43&gt;T46,1.0,IF(T43=T46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA43" s="18">
@@ -6286,27 +6286,27 @@
         <v/>
       </c>
       <c r="U44" s="18">
-        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S43),IF(S44&gt;S43,1.0,IF(S44=S43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S43),IF(S44&gt;S43,1.0,IF(S44=S43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V44">
-        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S45),IF(S44&gt;S45,1.0,IF(S44=S45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S45),IF(S44&gt;S45,1.0,IF(S44=S45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W44">
-        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S46),IF(S44&gt;S46,1.0,IF(S44=S46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S46),IF(S44&gt;S46,1.0,IF(S44=S46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X44">
-        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T43),IF(T44&gt;T43,1.0,IF(T44=T43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T43),IF(T44&gt;T43,1.0,IF(T44=T43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T45),IF(T44&gt;T45,1.0,IF(T44=T45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T45),IF(T44&gt;T45,1.0,IF(T44=T45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z44">
-        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T46),IF(T44&gt;T46,1.0,IF(T44=T46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T46),IF(T44&gt;T46,1.0,IF(T44=T46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA44" s="18">
@@ -6412,27 +6412,27 @@
         <v/>
       </c>
       <c r="U45" s="18">
-        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S43),IF(S45&gt;S43,1.0,IF(S45=S43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S43),IF(S45&gt;S43,1.0,IF(S45=S43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V45">
-        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S44),IF(S45&gt;S44,1.0,IF(S45=S44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S44),IF(S45&gt;S44,1.0,IF(S45=S44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W45">
-        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S46),IF(S45&gt;S46,1.0,IF(S45=S46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S46),IF(S45&gt;S46,1.0,IF(S45=S46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X45">
-        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T43),IF(T45&gt;T43,1.0,IF(T45=T43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T43),IF(T45&gt;T43,1.0,IF(T45=T43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T44),IF(T45&gt;T44,1.0,IF(T45=T44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T44),IF(T45&gt;T44,1.0,IF(T45=T44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z45">
-        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T46),IF(T45&gt;T46,1.0,IF(T45=T46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T46),IF(T45&gt;T46,1.0,IF(T45=T46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA45" s="18">
@@ -6539,27 +6539,27 @@
         <v/>
       </c>
       <c r="U46" s="22">
-        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S43),IF(S46&gt;S43,1.0,IF(S46=S43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S43),IF(S46&gt;S43,1.0,IF(S46=S43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V46" s="7">
-        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S44),IF(S46&gt;S44,1.0,IF(S46=S44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S44),IF(S46&gt;S44,1.0,IF(S46=S44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W46" s="7">
-        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S45),IF(S46&gt;S45,1.0,IF(S46=S45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S45),IF(S46&gt;S45,1.0,IF(S46=S45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X46" s="7">
-        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T43),IF(T46&gt;T43,1.0,IF(T46=T43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T43),IF(T46&gt;T43,1.0,IF(T46=T43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y46" s="7">
-        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T44),IF(T46&gt;T44,1.0,IF(T46=T44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T44),IF(T46&gt;T44,1.0,IF(T46=T44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z46" s="7">
-        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T45),IF(T46&gt;T45,1.0,IF(T46=T45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T45),IF(T46&gt;T45,1.0,IF(T46=T45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA46" s="22">
@@ -6668,27 +6668,27 @@
         <v/>
       </c>
       <c r="U47" s="18">
-        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S48),IF(S47&gt;S48,1.0,IF(S47=S48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S48),IF(S47&gt;S48,1.0,IF(S47=S48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V47">
-        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S49),IF(S47&gt;S49,1.0,IF(S47=S49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S49),IF(S47&gt;S49,1.0,IF(S47=S49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W47">
-        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S50),IF(S47&gt;S50,1.0,IF(S47=S50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S50),IF(S47&gt;S50,1.0,IF(S47=S50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X47">
-        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T48),IF(T47&gt;T48,1.0,IF(T47=T48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T48),IF(T47&gt;T48,1.0,IF(T47=T48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T49),IF(T47&gt;T49,1.0,IF(T47=T49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T49),IF(T47&gt;T49,1.0,IF(T47=T49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z47">
-        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T50),IF(T47&gt;T50,1.0,IF(T47=T50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T50),IF(T47&gt;T50,1.0,IF(T47=T50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA47" s="18">
@@ -6794,27 +6794,27 @@
         <v/>
       </c>
       <c r="U48" s="18">
-        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S47),IF(S48&gt;S47,1.0,IF(S48=S47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S47),IF(S48&gt;S47,1.0,IF(S48=S47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V48">
-        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S49),IF(S48&gt;S49,1.0,IF(S48=S49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S49),IF(S48&gt;S49,1.0,IF(S48=S49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W48">
-        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S50),IF(S48&gt;S50,1.0,IF(S48=S50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S50),IF(S48&gt;S50,1.0,IF(S48=S50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X48">
-        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T47),IF(T48&gt;T47,1.0,IF(T48=T47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T47),IF(T48&gt;T47,1.0,IF(T48=T47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T49),IF(T48&gt;T49,1.0,IF(T48=T49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T49),IF(T48&gt;T49,1.0,IF(T48=T49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z48">
-        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T50),IF(T48&gt;T50,1.0,IF(T48=T50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T50),IF(T48&gt;T50,1.0,IF(T48=T50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA48" s="18">
@@ -6920,27 +6920,27 @@
         <v/>
       </c>
       <c r="U49" s="18">
-        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S47),IF(S49&gt;S47,1.0,IF(S49=S47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S47),IF(S49&gt;S47,1.0,IF(S49=S47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V49">
-        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S48),IF(S49&gt;S48,1.0,IF(S49=S48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S48),IF(S49&gt;S48,1.0,IF(S49=S48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W49">
-        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S50),IF(S49&gt;S50,1.0,IF(S49=S50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S50),IF(S49&gt;S50,1.0,IF(S49=S50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X49">
-        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T47),IF(T49&gt;T47,1.0,IF(T49=T47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T47),IF(T49&gt;T47,1.0,IF(T49=T47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T48),IF(T49&gt;T48,1.0,IF(T49=T48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T48),IF(T49&gt;T48,1.0,IF(T49=T48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z49">
-        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T50),IF(T49&gt;T50,1.0,IF(T49=T50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T50),IF(T49&gt;T50,1.0,IF(T49=T50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA49" s="18">
@@ -7047,27 +7047,27 @@
         <v/>
       </c>
       <c r="U50" s="22">
-        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S47),IF(S50&gt;S47,1.0,IF(S50=S47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S47),IF(S50&gt;S47,1.0,IF(S50=S47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V50" s="7">
-        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S48),IF(S50&gt;S48,1.0,IF(S50=S48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S48),IF(S50&gt;S48,1.0,IF(S50=S48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W50" s="7">
-        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S49),IF(S50&gt;S49,1.0,IF(S50=S49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S49),IF(S50&gt;S49,1.0,IF(S50=S49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X50" s="7">
-        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T47),IF(T50&gt;T47,1.0,IF(T50=T47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T47),IF(T50&gt;T47,1.0,IF(T50=T47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y50" s="7">
-        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T48),IF(T50&gt;T48,1.0,IF(T50=T48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T48),IF(T50&gt;T48,1.0,IF(T50=T48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z50" s="7">
-        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T49),IF(T50&gt;T49,1.0,IF(T50=T49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T49),IF(T50&gt;T49,1.0,IF(T50=T49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA50" s="22">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 47</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 19</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 72</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 76</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 76</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 62</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 20</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 14</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,7 +775,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 14</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 57</t>
+          <t>Name 23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 76</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 76</t>
+          <t>Name 87</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 21</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 77</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 62</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 40</t>
+          <t>Name 13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 14</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 85</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -499,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Apr 23, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Jun 18, 2026.</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 14</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 23</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 19</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 87</t>
+          <t>Name 72</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 77</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 69</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 12</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 13</t>
+          <t>Name 56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 85</t>
+          <t>Name 88</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 29</t>
+          <t>Name 74</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -499,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Jun 18, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Jul 29, 2026.</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 19</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 71</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 54</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 19</t>
+          <t>Name 89</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 72</t>
+          <t>Name 40</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 36</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 21</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 12</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 56</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 41</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 74</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 69</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 87</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 35</t>
+          <t>Name 38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 54</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 89</t>
+          <t>Name 32</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 40</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 71</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 39</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 41</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 32</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 87</t>
+          <t>Name 52</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 38</t>
+          <t>Name 36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 27</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 74</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 85</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 32</t>
+          <t>Name 52</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 18</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 20</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 38</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 32</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -499,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Jul 29, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Jul 30, 2026.</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 52</t>
+          <t>Name 42</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 36</t>
+          <t>Name 60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 74</t>
+          <t>Name 25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 85</t>
+          <t>Name 86</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 52</t>
+          <t>Name 81</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 18</t>
+          <t>Name 85</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 38</t>
+          <t>Name 62</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 13</t>
         </is>
       </c>
       <c r="D20" s="8">

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -499,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Jul 30, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Aug 05, 2026.</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -609,7 +609,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 19</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 25</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 75</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 81</t>
+          <t>Name 90</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 85</t>
+          <t>Name 13</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 87</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 84</t>
+          <t>Name 39</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 62</t>
+          <t>Name 25</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
+          <t>Name 58</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
           <t>Name 80</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Name 13</t>
         </is>
       </c>
       <c r="D20" s="8">
@@ -8531,15 +8531,15 @@
         <v/>
       </c>
       <c r="N4">
-        <f>K3-100</f>
+        <f>N3-100</f>
         <v/>
       </c>
       <c r="O4">
-        <f>L3-300</f>
+        <f>O3-300</f>
         <v/>
       </c>
       <c r="P4">
-        <f>L4*2</f>
+        <f>O4*2</f>
         <v/>
       </c>
     </row>
@@ -8581,15 +8581,15 @@
         <v/>
       </c>
       <c r="N5">
-        <f>K4-100</f>
+        <f>N4-100</f>
         <v/>
       </c>
       <c r="O5">
-        <f>L4-300</f>
+        <f>O4-300</f>
         <v/>
       </c>
       <c r="P5">
-        <f>L5*2</f>
+        <f>O5*2</f>
         <v/>
       </c>
     </row>
@@ -8631,15 +8631,15 @@
         <v/>
       </c>
       <c r="N6">
-        <f>K5-100</f>
+        <f>N5-100</f>
         <v/>
       </c>
       <c r="O6">
-        <f>L5-300</f>
+        <f>O5-300</f>
         <v/>
       </c>
       <c r="P6">
-        <f>L6*2</f>
+        <f>O6*2</f>
         <v/>
       </c>
     </row>
@@ -8681,15 +8681,15 @@
         <v/>
       </c>
       <c r="N7">
-        <f>K6-100</f>
+        <f>N6-100</f>
         <v/>
       </c>
       <c r="O7">
-        <f>L6-300</f>
+        <f>O6-300</f>
         <v/>
       </c>
       <c r="P7">
-        <f>L7*2</f>
+        <f>O7*2</f>
         <v/>
       </c>
     </row>
@@ -8731,15 +8731,15 @@
         <v/>
       </c>
       <c r="N8">
-        <f>K7-100</f>
+        <f>N7-100</f>
         <v/>
       </c>
       <c r="O8">
-        <f>L7-300</f>
+        <f>O7-300</f>
         <v/>
       </c>
       <c r="P8">
-        <f>L8*2</f>
+        <f>O8*2</f>
         <v/>
       </c>
     </row>
@@ -8781,15 +8781,15 @@
         <v/>
       </c>
       <c r="N9">
-        <f>K8-100</f>
+        <f>N8-100</f>
         <v/>
       </c>
       <c r="O9">
-        <f>L8-300</f>
+        <f>O8-300</f>
         <v/>
       </c>
       <c r="P9">
-        <f>L9*2</f>
+        <f>O9*2</f>
         <v/>
       </c>
     </row>
@@ -8836,15 +8836,15 @@
         <v/>
       </c>
       <c r="N10">
-        <f>K9-100</f>
+        <f>N9-100</f>
         <v/>
       </c>
       <c r="O10">
-        <f>L9-300</f>
+        <f>O9-300</f>
         <v/>
       </c>
       <c r="P10">
-        <f>L10*2</f>
+        <f>O10*2</f>
         <v/>
       </c>
     </row>
@@ -8886,15 +8886,15 @@
         <v/>
       </c>
       <c r="N11">
-        <f>K10-100</f>
+        <f>N10-100</f>
         <v/>
       </c>
       <c r="O11">
-        <f>L10-300</f>
+        <f>O10-300</f>
         <v/>
       </c>
       <c r="P11">
-        <f>L11*2</f>
+        <f>O11*2</f>
         <v/>
       </c>
     </row>
@@ -8936,15 +8936,15 @@
         <v/>
       </c>
       <c r="N12">
-        <f>K11-100</f>
+        <f>N11-100</f>
         <v/>
       </c>
       <c r="O12">
-        <f>L11-300</f>
+        <f>O11-300</f>
         <v/>
       </c>
       <c r="P12">
-        <f>L12*2</f>
+        <f>O12*2</f>
         <v/>
       </c>
     </row>
@@ -8986,15 +8986,15 @@
         <v/>
       </c>
       <c r="N13">
-        <f>K12-100</f>
+        <f>N12-100</f>
         <v/>
       </c>
       <c r="O13">
-        <f>L12-300</f>
+        <f>O12-300</f>
         <v/>
       </c>
       <c r="P13">
-        <f>L13*2</f>
+        <f>O13*2</f>
         <v/>
       </c>
     </row>
@@ -9036,15 +9036,15 @@
         <v/>
       </c>
       <c r="N14">
-        <f>K13-100</f>
+        <f>N13-100</f>
         <v/>
       </c>
       <c r="O14">
-        <f>L13-300</f>
+        <f>O13-300</f>
         <v/>
       </c>
       <c r="P14">
-        <f>L14*2</f>
+        <f>O14*2</f>
         <v/>
       </c>
     </row>
@@ -9086,15 +9086,15 @@
         <v/>
       </c>
       <c r="N15">
-        <f>K14-100</f>
+        <f>N14-100</f>
         <v/>
       </c>
       <c r="O15">
-        <f>L14-300</f>
+        <f>O14-300</f>
         <v/>
       </c>
       <c r="P15">
-        <f>L15*2</f>
+        <f>O15*2</f>
         <v/>
       </c>
     </row>

--- a/mitchell8x3Sq.xlsx
+++ b/mitchell8x3Sq.xlsx
@@ -499,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Aug 05, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Sep 06, 2026.</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 18</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 60</t>
+          <t>Name 12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 19</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 75</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Name 90</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="D13" s="8">
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Name 13</t>
+          <t>Name 40</t>
         </is>
       </c>
       <c r="D17" s="4">
@@ -729,12 +729,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name 87</t>
+          <t>Name 46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D18" s="4">
@@ -752,12 +752,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Name 25</t>
+          <t>Name 12</t>
         </is>
       </c>
       <c r="D19" s="4">
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 12</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="D20" s="8">
